--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61BA31B5-40EA-4E74-8202-1C295B217A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C72915-4098-419A-92A9-6563818524E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9685,7 +9685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
         <v>650</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>31</v>
       </c>
       <c r="S112" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BAF6C6-6A60-427D-8272-64F73427C893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C21A134-395A-480A-BB5B-15B2C53F1DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3131" uniqueCount="1246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3164" uniqueCount="1256">
   <si>
     <t>Image</t>
   </si>
@@ -2545,9 +2545,6 @@
     <t>1857</t>
   </si>
   <si>
-    <t>"Des glaneuses"</t>
-  </si>
-  <si>
     <t>83,5 cm</t>
   </si>
   <si>
@@ -3758,6 +3755,39 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Camille_Pissarro_-_La_C%C3%B4te_du_Jallais%2C_Pontoise_-_1867.jpg/1280px-Camille_Pissarro_-_La_C%C3%B4te_du_Jallais%2C_Pontoise_-_1867.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Museum of Fine Arts (MFA)</t>
+  </si>
+  <si>
+    <t>Le Semeur</t>
+  </si>
+  <si>
+    <t>101.6</t>
+  </si>
+  <si>
+    <t>82.6</t>
+  </si>
+  <si>
+    <t>1868-1873</t>
+  </si>
+  <si>
+    <t>Le Printemps</t>
+  </si>
+  <si>
+    <t>"Les glaneuses"</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/40/Jean-Fran%C3%A7ois_Millet_-_Le_Semeur.jpg/960px-Jean-Fran%C3%A7ois_Millet_-_Le_Semeur.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a1/Jean-Fran%C3%A7ois_Millet_%28II%29_007.jpg/1280px-Jean-Fran%C3%A7ois_Millet_%28II%29_007.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bergère avec son troupeau</t>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Jean-Fran%C3%A7ois_Millet_(II)_006.jpg#/media/File:Jean-Fran%C3%A7ois_Millet_(II)_-_Spring_-_WGA15693.jpg</t>
   </si>
 </sst>
 </file>
@@ -4207,26 +4237,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T238"/>
+  <dimension ref="A1:T241"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
     <col min="3" max="3" width="14.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="4.85546875" customWidth="1"/>
+    <col min="5" max="5" width="3.5703125" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" customWidth="1"/>
     <col min="7" max="7" width="11.140625" customWidth="1"/>
     <col min="8" max="8" width="12.140625" customWidth="1"/>
     <col min="9" max="9" width="23" customWidth="1"/>
     <col min="10" max="10" width="20.5703125" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="35" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="12" max="12" width="26.42578125" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="12.140625" customWidth="1"/>
     <col min="15" max="15" width="20.42578125" customWidth="1"/>
     <col min="16" max="17" width="10" customWidth="1"/>
-    <col min="18" max="18" width="12" customWidth="1"/>
+    <col min="18" max="18" width="7.85546875" customWidth="1"/>
     <col min="19" max="19" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4335,7 +4365,7 @@
         <v>31</v>
       </c>
       <c r="S2" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4384,7 +4414,7 @@
         <v>31</v>
       </c>
       <c r="S3" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4433,7 +4463,7 @@
         <v>31</v>
       </c>
       <c r="S4" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4482,7 +4512,7 @@
         <v>31</v>
       </c>
       <c r="S5" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4531,7 +4561,7 @@
         <v>31</v>
       </c>
       <c r="S6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4853,7 +4883,7 @@
         <v>91</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="4" t="s">
@@ -5075,7 +5105,7 @@
     </row>
     <row r="18" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>97</v>
@@ -5101,10 +5131,10 @@
         <v>34</v>
       </c>
       <c r="K18" s="9" t="s">
+        <v>1241</v>
+      </c>
+      <c r="L18" s="10" t="s">
         <v>1242</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>1243</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
@@ -5115,7 +5145,7 @@
         <v>87</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="R18" s="9" t="s">
         <v>31</v>
@@ -6897,7 +6927,7 @@
         <v>315</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>63</v>
@@ -8796,7 +8826,7 @@
         <v>91</v>
       </c>
       <c r="J92" s="9" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="K92" s="9"/>
       <c r="L92" s="10" t="s">
@@ -8992,7 +9022,7 @@
         <v>91</v>
       </c>
       <c r="J96" s="9" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="K96" s="9"/>
       <c r="L96" s="10" t="s">
@@ -9624,7 +9654,7 @@
         <v>640</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>445</v>
@@ -9673,7 +9703,7 @@
         <v>643</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>592</v>
@@ -9722,7 +9752,7 @@
         <v>288</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>592</v>
@@ -10389,7 +10419,7 @@
         <v>187</v>
       </c>
       <c r="S124" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10835,7 +10865,7 @@
     </row>
     <row r="134" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="13" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B134" s="9" t="s">
         <v>743</v>
@@ -10862,11 +10892,11 @@
       </c>
       <c r="K134" s="9"/>
       <c r="L134" s="10" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="M134" s="10"/>
       <c r="N134" s="10" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="O134" s="9" t="s">
         <v>28</v>
@@ -11599,7 +11629,7 @@
       </c>
       <c r="K149" s="9"/>
       <c r="L149" s="10" t="s">
-        <v>841</v>
+        <v>1251</v>
       </c>
       <c r="M149" s="10"/>
       <c r="N149" s="10"/>
@@ -11607,7 +11637,7 @@
         <v>28</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="Q149" s="9" t="s">
         <v>66</v>
@@ -11616,12 +11646,12 @@
         <v>31</v>
       </c>
       <c r="S149" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B150" s="9" t="s">
         <v>838</v>
@@ -11638,7 +11668,7 @@
         <v>46</v>
       </c>
       <c r="H150" s="9" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="I150" s="9" t="s">
         <v>40</v>
@@ -11648,7 +11678,7 @@
       </c>
       <c r="K150" s="9"/>
       <c r="L150" s="10" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M150" s="10"/>
       <c r="N150" s="10"/>
@@ -11656,136 +11686,136 @@
         <v>28</v>
       </c>
       <c r="P150" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="Q150" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="Q150" s="9" t="s">
-        <v>847</v>
-      </c>
       <c r="R150" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S150" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="6" t="s">
-        <v>848</v>
+      <c r="A151" s="14" t="s">
+        <v>1252</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>849</v>
+        <v>838</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>850</v>
+        <v>839</v>
       </c>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
       <c r="F151" s="9" t="s">
-        <v>851</v>
+        <v>492</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>852</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>784</v>
+        <v>46</v>
+      </c>
+      <c r="H151" s="9">
+        <v>1850</v>
       </c>
       <c r="I151" s="9" t="s">
-        <v>40</v>
+        <v>738</v>
       </c>
       <c r="J151" s="9" t="s">
-        <v>853</v>
+        <v>1245</v>
       </c>
       <c r="K151" s="9"/>
       <c r="L151" s="10" t="s">
-        <v>854</v>
+        <v>1246</v>
       </c>
       <c r="M151" s="10"/>
       <c r="N151" s="10"/>
       <c r="O151" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P151" s="9">
-        <v>60</v>
-      </c>
-      <c r="Q151" s="9">
-        <v>30</v>
+      <c r="P151" s="9" t="s">
+        <v>1247</v>
+      </c>
+      <c r="Q151" s="9" t="s">
+        <v>1248</v>
       </c>
       <c r="R151" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S151" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="152" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="C152" s="11" t="s">
-        <v>850</v>
-      </c>
-      <c r="D152" s="11"/>
-      <c r="E152" s="11"/>
-      <c r="F152" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="I152" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="14" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="C152" s="9" t="s">
+        <v>839</v>
+      </c>
+      <c r="D152" s="9"/>
+      <c r="E152" s="9"/>
+      <c r="F152" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="G152" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H152" s="9">
+        <v>1863</v>
+      </c>
+      <c r="I152" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="J152" s="2" t="s">
+      <c r="J152" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="K152" s="11"/>
-      <c r="L152" s="4" t="s">
-        <v>857</v>
-      </c>
-      <c r="M152" s="4"/>
-      <c r="N152" s="4"/>
-      <c r="O152" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P152" s="11">
-        <v>63</v>
-      </c>
-      <c r="Q152" s="11">
-        <v>38.5</v>
-      </c>
-      <c r="R152" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S152" s="2">
-        <v>3</v>
+      <c r="K152" s="9"/>
+      <c r="L152" s="10" t="s">
+        <v>1254</v>
+      </c>
+      <c r="M152" s="10"/>
+      <c r="N152" s="10"/>
+      <c r="O152" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P152" s="9">
+        <v>81</v>
+      </c>
+      <c r="Q152" s="9">
+        <v>101</v>
+      </c>
+      <c r="R152" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S152" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="6" t="s">
-        <v>858</v>
+      <c r="A153" s="14" t="s">
+        <v>1255</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>859</v>
+        <v>838</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>860</v>
+        <v>839</v>
       </c>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
       <c r="F153" s="9" t="s">
-        <v>387</v>
+        <v>492</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>861</v>
+        <v>46</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>862</v>
+        <v>1249</v>
       </c>
       <c r="I153" s="9" t="s">
         <v>40</v>
@@ -11795,67 +11825,67 @@
       </c>
       <c r="K153" s="9"/>
       <c r="L153" s="10" t="s">
-        <v>863</v>
+        <v>1250</v>
       </c>
       <c r="M153" s="10"/>
       <c r="N153" s="10"/>
       <c r="O153" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P153" s="9" t="s">
-        <v>864</v>
-      </c>
-      <c r="Q153" s="9" t="s">
-        <v>865</v>
+      <c r="P153" s="9">
+        <v>86</v>
+      </c>
+      <c r="Q153" s="9">
+        <v>111</v>
       </c>
       <c r="R153" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S153" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>866</v>
+        <v>847</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>859</v>
+        <v>848</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>860</v>
+        <v>849</v>
       </c>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
       <c r="F154" s="9" t="s">
-        <v>387</v>
+        <v>850</v>
       </c>
       <c r="G154" s="9" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
       <c r="H154" s="9" t="s">
-        <v>450</v>
+        <v>784</v>
       </c>
       <c r="I154" s="9" t="s">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="J154" s="9" t="s">
-        <v>126</v>
+        <v>852</v>
       </c>
       <c r="K154" s="9"/>
       <c r="L154" s="10" t="s">
-        <v>867</v>
+        <v>853</v>
       </c>
       <c r="M154" s="10"/>
       <c r="N154" s="10"/>
       <c r="O154" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P154" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q154" s="9" t="s">
-        <v>766</v>
+      <c r="P154" s="9">
+        <v>60</v>
+      </c>
+      <c r="Q154" s="9">
+        <v>30</v>
       </c>
       <c r="R154" s="9" t="s">
         <v>31</v>
@@ -11864,75 +11894,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="B155" s="9" t="s">
-        <v>869</v>
-      </c>
-      <c r="C155" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="D155" s="9"/>
-      <c r="E155" s="9"/>
-      <c r="F155" s="9" t="s">
-        <v>604</v>
-      </c>
-      <c r="G155" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>834</v>
-      </c>
-      <c r="I155" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J155" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="K155" s="9"/>
-      <c r="L155" s="10" t="s">
-        <v>871</v>
-      </c>
-      <c r="M155" s="10"/>
-      <c r="N155" s="10"/>
-      <c r="O155" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P155" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q155" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="R155" s="9" t="s">
-        <v>872</v>
-      </c>
-      <c r="S155" s="9">
+    <row r="155" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>849</v>
+      </c>
+      <c r="D155" s="11"/>
+      <c r="E155" s="11"/>
+      <c r="F155" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K155" s="11"/>
+      <c r="L155" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="M155" s="4"/>
+      <c r="N155" s="4"/>
+      <c r="O155" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P155" s="11">
+        <v>63</v>
+      </c>
+      <c r="Q155" s="11">
+        <v>38.5</v>
+      </c>
+      <c r="R155" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S155" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>873</v>
+        <v>857</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>869</v>
+        <v>858</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>870</v>
+        <v>859</v>
       </c>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
       <c r="F156" s="9" t="s">
-        <v>604</v>
+        <v>387</v>
       </c>
       <c r="G156" s="9" t="s">
-        <v>149</v>
+        <v>860</v>
       </c>
       <c r="H156" s="9" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="I156" s="9" t="s">
         <v>40</v>
@@ -11942,7 +11972,7 @@
       </c>
       <c r="K156" s="9"/>
       <c r="L156" s="10" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="M156" s="10"/>
       <c r="N156" s="10"/>
@@ -11950,13 +11980,13 @@
         <v>28</v>
       </c>
       <c r="P156" s="9" t="s">
-        <v>217</v>
+        <v>863</v>
       </c>
       <c r="Q156" s="9" t="s">
-        <v>74</v>
+        <v>864</v>
       </c>
       <c r="R156" s="9" t="s">
-        <v>872</v>
+        <v>31</v>
       </c>
       <c r="S156" s="9">
         <v>3</v>
@@ -11964,34 +11994,34 @@
     </row>
     <row r="157" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>876</v>
+        <v>865</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>877</v>
+        <v>858</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>878</v>
+        <v>859</v>
       </c>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
       <c r="F157" s="9" t="s">
-        <v>879</v>
+        <v>387</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>398</v>
+        <v>860</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>880</v>
+        <v>450</v>
       </c>
       <c r="I157" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="J157" s="9" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="K157" s="9"/>
       <c r="L157" s="10" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="M157" s="10"/>
       <c r="N157" s="10"/>
@@ -11999,13 +12029,13 @@
         <v>28</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>882</v>
+        <v>297</v>
       </c>
       <c r="Q157" s="9" t="s">
-        <v>883</v>
+        <v>766</v>
       </c>
       <c r="R157" s="9" t="s">
-        <v>187</v>
+        <v>31</v>
       </c>
       <c r="S157" s="9">
         <v>3</v>
@@ -12013,34 +12043,34 @@
     </row>
     <row r="158" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>884</v>
+        <v>867</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
       <c r="F158" s="9" t="s">
-        <v>879</v>
+        <v>604</v>
       </c>
       <c r="G158" s="9" t="s">
-        <v>398</v>
+        <v>149</v>
       </c>
       <c r="H158" s="9" t="s">
-        <v>750</v>
+        <v>834</v>
       </c>
       <c r="I158" s="9" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="J158" s="9" t="s">
-        <v>885</v>
+        <v>34</v>
       </c>
       <c r="K158" s="9"/>
       <c r="L158" s="10" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="M158" s="10"/>
       <c r="N158" s="10"/>
@@ -12048,13 +12078,13 @@
         <v>28</v>
       </c>
       <c r="P158" s="9" t="s">
-        <v>671</v>
+        <v>217</v>
       </c>
       <c r="Q158" s="9" t="s">
-        <v>887</v>
+        <v>74</v>
       </c>
       <c r="R158" s="9" t="s">
-        <v>187</v>
+        <v>871</v>
       </c>
       <c r="S158" s="9">
         <v>3</v>
@@ -12062,34 +12092,34 @@
     </row>
     <row r="159" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>889</v>
+        <v>868</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>890</v>
+        <v>869</v>
       </c>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
       <c r="F159" s="9" t="s">
-        <v>851</v>
+        <v>604</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>891</v>
+        <v>149</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>892</v>
+        <v>873</v>
       </c>
       <c r="I159" s="9" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="J159" s="9" t="s">
-        <v>184</v>
+        <v>41</v>
       </c>
       <c r="K159" s="9"/>
       <c r="L159" s="10" t="s">
-        <v>893</v>
+        <v>874</v>
       </c>
       <c r="M159" s="10"/>
       <c r="N159" s="10"/>
@@ -12097,13 +12127,13 @@
         <v>28</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="Q159" s="9" t="s">
-        <v>894</v>
+        <v>74</v>
       </c>
       <c r="R159" s="9" t="s">
-        <v>187</v>
+        <v>871</v>
       </c>
       <c r="S159" s="9">
         <v>3</v>
@@ -12111,34 +12141,34 @@
     </row>
     <row r="160" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>895</v>
+        <v>875</v>
       </c>
       <c r="B160" s="9" t="s">
-        <v>889</v>
+        <v>876</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>890</v>
+        <v>877</v>
       </c>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
       <c r="F160" s="9" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="G160" s="9" t="s">
-        <v>891</v>
+        <v>398</v>
       </c>
       <c r="H160" s="9" t="s">
-        <v>605</v>
+        <v>879</v>
       </c>
       <c r="I160" s="9" t="s">
         <v>102</v>
       </c>
       <c r="J160" s="9" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="K160" s="9"/>
       <c r="L160" s="10" t="s">
-        <v>896</v>
+        <v>880</v>
       </c>
       <c r="M160" s="10"/>
       <c r="N160" s="10"/>
@@ -12146,10 +12176,10 @@
         <v>28</v>
       </c>
       <c r="P160" s="9" t="s">
-        <v>897</v>
+        <v>881</v>
       </c>
       <c r="Q160" s="9" t="s">
-        <v>898</v>
+        <v>882</v>
       </c>
       <c r="R160" s="9" t="s">
         <v>187</v>
@@ -12160,34 +12190,34 @@
     </row>
     <row r="161" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>899</v>
+        <v>883</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>900</v>
+        <v>876</v>
       </c>
       <c r="C161" s="9" t="s">
-        <v>901</v>
+        <v>877</v>
       </c>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
       <c r="F161" s="9" t="s">
-        <v>902</v>
+        <v>878</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>903</v>
+        <v>398</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>904</v>
+        <v>750</v>
       </c>
       <c r="I161" s="9" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="J161" s="9" t="s">
-        <v>34</v>
+        <v>884</v>
       </c>
       <c r="K161" s="9"/>
       <c r="L161" s="10" t="s">
-        <v>905</v>
+        <v>885</v>
       </c>
       <c r="M161" s="10"/>
       <c r="N161" s="10"/>
@@ -12195,13 +12225,13 @@
         <v>28</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>906</v>
+        <v>671</v>
       </c>
       <c r="Q161" s="9" t="s">
-        <v>907</v>
+        <v>886</v>
       </c>
       <c r="R161" s="9" t="s">
-        <v>516</v>
+        <v>187</v>
       </c>
       <c r="S161" s="9">
         <v>3</v>
@@ -12209,24 +12239,24 @@
     </row>
     <row r="162" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>908</v>
+        <v>887</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>900</v>
+        <v>888</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>901</v>
+        <v>889</v>
       </c>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
       <c r="F162" s="9" t="s">
-        <v>902</v>
+        <v>850</v>
       </c>
       <c r="G162" s="9" t="s">
-        <v>903</v>
+        <v>890</v>
       </c>
       <c r="H162" s="9" t="s">
-        <v>856</v>
+        <v>891</v>
       </c>
       <c r="I162" s="9" t="s">
         <v>102</v>
@@ -12236,7 +12266,7 @@
       </c>
       <c r="K162" s="9"/>
       <c r="L162" s="10" t="s">
-        <v>909</v>
+        <v>892</v>
       </c>
       <c r="M162" s="10"/>
       <c r="N162" s="10"/>
@@ -12244,13 +12274,13 @@
         <v>28</v>
       </c>
       <c r="P162" s="9" t="s">
-        <v>645</v>
+        <v>192</v>
       </c>
       <c r="Q162" s="9" t="s">
-        <v>910</v>
+        <v>893</v>
       </c>
       <c r="R162" s="9" t="s">
-        <v>516</v>
+        <v>187</v>
       </c>
       <c r="S162" s="9">
         <v>3</v>
@@ -12258,24 +12288,24 @@
     </row>
     <row r="163" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>911</v>
+        <v>894</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>912</v>
+        <v>888</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>913</v>
+        <v>889</v>
       </c>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
       <c r="F163" s="9" t="s">
-        <v>443</v>
+        <v>850</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>197</v>
+        <v>890</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>377</v>
+        <v>605</v>
       </c>
       <c r="I163" s="9" t="s">
         <v>102</v>
@@ -12285,7 +12315,7 @@
       </c>
       <c r="K163" s="9"/>
       <c r="L163" s="10" t="s">
-        <v>914</v>
+        <v>895</v>
       </c>
       <c r="M163" s="10"/>
       <c r="N163" s="10"/>
@@ -12293,10 +12323,10 @@
         <v>28</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>915</v>
+        <v>896</v>
       </c>
       <c r="Q163" s="9" t="s">
-        <v>222</v>
+        <v>897</v>
       </c>
       <c r="R163" s="9" t="s">
         <v>187</v>
@@ -12307,34 +12337,34 @@
     </row>
     <row r="164" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>916</v>
+        <v>898</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
       <c r="D164" s="9"/>
       <c r="E164" s="9"/>
       <c r="F164" s="9" t="s">
-        <v>443</v>
+        <v>901</v>
       </c>
       <c r="G164" s="9" t="s">
-        <v>197</v>
+        <v>902</v>
       </c>
       <c r="H164" s="9" t="s">
-        <v>72</v>
+        <v>903</v>
       </c>
       <c r="I164" s="9" t="s">
-        <v>917</v>
+        <v>33</v>
       </c>
       <c r="J164" s="9" t="s">
-        <v>918</v>
+        <v>34</v>
       </c>
       <c r="K164" s="9"/>
       <c r="L164" s="10" t="s">
-        <v>919</v>
+        <v>904</v>
       </c>
       <c r="M164" s="10"/>
       <c r="N164" s="10"/>
@@ -12342,13 +12372,13 @@
         <v>28</v>
       </c>
       <c r="P164" s="9" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="Q164" s="9" t="s">
-        <v>921</v>
+        <v>906</v>
       </c>
       <c r="R164" s="9" t="s">
-        <v>187</v>
+        <v>516</v>
       </c>
       <c r="S164" s="9">
         <v>3</v>
@@ -12356,34 +12386,34 @@
     </row>
     <row r="165" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>923</v>
+        <v>899</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>924</v>
+        <v>900</v>
       </c>
       <c r="D165" s="9"/>
       <c r="E165" s="9"/>
       <c r="F165" s="9" t="s">
-        <v>700</v>
+        <v>901</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>139</v>
+        <v>902</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I165" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J165" s="2" t="s">
-        <v>1237</v>
+        <v>855</v>
+      </c>
+      <c r="I165" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="J165" s="9" t="s">
+        <v>184</v>
       </c>
       <c r="K165" s="9"/>
       <c r="L165" s="10" t="s">
-        <v>925</v>
+        <v>908</v>
       </c>
       <c r="M165" s="10"/>
       <c r="N165" s="10"/>
@@ -12391,10 +12421,10 @@
         <v>28</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>926</v>
+        <v>645</v>
       </c>
       <c r="Q165" s="9" t="s">
-        <v>927</v>
+        <v>909</v>
       </c>
       <c r="R165" s="9" t="s">
         <v>516</v>
@@ -12405,34 +12435,34 @@
     </row>
     <row r="166" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="B166" s="9" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="D166" s="9"/>
       <c r="E166" s="9"/>
       <c r="F166" s="9" t="s">
-        <v>700</v>
+        <v>443</v>
       </c>
       <c r="G166" s="9" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="H166" s="9" t="s">
-        <v>177</v>
+        <v>377</v>
       </c>
       <c r="I166" s="9" t="s">
-        <v>790</v>
+        <v>102</v>
       </c>
       <c r="J166" s="9" t="s">
-        <v>791</v>
+        <v>184</v>
       </c>
       <c r="K166" s="9"/>
       <c r="L166" s="10" t="s">
-        <v>929</v>
+        <v>913</v>
       </c>
       <c r="M166" s="10"/>
       <c r="N166" s="10"/>
@@ -12440,13 +12470,13 @@
         <v>28</v>
       </c>
       <c r="P166" s="9" t="s">
-        <v>930</v>
+        <v>914</v>
       </c>
       <c r="Q166" s="9" t="s">
-        <v>931</v>
+        <v>222</v>
       </c>
       <c r="R166" s="9" t="s">
-        <v>516</v>
+        <v>187</v>
       </c>
       <c r="S166" s="9">
         <v>3</v>
@@ -12454,34 +12484,34 @@
     </row>
     <row r="167" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
-        <v>932</v>
+        <v>915</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>933</v>
+        <v>911</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>934</v>
+        <v>912</v>
       </c>
       <c r="D167" s="9"/>
       <c r="E167" s="9"/>
       <c r="F167" s="9" t="s">
-        <v>526</v>
+        <v>443</v>
       </c>
       <c r="G167" s="9" t="s">
-        <v>935</v>
+        <v>197</v>
       </c>
       <c r="H167" s="9" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="I167" s="9" t="s">
-        <v>40</v>
+        <v>916</v>
       </c>
       <c r="J167" s="9" t="s">
-        <v>41</v>
+        <v>917</v>
       </c>
       <c r="K167" s="9"/>
       <c r="L167" s="10" t="s">
-        <v>936</v>
+        <v>918</v>
       </c>
       <c r="M167" s="10"/>
       <c r="N167" s="10"/>
@@ -12489,13 +12519,13 @@
         <v>28</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>937</v>
+        <v>919</v>
       </c>
       <c r="Q167" s="9" t="s">
-        <v>938</v>
+        <v>920</v>
       </c>
       <c r="R167" s="9" t="s">
-        <v>31</v>
+        <v>187</v>
       </c>
       <c r="S167" s="9">
         <v>3</v>
@@ -12503,34 +12533,34 @@
     </row>
     <row r="168" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
-        <v>939</v>
+        <v>921</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>934</v>
+        <v>923</v>
       </c>
       <c r="D168" s="9"/>
       <c r="E168" s="9"/>
       <c r="F168" s="9" t="s">
-        <v>526</v>
+        <v>700</v>
       </c>
       <c r="G168" s="9" t="s">
-        <v>935</v>
+        <v>139</v>
       </c>
       <c r="H168" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I168" s="9" t="s">
-        <v>940</v>
-      </c>
-      <c r="J168" s="9" t="s">
-        <v>941</v>
+        <v>62</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J168" s="2" t="s">
+        <v>1236</v>
       </c>
       <c r="K168" s="9"/>
       <c r="L168" s="10" t="s">
-        <v>942</v>
+        <v>924</v>
       </c>
       <c r="M168" s="10"/>
       <c r="N168" s="10"/>
@@ -12538,13 +12568,13 @@
         <v>28</v>
       </c>
       <c r="P168" s="9" t="s">
-        <v>943</v>
+        <v>925</v>
       </c>
       <c r="Q168" s="9" t="s">
-        <v>864</v>
+        <v>926</v>
       </c>
       <c r="R168" s="9" t="s">
-        <v>31</v>
+        <v>516</v>
       </c>
       <c r="S168" s="9">
         <v>3</v>
@@ -12552,50 +12582,48 @@
     </row>
     <row r="169" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
-        <v>944</v>
+        <v>927</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>945</v>
+        <v>922</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>946</v>
+        <v>923</v>
       </c>
       <c r="D169" s="9"/>
       <c r="E169" s="9"/>
       <c r="F169" s="9" t="s">
-        <v>902</v>
+        <v>700</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>947</v>
+        <v>139</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="I169" s="9" t="s">
-        <v>141</v>
+        <v>790</v>
       </c>
       <c r="J169" s="9" t="s">
-        <v>948</v>
+        <v>791</v>
       </c>
       <c r="K169" s="9"/>
       <c r="L169" s="10" t="s">
-        <v>949</v>
+        <v>928</v>
       </c>
       <c r="M169" s="10"/>
-      <c r="N169" s="10" t="s">
-        <v>950</v>
-      </c>
+      <c r="N169" s="10"/>
       <c r="O169" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>951</v>
+        <v>929</v>
       </c>
       <c r="Q169" s="9" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="R169" s="9" t="s">
-        <v>709</v>
+        <v>516</v>
       </c>
       <c r="S169" s="9">
         <v>3</v>
@@ -12603,50 +12631,48 @@
     </row>
     <row r="170" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
-        <v>953</v>
+        <v>931</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>946</v>
+        <v>933</v>
       </c>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
       <c r="F170" s="9" t="s">
-        <v>902</v>
+        <v>526</v>
       </c>
       <c r="G170" s="9" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
       <c r="H170" s="9" t="s">
-        <v>891</v>
+        <v>62</v>
       </c>
       <c r="I170" s="9" t="s">
-        <v>703</v>
+        <v>40</v>
       </c>
       <c r="J170" s="9" t="s">
-        <v>954</v>
+        <v>41</v>
       </c>
       <c r="K170" s="9"/>
       <c r="L170" s="10" t="s">
-        <v>955</v>
+        <v>935</v>
       </c>
       <c r="M170" s="10"/>
-      <c r="N170" s="10" t="s">
-        <v>956</v>
-      </c>
+      <c r="N170" s="10"/>
       <c r="O170" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P170" s="9" t="s">
-        <v>957</v>
+        <v>936</v>
       </c>
       <c r="Q170" s="9" t="s">
-        <v>958</v>
+        <v>937</v>
       </c>
       <c r="R170" s="9" t="s">
-        <v>709</v>
+        <v>31</v>
       </c>
       <c r="S170" s="9">
         <v>3</v>
@@ -12654,45 +12680,45 @@
     </row>
     <row r="171" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
-        <v>959</v>
+        <v>938</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>960</v>
+        <v>932</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>961</v>
+        <v>933</v>
       </c>
       <c r="D171" s="9"/>
       <c r="E171" s="9"/>
       <c r="F171" s="9" t="s">
-        <v>123</v>
+        <v>526</v>
       </c>
       <c r="G171" s="9" t="s">
-        <v>962</v>
+        <v>934</v>
       </c>
       <c r="H171" s="9" t="s">
         <v>39</v>
       </c>
       <c r="I171" s="9" t="s">
-        <v>40</v>
+        <v>939</v>
       </c>
       <c r="J171" s="9" t="s">
-        <v>41</v>
+        <v>940</v>
       </c>
       <c r="K171" s="9"/>
       <c r="L171" s="10" t="s">
-        <v>963</v>
+        <v>941</v>
       </c>
       <c r="M171" s="10"/>
       <c r="N171" s="10"/>
       <c r="O171" s="9" t="s">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>964</v>
+        <v>942</v>
       </c>
       <c r="Q171" s="9" t="s">
-        <v>965</v>
+        <v>863</v>
       </c>
       <c r="R171" s="9" t="s">
         <v>31</v>
@@ -12703,48 +12729,50 @@
     </row>
     <row r="172" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
-        <v>966</v>
+        <v>943</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>960</v>
+        <v>944</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>961</v>
+        <v>945</v>
       </c>
       <c r="D172" s="9"/>
       <c r="E172" s="9"/>
       <c r="F172" s="9" t="s">
-        <v>123</v>
+        <v>901</v>
       </c>
       <c r="G172" s="9" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="H172" s="9" t="s">
-        <v>967</v>
+        <v>39</v>
       </c>
       <c r="I172" s="9" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="J172" s="9" t="s">
-        <v>41</v>
+        <v>947</v>
       </c>
       <c r="K172" s="9"/>
       <c r="L172" s="10" t="s">
-        <v>968</v>
+        <v>948</v>
       </c>
       <c r="M172" s="10"/>
-      <c r="N172" s="10"/>
+      <c r="N172" s="10" t="s">
+        <v>949</v>
+      </c>
       <c r="O172" s="9" t="s">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="P172" s="9" t="s">
-        <v>969</v>
+        <v>950</v>
       </c>
       <c r="Q172" s="9" t="s">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="R172" s="9" t="s">
-        <v>31</v>
+        <v>709</v>
       </c>
       <c r="S172" s="9">
         <v>3</v>
@@ -12752,48 +12780,50 @@
     </row>
     <row r="173" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
-        <v>971</v>
+        <v>952</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>972</v>
+        <v>944</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>973</v>
+        <v>945</v>
       </c>
       <c r="D173" s="9"/>
       <c r="E173" s="9"/>
       <c r="F173" s="9" t="s">
-        <v>22</v>
+        <v>901</v>
       </c>
       <c r="G173" s="9" t="s">
-        <v>974</v>
+        <v>946</v>
       </c>
       <c r="H173" s="9" t="s">
-        <v>83</v>
+        <v>890</v>
       </c>
       <c r="I173" s="9" t="s">
-        <v>33</v>
+        <v>703</v>
       </c>
       <c r="J173" s="9" t="s">
-        <v>34</v>
+        <v>953</v>
       </c>
       <c r="K173" s="9"/>
       <c r="L173" s="10" t="s">
-        <v>975</v>
+        <v>954</v>
       </c>
       <c r="M173" s="10"/>
-      <c r="N173" s="10"/>
+      <c r="N173" s="10" t="s">
+        <v>955</v>
+      </c>
       <c r="O173" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>36</v>
+        <v>956</v>
       </c>
       <c r="Q173" s="9" t="s">
-        <v>616</v>
+        <v>957</v>
       </c>
       <c r="R173" s="9" t="s">
-        <v>31</v>
+        <v>709</v>
       </c>
       <c r="S173" s="9">
         <v>3</v>
@@ -12801,45 +12831,45 @@
     </row>
     <row r="174" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
-        <v>976</v>
+        <v>958</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>972</v>
+        <v>959</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>973</v>
+        <v>960</v>
       </c>
       <c r="D174" s="9"/>
       <c r="E174" s="9"/>
       <c r="F174" s="9" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="G174" s="9" t="s">
-        <v>974</v>
+        <v>961</v>
       </c>
       <c r="H174" s="9" t="s">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="I174" s="9" t="s">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c r="J174" s="9" t="s">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="K174" s="9"/>
       <c r="L174" s="10" t="s">
-        <v>977</v>
+        <v>962</v>
       </c>
       <c r="M174" s="10"/>
       <c r="N174" s="10"/>
       <c r="O174" s="9" t="s">
-        <v>28</v>
+        <v>336</v>
       </c>
       <c r="P174" s="9" t="s">
-        <v>351</v>
+        <v>963</v>
       </c>
       <c r="Q174" s="9" t="s">
-        <v>978</v>
+        <v>964</v>
       </c>
       <c r="R174" s="9" t="s">
         <v>31</v>
@@ -12850,24 +12880,24 @@
     </row>
     <row r="175" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
-        <v>979</v>
+        <v>965</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>972</v>
+        <v>959</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>973</v>
+        <v>960</v>
       </c>
       <c r="D175" s="9"/>
       <c r="E175" s="9"/>
       <c r="F175" s="9" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="G175" s="9" t="s">
-        <v>974</v>
+        <v>961</v>
       </c>
       <c r="H175" s="9" t="s">
-        <v>980</v>
+        <v>966</v>
       </c>
       <c r="I175" s="9" t="s">
         <v>40</v>
@@ -12877,35 +12907,35 @@
       </c>
       <c r="K175" s="9"/>
       <c r="L175" s="10" t="s">
-        <v>981</v>
+        <v>967</v>
       </c>
       <c r="M175" s="10"/>
       <c r="N175" s="10"/>
       <c r="O175" s="9" t="s">
-        <v>28</v>
+        <v>336</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>982</v>
+        <v>968</v>
       </c>
       <c r="Q175" s="9" t="s">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="R175" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S175" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>984</v>
+        <v>970</v>
       </c>
       <c r="B176" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="C176" s="9" t="s">
         <v>972</v>
-      </c>
-      <c r="C176" s="9" t="s">
-        <v>973</v>
       </c>
       <c r="D176" s="9"/>
       <c r="E176" s="9"/>
@@ -12913,20 +12943,20 @@
         <v>22</v>
       </c>
       <c r="G176" s="9" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H176" s="9" t="s">
-        <v>985</v>
+        <v>83</v>
       </c>
       <c r="I176" s="9" t="s">
-        <v>790</v>
+        <v>33</v>
       </c>
       <c r="J176" s="9" t="s">
-        <v>791</v>
+        <v>34</v>
       </c>
       <c r="K176" s="9"/>
       <c r="L176" s="10" t="s">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="M176" s="10"/>
       <c r="N176" s="10"/>
@@ -12934,10 +12964,10 @@
         <v>28</v>
       </c>
       <c r="P176" s="9" t="s">
-        <v>987</v>
+        <v>36</v>
       </c>
       <c r="Q176" s="9" t="s">
-        <v>988</v>
+        <v>616</v>
       </c>
       <c r="R176" s="9" t="s">
         <v>31</v>
@@ -12948,13 +12978,13 @@
     </row>
     <row r="177" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
-        <v>989</v>
+        <v>975</v>
       </c>
       <c r="B177" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="C177" s="9" t="s">
         <v>972</v>
-      </c>
-      <c r="C177" s="9" t="s">
-        <v>973</v>
       </c>
       <c r="D177" s="9"/>
       <c r="E177" s="9"/>
@@ -12962,20 +12992,20 @@
         <v>22</v>
       </c>
       <c r="G177" s="9" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H177" s="9" t="s">
-        <v>990</v>
+        <v>149</v>
       </c>
       <c r="I177" s="9" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="J177" s="9" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="K177" s="9"/>
       <c r="L177" s="10" t="s">
-        <v>991</v>
+        <v>976</v>
       </c>
       <c r="M177" s="10"/>
       <c r="N177" s="10"/>
@@ -12983,10 +13013,10 @@
         <v>28</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>992</v>
+        <v>351</v>
       </c>
       <c r="Q177" s="9" t="s">
-        <v>209</v>
+        <v>977</v>
       </c>
       <c r="R177" s="9" t="s">
         <v>31</v>
@@ -12995,165 +13025,171 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
-        <v>993</v>
-      </c>
-      <c r="B178" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="B178" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="C178" s="9" t="s">
         <v>972</v>
       </c>
-      <c r="C178" s="2" t="s">
-        <v>973</v>
-      </c>
+      <c r="D178" s="9"/>
+      <c r="E178" s="9"/>
       <c r="F178" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G178" s="9" t="s">
-        <v>974</v>
-      </c>
-      <c r="H178" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="I178" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="H178" s="9" t="s">
+        <v>979</v>
+      </c>
+      <c r="I178" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="J178" s="2" t="s">
+      <c r="J178" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="K178" s="2"/>
-      <c r="L178" s="4" t="s">
-        <v>994</v>
-      </c>
-      <c r="N178" s="2"/>
-      <c r="O178" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P178" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q178" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="R178" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S178" s="2">
+      <c r="K178" s="9"/>
+      <c r="L178" s="10" t="s">
+        <v>980</v>
+      </c>
+      <c r="M178" s="10"/>
+      <c r="N178" s="10"/>
+      <c r="O178" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P178" s="9" t="s">
+        <v>981</v>
+      </c>
+      <c r="Q178" s="9" t="s">
+        <v>982</v>
+      </c>
+      <c r="R178" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S178" s="9">
         <v>1</v>
       </c>
-      <c r="T178" s="7"/>
-    </row>
-    <row r="179" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
-        <v>995</v>
-      </c>
-      <c r="B179" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="C179" s="9" t="s">
         <v>972</v>
       </c>
-      <c r="C179" s="2" t="s">
-        <v>973</v>
-      </c>
+      <c r="D179" s="9"/>
+      <c r="E179" s="9"/>
       <c r="F179" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G179" s="9" t="s">
-        <v>974</v>
-      </c>
-      <c r="H179" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I179" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J179" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K179" s="2"/>
-      <c r="L179" s="4" t="s">
-        <v>996</v>
-      </c>
-      <c r="N179" s="2"/>
-      <c r="O179" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P179" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q179" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="R179" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S179" s="2">
+        <v>973</v>
+      </c>
+      <c r="H179" s="9" t="s">
+        <v>984</v>
+      </c>
+      <c r="I179" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="J179" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="K179" s="9"/>
+      <c r="L179" s="10" t="s">
+        <v>985</v>
+      </c>
+      <c r="M179" s="10"/>
+      <c r="N179" s="10"/>
+      <c r="O179" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P179" s="9" t="s">
+        <v>986</v>
+      </c>
+      <c r="Q179" s="9" t="s">
+        <v>987</v>
+      </c>
+      <c r="R179" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S179" s="9">
         <v>1</v>
       </c>
-      <c r="T179" s="7"/>
-    </row>
-    <row r="180" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
-        <v>997</v>
-      </c>
-      <c r="B180" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="C180" s="9" t="s">
         <v>972</v>
       </c>
-      <c r="C180" s="2" t="s">
-        <v>973</v>
-      </c>
+      <c r="D180" s="9"/>
+      <c r="E180" s="9"/>
       <c r="F180" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G180" s="9" t="s">
-        <v>974</v>
-      </c>
-      <c r="H180" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I180" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J180" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K180" s="2"/>
-      <c r="L180" s="4" t="s">
-        <v>998</v>
-      </c>
-      <c r="N180" s="2"/>
-      <c r="O180" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P180" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="Q180" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="R180" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S180" s="2">
+        <v>973</v>
+      </c>
+      <c r="H180" s="9" t="s">
+        <v>989</v>
+      </c>
+      <c r="I180" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="J180" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="K180" s="9"/>
+      <c r="L180" s="10" t="s">
+        <v>990</v>
+      </c>
+      <c r="M180" s="10"/>
+      <c r="N180" s="10"/>
+      <c r="O180" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P180" s="9" t="s">
+        <v>991</v>
+      </c>
+      <c r="Q180" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="R180" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S180" s="9">
         <v>1</v>
       </c>
-      <c r="T180" s="7"/>
     </row>
     <row r="181" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B181" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G181" s="9" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>1000</v>
+        <v>526</v>
       </c>
       <c r="I181" s="2" t="s">
         <v>40</v>
@@ -13163,17 +13199,17 @@
       </c>
       <c r="K181" s="2"/>
       <c r="L181" s="4" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2" t="s">
         <v>28</v>
       </c>
       <c r="P181" s="2" t="s">
-        <v>1002</v>
+        <v>105</v>
       </c>
       <c r="Q181" s="2" t="s">
-        <v>1003</v>
+        <v>30</v>
       </c>
       <c r="R181" s="2" t="s">
         <v>31</v>
@@ -13185,42 +13221,42 @@
     </row>
     <row r="182" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
-        <v>1004</v>
+        <v>994</v>
       </c>
       <c r="B182" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G182" s="9" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>856</v>
+        <v>101</v>
       </c>
       <c r="I182" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K182" s="2"/>
       <c r="L182" s="4" t="s">
-        <v>1005</v>
+        <v>995</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2" t="s">
         <v>28</v>
       </c>
       <c r="P182" s="2" t="s">
-        <v>236</v>
+        <v>616</v>
       </c>
       <c r="Q182" s="2" t="s">
-        <v>926</v>
+        <v>846</v>
       </c>
       <c r="R182" s="2" t="s">
         <v>31</v>
@@ -13232,22 +13268,22 @@
     </row>
     <row r="183" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
-        <v>1006</v>
+        <v>996</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G183" s="9" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>1007</v>
+        <v>111</v>
       </c>
       <c r="I183" s="2" t="s">
         <v>40</v>
@@ -13257,17 +13293,17 @@
       </c>
       <c r="K183" s="2"/>
       <c r="L183" s="4" t="s">
-        <v>1008</v>
+        <v>997</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2" t="s">
         <v>28</v>
       </c>
       <c r="P183" s="2" t="s">
-        <v>151</v>
+        <v>395</v>
       </c>
       <c r="Q183" s="2" t="s">
-        <v>106</v>
+        <v>631</v>
       </c>
       <c r="R183" s="2" t="s">
         <v>31</v>
@@ -13279,42 +13315,42 @@
     </row>
     <row r="184" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>1009</v>
+        <v>998</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G184" s="9" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>1010</v>
+        <v>999</v>
       </c>
       <c r="I184" s="2" t="s">
-        <v>1011</v>
+        <v>40</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>1012</v>
+        <v>41</v>
       </c>
       <c r="K184" s="2"/>
       <c r="L184" s="4" t="s">
-        <v>1013</v>
+        <v>1000</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2" t="s">
         <v>28</v>
       </c>
       <c r="P184" s="2" t="s">
-        <v>297</v>
+        <v>1001</v>
       </c>
       <c r="Q184" s="2" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="R184" s="2" t="s">
         <v>31</v>
@@ -13324,162 +13360,156 @@
       </c>
       <c r="T184" s="7"/>
     </row>
-    <row r="185" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B185" s="9" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>972</v>
       </c>
-      <c r="C185" s="9" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D185" s="9"/>
-      <c r="E185" s="9"/>
       <c r="F185" s="9" t="s">
-        <v>577</v>
+        <v>22</v>
       </c>
       <c r="G185" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="H185" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="I185" s="9" t="s">
+        <v>973</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="I185" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J185" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K185" s="2"/>
+      <c r="L185" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="N185" s="2"/>
+      <c r="O185" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P185" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q185" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="R185" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S185" s="2">
+        <v>1</v>
+      </c>
+      <c r="T185" s="7"/>
+    </row>
+    <row r="186" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="F186" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G186" s="9" t="s">
+        <v>973</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I186" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J185" s="9" t="s">
+      <c r="J186" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K185" s="9"/>
-      <c r="L185" s="10" t="s">
-        <v>1017</v>
-      </c>
-      <c r="M185" s="10"/>
-      <c r="N185" s="10"/>
-      <c r="O185" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P185" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q185" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="R185" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S185" s="9">
+      <c r="K186" s="2"/>
+      <c r="L186" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="N186" s="2"/>
+      <c r="O186" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P186" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q186" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="R186" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S186" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="186" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="6" t="s">
-        <v>1018</v>
-      </c>
-      <c r="B186" s="9" t="s">
+      <c r="T186" s="7"/>
+    </row>
+    <row r="187" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="6" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>972</v>
       </c>
-      <c r="C186" s="9" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D186" s="9"/>
-      <c r="E186" s="9"/>
-      <c r="F186" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="G186" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="H186" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I186" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="J186" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="K186" s="9"/>
-      <c r="L186" s="10" t="s">
-        <v>1019</v>
-      </c>
-      <c r="M186" s="10"/>
-      <c r="N186" s="10"/>
-      <c r="O186" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P186" s="9" t="s">
-        <v>1020</v>
-      </c>
-      <c r="Q186" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="R186" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S186" s="9">
+      <c r="F187" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G187" s="9" t="s">
+        <v>973</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I187" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J187" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K187" s="2"/>
+      <c r="L187" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="N187" s="2"/>
+      <c r="O187" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P187" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q187" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="R187" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S187" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="6" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B187" s="9" t="s">
-        <v>972</v>
-      </c>
-      <c r="C187" s="9" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D187" s="9"/>
-      <c r="E187" s="9"/>
-      <c r="F187" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="G187" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="H187" s="9" t="s">
-        <v>1022</v>
-      </c>
-      <c r="I187" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="J187" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K187" s="9"/>
-      <c r="L187" s="10" t="s">
-        <v>1023</v>
-      </c>
-      <c r="M187" s="10"/>
-      <c r="N187" s="10"/>
-      <c r="O187" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="P187" s="9" t="s">
-        <v>1024</v>
-      </c>
-      <c r="Q187" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="R187" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S187" s="9">
-        <v>1</v>
-      </c>
+      <c r="T187" s="7"/>
     </row>
     <row r="188" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D188" s="9"/>
       <c r="E188" s="9"/>
@@ -13490,7 +13520,7 @@
         <v>100</v>
       </c>
       <c r="H188" s="9" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I188" s="9" t="s">
         <v>40</v>
@@ -13500,7 +13530,7 @@
       </c>
       <c r="K188" s="9"/>
       <c r="L188" s="10" t="s">
-        <v>1027</v>
+        <v>1016</v>
       </c>
       <c r="M188" s="10"/>
       <c r="N188" s="10"/>
@@ -13508,10 +13538,10 @@
         <v>28</v>
       </c>
       <c r="P188" s="9" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="Q188" s="9" t="s">
-        <v>1028</v>
+        <v>351</v>
       </c>
       <c r="R188" s="9" t="s">
         <v>31</v>
@@ -13522,13 +13552,13 @@
     </row>
     <row r="189" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
-        <v>1029</v>
+        <v>1017</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -13539,17 +13569,17 @@
         <v>100</v>
       </c>
       <c r="H189" s="9" t="s">
-        <v>1022</v>
+        <v>62</v>
       </c>
       <c r="I189" s="9" t="s">
-        <v>33</v>
+        <v>163</v>
       </c>
       <c r="J189" s="9" t="s">
-        <v>1030</v>
+        <v>164</v>
       </c>
       <c r="K189" s="9"/>
       <c r="L189" s="10" t="s">
-        <v>1031</v>
+        <v>1018</v>
       </c>
       <c r="M189" s="10"/>
       <c r="N189" s="10"/>
@@ -13557,10 +13587,10 @@
         <v>28</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>1032</v>
+        <v>1019</v>
       </c>
       <c r="Q189" s="9" t="s">
-        <v>1033</v>
+        <v>352</v>
       </c>
       <c r="R189" s="9" t="s">
         <v>31</v>
@@ -13571,13 +13601,13 @@
     </row>
     <row r="190" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
-        <v>1034</v>
+        <v>1020</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D190" s="9"/>
       <c r="E190" s="9"/>
@@ -13588,28 +13618,28 @@
         <v>100</v>
       </c>
       <c r="H190" s="9" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="I190" s="9" t="s">
-        <v>738</v>
+        <v>102</v>
       </c>
       <c r="J190" s="9" t="s">
-        <v>739</v>
+        <v>103</v>
       </c>
       <c r="K190" s="9"/>
       <c r="L190" s="10" t="s">
-        <v>1036</v>
+        <v>1022</v>
       </c>
       <c r="M190" s="10"/>
       <c r="N190" s="10"/>
       <c r="O190" s="9" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="P190" s="9" t="s">
-        <v>1037</v>
+        <v>1023</v>
       </c>
       <c r="Q190" s="9" t="s">
-        <v>1038</v>
+        <v>1024</v>
       </c>
       <c r="R190" s="9" t="s">
         <v>31</v>
@@ -13620,24 +13650,24 @@
     </row>
     <row r="191" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6" t="s">
-        <v>1039</v>
+        <v>1025</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>1040</v>
+        <v>1015</v>
       </c>
       <c r="D191" s="9"/>
       <c r="E191" s="9"/>
       <c r="F191" s="9" t="s">
-        <v>667</v>
+        <v>577</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>1041</v>
+        <v>100</v>
       </c>
       <c r="H191" s="9" t="s">
-        <v>377</v>
+        <v>140</v>
       </c>
       <c r="I191" s="9" t="s">
         <v>40</v>
@@ -13647,56 +13677,56 @@
       </c>
       <c r="K191" s="9"/>
       <c r="L191" s="10" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="M191" s="10"/>
       <c r="N191" s="10"/>
       <c r="O191" s="9" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>236</v>
+        <v>59</v>
       </c>
       <c r="Q191" s="9" t="s">
-        <v>696</v>
+        <v>1027</v>
       </c>
       <c r="R191" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S191" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
-        <v>1043</v>
+        <v>1028</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>1040</v>
+        <v>1015</v>
       </c>
       <c r="D192" s="9"/>
       <c r="E192" s="9"/>
       <c r="F192" s="9" t="s">
-        <v>667</v>
+        <v>577</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>1041</v>
+        <v>100</v>
       </c>
       <c r="H192" s="9" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="I192" s="9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J192" s="9" t="s">
-        <v>41</v>
+        <v>1029</v>
       </c>
       <c r="K192" s="9"/>
       <c r="L192" s="10" t="s">
-        <v>1044</v>
+        <v>1030</v>
       </c>
       <c r="M192" s="10"/>
       <c r="N192" s="10"/>
@@ -13704,48 +13734,48 @@
         <v>28</v>
       </c>
       <c r="P192" s="9" t="s">
-        <v>236</v>
+        <v>1031</v>
       </c>
       <c r="Q192" s="9" t="s">
-        <v>696</v>
+        <v>1032</v>
       </c>
       <c r="R192" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S192" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>1046</v>
+        <v>1015</v>
       </c>
       <c r="D193" s="9"/>
       <c r="E193" s="9"/>
       <c r="F193" s="9" t="s">
-        <v>264</v>
+        <v>577</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>1047</v>
+        <v>100</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>39</v>
+        <v>1034</v>
       </c>
       <c r="I193" s="9" t="s">
-        <v>33</v>
+        <v>738</v>
       </c>
       <c r="J193" s="9" t="s">
-        <v>334</v>
+        <v>739</v>
       </c>
       <c r="K193" s="9"/>
       <c r="L193" s="10" t="s">
-        <v>1048</v>
+        <v>1035</v>
       </c>
       <c r="M193" s="10"/>
       <c r="N193" s="10"/>
@@ -13753,87 +13783,87 @@
         <v>28</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>352</v>
+        <v>1036</v>
       </c>
       <c r="Q193" s="9" t="s">
-        <v>1020</v>
+        <v>1037</v>
       </c>
       <c r="R193" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S193" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="194" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="1" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>972</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D194" s="11"/>
-      <c r="E194" s="11"/>
-      <c r="F194" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G194" s="2" t="s">
-        <v>1047</v>
-      </c>
-      <c r="H194" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I194" s="2" t="s">
-        <v>1050</v>
-      </c>
-      <c r="J194" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="K194" s="11"/>
-      <c r="L194" s="4" t="s">
-        <v>1052</v>
-      </c>
-      <c r="M194" s="4"/>
-      <c r="N194" s="4"/>
-      <c r="O194" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P194" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q194" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="R194" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S194" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="C194" s="9" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D194" s="9"/>
+      <c r="E194" s="9"/>
+      <c r="F194" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="G194" s="9" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H194" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="I194" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J194" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K194" s="9"/>
+      <c r="L194" s="10" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M194" s="10"/>
+      <c r="N194" s="10"/>
+      <c r="O194" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="P194" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q194" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="R194" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S194" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="195" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
-        <v>1053</v>
+        <v>1042</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>1054</v>
+        <v>971</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>1055</v>
+        <v>1039</v>
       </c>
       <c r="D195" s="9"/>
       <c r="E195" s="9"/>
       <c r="F195" s="9" t="s">
-        <v>159</v>
+        <v>667</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="H195" s="9" t="s">
-        <v>323</v>
+        <v>1021</v>
       </c>
       <c r="I195" s="9" t="s">
         <v>40</v>
@@ -13843,18 +13873,18 @@
       </c>
       <c r="K195" s="9"/>
       <c r="L195" s="10" t="s">
-        <v>1057</v>
+        <v>1043</v>
       </c>
       <c r="M195" s="10"/>
       <c r="N195" s="10"/>
       <c r="O195" s="9" t="s">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>1058</v>
+        <v>236</v>
       </c>
       <c r="Q195" s="9" t="s">
-        <v>1059</v>
+        <v>696</v>
       </c>
       <c r="R195" s="9" t="s">
         <v>31</v>
@@ -13863,124 +13893,124 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="1" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D196" s="11"/>
-      <c r="E196" s="11"/>
-      <c r="F196" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G196" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="H196" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="I196" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J196" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="K196" s="11"/>
-      <c r="L196" s="4" t="s">
-        <v>1062</v>
-      </c>
-      <c r="M196" s="4"/>
-      <c r="N196" s="4"/>
-      <c r="O196" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="P196" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q196" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R196" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S196" s="2">
+    <row r="196" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="C196" s="9" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D196" s="9"/>
+      <c r="E196" s="9"/>
+      <c r="F196" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G196" s="9" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H196" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I196" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J196" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="K196" s="9"/>
+      <c r="L196" s="10" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M196" s="10"/>
+      <c r="N196" s="10"/>
+      <c r="O196" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P196" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q196" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="R196" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S196" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="6" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C197" s="9" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D197" s="9"/>
-      <c r="E197" s="9"/>
-      <c r="F197" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G197" s="9" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H197" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I197" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J197" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K197" s="9"/>
-      <c r="L197" s="10" t="s">
-        <v>1068</v>
-      </c>
-      <c r="M197" s="10"/>
-      <c r="N197" s="10"/>
-      <c r="O197" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P197" s="9" t="s">
-        <v>836</v>
-      </c>
-      <c r="Q197" s="9" t="s">
-        <v>1069</v>
-      </c>
-      <c r="R197" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S197" s="9">
-        <v>1</v>
+    <row r="197" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D197" s="11"/>
+      <c r="E197" s="11"/>
+      <c r="F197" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I197" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J197" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K197" s="11"/>
+      <c r="L197" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="M197" s="4"/>
+      <c r="N197" s="4"/>
+      <c r="O197" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P197" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q197" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R197" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S197" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
-        <v>1070</v>
+        <v>1052</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="C198" s="9" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="D198" s="9"/>
       <c r="E198" s="9"/>
       <c r="F198" s="9" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="G198" s="9" t="s">
-        <v>1067</v>
+        <v>1055</v>
       </c>
       <c r="H198" s="9" t="s">
-        <v>24</v>
+        <v>323</v>
       </c>
       <c r="I198" s="9" t="s">
         <v>40</v>
@@ -13990,84 +14020,84 @@
       </c>
       <c r="K198" s="9"/>
       <c r="L198" s="10" t="s">
-        <v>1071</v>
+        <v>1056</v>
       </c>
       <c r="M198" s="10"/>
       <c r="N198" s="10"/>
       <c r="O198" s="9" t="s">
-        <v>28</v>
+        <v>336</v>
       </c>
       <c r="P198" s="9" t="s">
-        <v>209</v>
+        <v>1057</v>
       </c>
       <c r="Q198" s="9" t="s">
-        <v>236</v>
+        <v>1058</v>
       </c>
       <c r="R198" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S198" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="6" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B199" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C199" s="9" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D199" s="9"/>
-      <c r="E199" s="9"/>
-      <c r="F199" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G199" s="9" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H199" s="9" t="s">
-        <v>1073</v>
-      </c>
-      <c r="I199" s="9" t="s">
-        <v>790</v>
-      </c>
-      <c r="J199" s="9" t="s">
-        <v>1074</v>
-      </c>
-      <c r="K199" s="9"/>
-      <c r="L199" s="10" t="s">
-        <v>1075</v>
-      </c>
-      <c r="M199" s="10"/>
-      <c r="N199" s="10"/>
-      <c r="O199" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P199" s="9" t="s">
-        <v>1076</v>
-      </c>
-      <c r="Q199" s="9" t="s">
-        <v>1077</v>
-      </c>
-      <c r="R199" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S199" s="9">
-        <v>1</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D199" s="11"/>
+      <c r="E199" s="11"/>
+      <c r="F199" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I199" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J199" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="K199" s="11"/>
+      <c r="L199" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="M199" s="4"/>
+      <c r="N199" s="4"/>
+      <c r="O199" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="P199" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q199" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R199" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S199" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
-        <v>1078</v>
+        <v>1063</v>
       </c>
       <c r="B200" s="9" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C200" s="9" t="s">
         <v>1065</v>
-      </c>
-      <c r="C200" s="9" t="s">
-        <v>1066</v>
       </c>
       <c r="D200" s="9"/>
       <c r="E200" s="9"/>
@@ -14075,10 +14105,10 @@
         <v>71</v>
       </c>
       <c r="G200" s="9" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H200" s="9" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="I200" s="9" t="s">
         <v>40</v>
@@ -14088,7 +14118,7 @@
       </c>
       <c r="K200" s="9"/>
       <c r="L200" s="10" t="s">
-        <v>1079</v>
+        <v>1067</v>
       </c>
       <c r="M200" s="10"/>
       <c r="N200" s="10"/>
@@ -14096,10 +14126,10 @@
         <v>28</v>
       </c>
       <c r="P200" s="9" t="s">
-        <v>800</v>
+        <v>836</v>
       </c>
       <c r="Q200" s="9" t="s">
-        <v>780</v>
+        <v>1068</v>
       </c>
       <c r="R200" s="9" t="s">
         <v>31</v>
@@ -14110,13 +14140,13 @@
     </row>
     <row r="201" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
-        <v>1080</v>
+        <v>1069</v>
       </c>
       <c r="B201" s="9" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C201" s="9" t="s">
         <v>1065</v>
-      </c>
-      <c r="C201" s="9" t="s">
-        <v>1066</v>
       </c>
       <c r="D201" s="9"/>
       <c r="E201" s="9"/>
@@ -14124,7 +14154,7 @@
         <v>71</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H201" s="9" t="s">
         <v>24</v>
@@ -14137,7 +14167,7 @@
       </c>
       <c r="K201" s="9"/>
       <c r="L201" s="10" t="s">
-        <v>1081</v>
+        <v>1070</v>
       </c>
       <c r="M201" s="10"/>
       <c r="N201" s="10"/>
@@ -14145,10 +14175,10 @@
         <v>28</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>30</v>
+        <v>209</v>
       </c>
       <c r="Q201" s="9" t="s">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="R201" s="9" t="s">
         <v>31</v>
@@ -14159,13 +14189,13 @@
     </row>
     <row r="202" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
-        <v>1082</v>
+        <v>1071</v>
       </c>
       <c r="B202" s="9" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C202" s="9" t="s">
         <v>1065</v>
-      </c>
-      <c r="C202" s="9" t="s">
-        <v>1066</v>
       </c>
       <c r="D202" s="9"/>
       <c r="E202" s="9"/>
@@ -14173,20 +14203,20 @@
         <v>71</v>
       </c>
       <c r="G202" s="9" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H202" s="9" t="s">
-        <v>1083</v>
+        <v>1072</v>
       </c>
       <c r="I202" s="9" t="s">
-        <v>1084</v>
+        <v>790</v>
       </c>
       <c r="J202" s="9" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="K202" s="9"/>
       <c r="L202" s="10" t="s">
-        <v>986</v>
+        <v>1074</v>
       </c>
       <c r="M202" s="10"/>
       <c r="N202" s="10"/>
@@ -14194,10 +14224,10 @@
         <v>28</v>
       </c>
       <c r="P202" s="9" t="s">
-        <v>1086</v>
+        <v>1075</v>
       </c>
       <c r="Q202" s="9" t="s">
-        <v>1087</v>
+        <v>1076</v>
       </c>
       <c r="R202" s="9" t="s">
         <v>31</v>
@@ -14206,162 +14236,162 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B203" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C203" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="C203" s="2" t="s">
+      <c r="D203" s="9"/>
+      <c r="E203" s="9"/>
+      <c r="F203" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G203" s="9" t="s">
         <v>1066</v>
       </c>
-      <c r="D203" s="3"/>
-      <c r="E203" s="3"/>
-      <c r="F203" s="11" t="s">
+      <c r="H203" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I203" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J203" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K203" s="9"/>
+      <c r="L203" s="10" t="s">
+        <v>1078</v>
+      </c>
+      <c r="M203" s="10"/>
+      <c r="N203" s="10"/>
+      <c r="O203" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P203" s="9" t="s">
+        <v>800</v>
+      </c>
+      <c r="Q203" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="R203" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S203" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="6" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C204" s="9" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D204" s="9"/>
+      <c r="E204" s="9"/>
+      <c r="F204" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="G203" s="11" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H203" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I203" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J203" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="K203" s="2"/>
-      <c r="L203" s="4" t="s">
-        <v>1089</v>
-      </c>
-      <c r="M203" s="3"/>
-      <c r="N203" s="2"/>
-      <c r="O203" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P203" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q203" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="R203" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S203" s="2">
+      <c r="G204" s="9" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H204" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I204" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J204" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K204" s="9"/>
+      <c r="L204" s="10" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M204" s="10"/>
+      <c r="N204" s="10"/>
+      <c r="O204" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P204" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q204" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="R204" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S204" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="6" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B204" s="2" t="s">
+    <row r="205" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C205" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="C204" s="2" t="s">
+      <c r="D205" s="9"/>
+      <c r="E205" s="9"/>
+      <c r="F205" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G205" s="9" t="s">
         <v>1066</v>
       </c>
-      <c r="D204" s="3"/>
-      <c r="E204" s="3"/>
-      <c r="F204" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G204" s="11" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H204" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I204" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J204" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K204" s="2"/>
-      <c r="L204" s="4" t="s">
-        <v>1092</v>
-      </c>
-      <c r="M204" s="3"/>
-      <c r="N204" s="2"/>
-      <c r="O204" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P204" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="Q204" s="2" t="s">
-        <v>1093</v>
-      </c>
-      <c r="R204" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S204" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="6" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D205" s="3"/>
-      <c r="E205" s="3"/>
-      <c r="F205" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G205" s="11" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H205" s="2" t="s">
-        <v>967</v>
-      </c>
-      <c r="I205" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J205" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K205" s="2"/>
-      <c r="L205" s="4" t="s">
-        <v>1095</v>
-      </c>
-      <c r="M205" s="3"/>
-      <c r="N205" s="2"/>
-      <c r="O205" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P205" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="Q205" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="R205" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S205" s="2">
+      <c r="H205" s="9" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I205" s="9" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J205" s="9" t="s">
+        <v>1084</v>
+      </c>
+      <c r="K205" s="9"/>
+      <c r="L205" s="10" t="s">
+        <v>985</v>
+      </c>
+      <c r="M205" s="10"/>
+      <c r="N205" s="10"/>
+      <c r="O205" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P205" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="Q205" s="9" t="s">
+        <v>1086</v>
+      </c>
+      <c r="R205" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S205" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>1097</v>
+        <v>1087</v>
       </c>
       <c r="B206" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>1065</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>1066</v>
       </c>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -14369,33 +14399,31 @@
         <v>71</v>
       </c>
       <c r="G206" s="11" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>263</v>
+        <v>76</v>
       </c>
       <c r="I206" s="2" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="J206" s="2" t="s">
-        <v>41</v>
+        <v>271</v>
       </c>
       <c r="K206" s="2"/>
       <c r="L206" s="4" t="s">
-        <v>1098</v>
-      </c>
-      <c r="M206" s="4" t="s">
-        <v>1099</v>
-      </c>
+        <v>1088</v>
+      </c>
+      <c r="M206" s="3"/>
       <c r="N206" s="2"/>
       <c r="O206" s="2" t="s">
         <v>28</v>
       </c>
       <c r="P206" s="2" t="s">
-        <v>409</v>
+        <v>297</v>
       </c>
       <c r="Q206" s="2" t="s">
-        <v>780</v>
+        <v>1089</v>
       </c>
       <c r="R206" s="2" t="s">
         <v>31</v>
@@ -14406,13 +14434,13 @@
     </row>
     <row r="207" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6" t="s">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>1065</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>1066</v>
       </c>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -14420,33 +14448,31 @@
         <v>71</v>
       </c>
       <c r="G207" s="11" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>263</v>
+        <v>177</v>
       </c>
       <c r="I207" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J207" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K207" s="2"/>
       <c r="L207" s="4" t="s">
-        <v>1101</v>
-      </c>
-      <c r="M207" s="4" t="s">
-        <v>1102</v>
-      </c>
+        <v>1091</v>
+      </c>
+      <c r="M207" s="3"/>
       <c r="N207" s="2"/>
       <c r="O207" s="2" t="s">
         <v>28</v>
       </c>
       <c r="P207" s="2" t="s">
-        <v>409</v>
+        <v>909</v>
       </c>
       <c r="Q207" s="2" t="s">
-        <v>780</v>
+        <v>1092</v>
       </c>
       <c r="R207" s="2" t="s">
         <v>31</v>
@@ -14455,183 +14481,187 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B208" s="9" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C208" s="9" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D208" s="9"/>
-      <c r="E208" s="9"/>
-      <c r="F208" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="G208" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="H208" s="9" t="s">
-        <v>967</v>
-      </c>
-      <c r="I208" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+      <c r="F208" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G208" s="11" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="I208" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J208" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K208" s="2"/>
+      <c r="L208" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="M208" s="3"/>
+      <c r="N208" s="2"/>
+      <c r="O208" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P208" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Q208" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R208" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S208" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="6" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D209" s="3"/>
+      <c r="E209" s="3"/>
+      <c r="F209" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G209" s="11" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I209" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J208" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="K208" s="9"/>
-      <c r="L208" s="10" t="s">
-        <v>1105</v>
-      </c>
-      <c r="M208" s="10"/>
-      <c r="N208" s="10"/>
-      <c r="O208" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P208" s="9" t="s">
-        <v>1106</v>
-      </c>
-      <c r="Q208" s="9" t="s">
-        <v>1107</v>
-      </c>
-      <c r="R208" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S208" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="209" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="6" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B209" s="9" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C209" s="9" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D209" s="9"/>
-      <c r="E209" s="9"/>
-      <c r="F209" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="G209" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="H209" s="9" t="s">
+      <c r="J209" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K209" s="2"/>
+      <c r="L209" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M209" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="N209" s="2"/>
+      <c r="O209" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P209" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q209" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="R209" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S209" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D210" s="3"/>
+      <c r="E210" s="3"/>
+      <c r="F210" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G210" s="11" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H210" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="I209" s="9" t="s">
+      <c r="I210" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J209" s="9" t="s">
+      <c r="J210" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K209" s="9"/>
-      <c r="L209" s="10" t="s">
-        <v>1109</v>
-      </c>
-      <c r="M209" s="10"/>
-      <c r="N209" s="10"/>
-      <c r="O209" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P209" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q209" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="R209" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S209" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="210" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="6" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B210" s="9" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C210" s="9" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D210" s="9"/>
-      <c r="E210" s="9"/>
-      <c r="F210" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="G210" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H210" s="9" t="s">
-        <v>1022</v>
-      </c>
-      <c r="I210" s="9" t="s">
-        <v>1241</v>
-      </c>
-      <c r="J210" s="9" t="s">
-        <v>1113</v>
-      </c>
-      <c r="K210" s="9"/>
-      <c r="L210" s="10" t="s">
-        <v>1114</v>
-      </c>
-      <c r="M210" s="10"/>
-      <c r="N210" s="10"/>
-      <c r="O210" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P210" s="9" t="s">
-        <v>1115</v>
-      </c>
-      <c r="Q210" s="9" t="s">
-        <v>1116</v>
-      </c>
-      <c r="R210" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S210" s="9">
-        <v>3</v>
+      <c r="K210" s="2"/>
+      <c r="L210" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="M210" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="N210" s="2"/>
+      <c r="O210" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P210" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q210" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="R210" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S210" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6" t="s">
-        <v>1117</v>
+        <v>1102</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>1111</v>
+        <v>1053</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>1112</v>
+        <v>1103</v>
       </c>
       <c r="D211" s="9"/>
       <c r="E211" s="9"/>
       <c r="F211" s="9" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>23</v>
+        <v>363</v>
       </c>
       <c r="H211" s="9" t="s">
-        <v>1118</v>
+        <v>966</v>
       </c>
       <c r="I211" s="9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J211" s="9" t="s">
-        <v>34</v>
+        <v>388</v>
       </c>
       <c r="K211" s="9"/>
       <c r="L211" s="10" t="s">
-        <v>1119</v>
+        <v>1104</v>
       </c>
       <c r="M211" s="10"/>
       <c r="N211" s="10"/>
@@ -14639,10 +14669,10 @@
         <v>28</v>
       </c>
       <c r="P211" s="9" t="s">
-        <v>1120</v>
+        <v>1105</v>
       </c>
       <c r="Q211" s="9" t="s">
-        <v>1121</v>
+        <v>1106</v>
       </c>
       <c r="R211" s="9" t="s">
         <v>31</v>
@@ -14653,24 +14683,24 @@
     </row>
     <row r="212" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6" t="s">
-        <v>1122</v>
+        <v>1107</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>1123</v>
+        <v>1053</v>
       </c>
       <c r="C212" s="9" t="s">
-        <v>1124</v>
+        <v>1103</v>
       </c>
       <c r="D212" s="9"/>
       <c r="E212" s="9"/>
       <c r="F212" s="9" t="s">
-        <v>299</v>
+        <v>387</v>
       </c>
       <c r="G212" s="9" t="s">
-        <v>139</v>
+        <v>363</v>
       </c>
       <c r="H212" s="9" t="s">
-        <v>323</v>
+        <v>263</v>
       </c>
       <c r="I212" s="9" t="s">
         <v>40</v>
@@ -14680,21 +14710,21 @@
       </c>
       <c r="K212" s="9"/>
       <c r="L212" s="10" t="s">
-        <v>1125</v>
+        <v>1108</v>
       </c>
       <c r="M212" s="10"/>
       <c r="N212" s="10"/>
       <c r="O212" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P212" s="9">
-        <v>197</v>
-      </c>
-      <c r="Q212" s="9">
-        <v>114.5</v>
+      <c r="P212" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q212" s="9" t="s">
+        <v>588</v>
       </c>
       <c r="R212" s="9" t="s">
-        <v>776</v>
+        <v>31</v>
       </c>
       <c r="S212" s="9">
         <v>3</v>
@@ -14702,48 +14732,48 @@
     </row>
     <row r="213" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6" t="s">
-        <v>1126</v>
+        <v>1109</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>1123</v>
+        <v>1110</v>
       </c>
       <c r="C213" s="9" t="s">
-        <v>1124</v>
+        <v>1111</v>
       </c>
       <c r="D213" s="9"/>
       <c r="E213" s="9"/>
       <c r="F213" s="9" t="s">
-        <v>299</v>
+        <v>401</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="H213" s="9" t="s">
-        <v>23</v>
+        <v>1021</v>
       </c>
       <c r="I213" s="9" t="s">
-        <v>40</v>
+        <v>1240</v>
       </c>
       <c r="J213" s="9" t="s">
-        <v>41</v>
+        <v>1112</v>
       </c>
       <c r="K213" s="9"/>
       <c r="L213" s="10" t="s">
-        <v>1127</v>
+        <v>1113</v>
       </c>
       <c r="M213" s="10"/>
       <c r="N213" s="10"/>
       <c r="O213" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P213" s="9">
-        <v>96</v>
-      </c>
-      <c r="Q213" s="9">
-        <v>129</v>
+      <c r="P213" s="9" t="s">
+        <v>1114</v>
+      </c>
+      <c r="Q213" s="9" t="s">
+        <v>1115</v>
       </c>
       <c r="R213" s="9" t="s">
-        <v>776</v>
+        <v>31</v>
       </c>
       <c r="S213" s="9">
         <v>3</v>
@@ -14751,34 +14781,34 @@
     </row>
     <row r="214" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>1129</v>
+        <v>1110</v>
       </c>
       <c r="C214" s="9" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="D214" s="9"/>
       <c r="E214" s="9"/>
       <c r="F214" s="9" t="s">
-        <v>462</v>
+        <v>401</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>387</v>
+        <v>23</v>
       </c>
       <c r="H214" s="9" t="s">
-        <v>604</v>
+        <v>1117</v>
       </c>
       <c r="I214" s="9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J214" s="9" t="s">
-        <v>388</v>
+        <v>34</v>
       </c>
       <c r="K214" s="9"/>
       <c r="L214" s="10" t="s">
-        <v>1131</v>
+        <v>1118</v>
       </c>
       <c r="M214" s="10"/>
       <c r="N214" s="10"/>
@@ -14786,234 +14816,234 @@
         <v>28</v>
       </c>
       <c r="P214" s="9" t="s">
-        <v>1132</v>
+        <v>1119</v>
       </c>
       <c r="Q214" s="9" t="s">
-        <v>1133</v>
+        <v>1120</v>
       </c>
       <c r="R214" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S214" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6" t="s">
-        <v>1134</v>
+        <v>1121</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="C215" s="9" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
       <c r="D215" s="9"/>
       <c r="E215" s="9"/>
       <c r="F215" s="9" t="s">
-        <v>462</v>
+        <v>299</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>387</v>
+        <v>139</v>
       </c>
       <c r="H215" s="9" t="s">
-        <v>1135</v>
+        <v>323</v>
       </c>
       <c r="I215" s="9" t="s">
         <v>40</v>
       </c>
       <c r="J215" s="9" t="s">
-        <v>388</v>
+        <v>41</v>
       </c>
       <c r="K215" s="9"/>
       <c r="L215" s="10" t="s">
-        <v>1136</v>
+        <v>1124</v>
       </c>
       <c r="M215" s="10"/>
       <c r="N215" s="10"/>
       <c r="O215" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P215" s="9" t="s">
-        <v>1137</v>
-      </c>
-      <c r="Q215" s="9" t="s">
-        <v>1138</v>
+      <c r="P215" s="9">
+        <v>197</v>
+      </c>
+      <c r="Q215" s="9">
+        <v>114.5</v>
       </c>
       <c r="R215" s="9" t="s">
-        <v>31</v>
+        <v>776</v>
       </c>
       <c r="S215" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
-        <v>1139</v>
+        <v>1125</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="C216" s="9" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
       <c r="D216" s="9"/>
       <c r="E216" s="9"/>
       <c r="F216" s="9" t="s">
-        <v>462</v>
+        <v>299</v>
       </c>
       <c r="G216" s="9" t="s">
-        <v>387</v>
+        <v>139</v>
       </c>
       <c r="H216" s="9" t="s">
-        <v>880</v>
+        <v>23</v>
       </c>
       <c r="I216" s="9" t="s">
         <v>40</v>
       </c>
       <c r="J216" s="9" t="s">
-        <v>388</v>
+        <v>41</v>
       </c>
       <c r="K216" s="9"/>
       <c r="L216" s="10" t="s">
-        <v>1140</v>
+        <v>1126</v>
       </c>
       <c r="M216" s="10"/>
       <c r="N216" s="10"/>
       <c r="O216" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P216" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q216" s="9" t="s">
-        <v>1141</v>
+      <c r="P216" s="9">
+        <v>96</v>
+      </c>
+      <c r="Q216" s="9">
+        <v>129</v>
       </c>
       <c r="R216" s="9" t="s">
-        <v>31</v>
+        <v>776</v>
       </c>
       <c r="S216" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="217" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B217" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C217" s="9" t="s">
         <v>1129</v>
       </c>
-      <c r="C217" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D217" s="3"/>
-      <c r="E217" s="3"/>
+      <c r="D217" s="9"/>
+      <c r="E217" s="9"/>
       <c r="F217" s="9" t="s">
         <v>462</v>
       </c>
       <c r="G217" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="H217" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="I217" s="2" t="s">
-        <v>1144</v>
-      </c>
-      <c r="J217" s="2" t="s">
-        <v>1145</v>
-      </c>
-      <c r="K217" s="2"/>
-      <c r="L217" s="4" t="s">
-        <v>1146</v>
-      </c>
-      <c r="M217" s="3"/>
-      <c r="N217" s="3"/>
-      <c r="O217" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P217" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="Q217" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="R217" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S217" s="2">
+      <c r="H217" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="I217" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J217" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="K217" s="9"/>
+      <c r="L217" s="10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="M217" s="10"/>
+      <c r="N217" s="10"/>
+      <c r="O217" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P217" s="9" t="s">
+        <v>1131</v>
+      </c>
+      <c r="Q217" s="9" t="s">
+        <v>1132</v>
+      </c>
+      <c r="R217" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S217" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B218" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B218" s="9" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C218" s="9" t="s">
         <v>1129</v>
       </c>
-      <c r="C218" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D218" s="3"/>
-      <c r="E218" s="3"/>
+      <c r="D218" s="9"/>
+      <c r="E218" s="9"/>
       <c r="F218" s="9" t="s">
         <v>462</v>
       </c>
       <c r="G218" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="H218" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="I218" s="2" t="s">
-        <v>1149</v>
-      </c>
-      <c r="J218" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="K218" s="2"/>
-      <c r="L218" s="4" t="s">
-        <v>1151</v>
-      </c>
-      <c r="M218" s="3"/>
-      <c r="N218" s="3"/>
-      <c r="O218" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P218" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q218" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R218" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S218" s="2">
+      <c r="H218" s="9" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I218" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J218" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="K218" s="9"/>
+      <c r="L218" s="10" t="s">
+        <v>1135</v>
+      </c>
+      <c r="M218" s="10"/>
+      <c r="N218" s="10"/>
+      <c r="O218" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P218" s="9" t="s">
+        <v>1136</v>
+      </c>
+      <c r="Q218" s="9" t="s">
+        <v>1137</v>
+      </c>
+      <c r="R218" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S218" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="219" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
-        <v>1152</v>
+        <v>1138</v>
       </c>
       <c r="B219" s="9" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C219" s="9" t="s">
         <v>1129</v>
-      </c>
-      <c r="C219" s="9" t="s">
-        <v>1153</v>
       </c>
       <c r="D219" s="9"/>
       <c r="E219" s="9"/>
       <c r="F219" s="9" t="s">
-        <v>1135</v>
+        <v>462</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>159</v>
+        <v>387</v>
       </c>
       <c r="H219" s="9" t="s">
-        <v>640</v>
+        <v>879</v>
       </c>
       <c r="I219" s="9" t="s">
         <v>40</v>
@@ -15023,7 +15053,7 @@
       </c>
       <c r="K219" s="9"/>
       <c r="L219" s="10" t="s">
-        <v>1154</v>
+        <v>1139</v>
       </c>
       <c r="M219" s="10"/>
       <c r="N219" s="10"/>
@@ -15031,162 +15061,160 @@
         <v>28</v>
       </c>
       <c r="P219" s="9" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="Q219" s="9" t="s">
-        <v>943</v>
+        <v>1140</v>
       </c>
       <c r="R219" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S219" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="220" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
-        <v>1155</v>
-      </c>
-      <c r="B220" s="9" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C220" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="C220" s="9" t="s">
-        <v>1153</v>
-      </c>
-      <c r="D220" s="9"/>
-      <c r="E220" s="9"/>
+      <c r="D220" s="3"/>
+      <c r="E220" s="3"/>
       <c r="F220" s="9" t="s">
-        <v>1135</v>
+        <v>462</v>
       </c>
       <c r="G220" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="H220" s="9" t="s">
-        <v>1156</v>
-      </c>
-      <c r="I220" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J220" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="K220" s="9"/>
-      <c r="L220" s="10" t="s">
-        <v>1157</v>
-      </c>
-      <c r="M220" s="10"/>
-      <c r="N220" s="10"/>
-      <c r="O220" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P220" s="9" t="s">
-        <v>1090</v>
-      </c>
-      <c r="Q220" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="R220" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S220" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="221" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I220" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="J220" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="K220" s="2"/>
+      <c r="L220" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="M220" s="3"/>
+      <c r="N220" s="3"/>
+      <c r="O220" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P220" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="Q220" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="R220" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S220" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B221" s="9" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C221" s="9" t="s">
-        <v>1160</v>
-      </c>
-      <c r="D221" s="9"/>
-      <c r="E221" s="9"/>
+        <v>1146</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D221" s="3"/>
+      <c r="E221" s="3"/>
       <c r="F221" s="9" t="s">
-        <v>1161</v>
+        <v>462</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="H221" s="9" t="s">
-        <v>728</v>
-      </c>
-      <c r="I221" s="9" t="s">
-        <v>790</v>
-      </c>
-      <c r="J221" s="9" t="s">
-        <v>791</v>
-      </c>
-      <c r="K221" s="9"/>
-      <c r="L221" s="10" t="s">
-        <v>1162</v>
-      </c>
-      <c r="M221" s="10"/>
-      <c r="N221" s="10"/>
-      <c r="O221" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P221" s="9" t="s">
-        <v>1163</v>
-      </c>
-      <c r="Q221" s="9" t="s">
-        <v>1164</v>
-      </c>
-      <c r="R221" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="S221" s="9">
-        <v>3</v>
+        <v>387</v>
+      </c>
+      <c r="H221" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I221" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="J221" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K221" s="2"/>
+      <c r="L221" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="M221" s="3"/>
+      <c r="N221" s="3"/>
+      <c r="O221" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P221" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q221" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R221" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S221" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
-        <v>1165</v>
+        <v>1151</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>1159</v>
+        <v>1128</v>
       </c>
       <c r="C222" s="9" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
       <c r="D222" s="9"/>
       <c r="E222" s="9"/>
       <c r="F222" s="9" t="s">
-        <v>1161</v>
+        <v>1134</v>
       </c>
       <c r="G222" s="9" t="s">
-        <v>577</v>
+        <v>159</v>
       </c>
       <c r="H222" s="9" t="s">
-        <v>262</v>
+        <v>640</v>
       </c>
       <c r="I222" s="9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J222" s="9" t="s">
-        <v>34</v>
+        <v>388</v>
       </c>
       <c r="K222" s="9"/>
       <c r="L222" s="10" t="s">
-        <v>1166</v>
+        <v>1153</v>
       </c>
       <c r="M222" s="10"/>
-      <c r="N222" s="10" t="s">
-        <v>1167</v>
-      </c>
+      <c r="N222" s="10"/>
       <c r="O222" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P222" s="9" t="s">
-        <v>1168</v>
+        <v>175</v>
       </c>
       <c r="Q222" s="9" t="s">
-        <v>1169</v>
+        <v>942</v>
       </c>
       <c r="R222" s="9" t="s">
-        <v>516</v>
+        <v>31</v>
       </c>
       <c r="S222" s="9">
         <v>3</v>
@@ -15194,34 +15222,34 @@
     </row>
     <row r="223" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>1170</v>
+        <v>1154</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>1159</v>
+        <v>1128</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>1171</v>
+        <v>1152</v>
       </c>
       <c r="D223" s="9"/>
       <c r="E223" s="9"/>
       <c r="F223" s="9" t="s">
-        <v>700</v>
+        <v>1134</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>962</v>
+        <v>159</v>
       </c>
       <c r="H223" s="9" t="s">
-        <v>46</v>
+        <v>1155</v>
       </c>
       <c r="I223" s="9" t="s">
-        <v>1084</v>
+        <v>40</v>
       </c>
       <c r="J223" s="9" t="s">
-        <v>1085</v>
+        <v>388</v>
       </c>
       <c r="K223" s="9"/>
       <c r="L223" s="10" t="s">
-        <v>1172</v>
+        <v>1156</v>
       </c>
       <c r="M223" s="10"/>
       <c r="N223" s="10"/>
@@ -15229,13 +15257,13 @@
         <v>28</v>
       </c>
       <c r="P223" s="9" t="s">
-        <v>748</v>
+        <v>1089</v>
       </c>
       <c r="Q223" s="9" t="s">
-        <v>1173</v>
+        <v>663</v>
       </c>
       <c r="R223" s="9" t="s">
-        <v>516</v>
+        <v>31</v>
       </c>
       <c r="S223" s="9">
         <v>3</v>
@@ -15243,34 +15271,34 @@
     </row>
     <row r="224" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
-        <v>1174</v>
+        <v>1157</v>
       </c>
       <c r="B224" s="9" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C224" s="9" t="s">
         <v>1159</v>
-      </c>
-      <c r="C224" s="9" t="s">
-        <v>1171</v>
       </c>
       <c r="D224" s="9"/>
       <c r="E224" s="9"/>
       <c r="F224" s="9" t="s">
-        <v>700</v>
+        <v>1160</v>
       </c>
       <c r="G224" s="9" t="s">
-        <v>962</v>
+        <v>577</v>
       </c>
       <c r="H224" s="9" t="s">
-        <v>55</v>
+        <v>728</v>
       </c>
       <c r="I224" s="9" t="s">
-        <v>1084</v>
+        <v>790</v>
       </c>
       <c r="J224" s="9" t="s">
-        <v>1085</v>
+        <v>791</v>
       </c>
       <c r="K224" s="9"/>
       <c r="L224" s="10" t="s">
-        <v>1175</v>
+        <v>1161</v>
       </c>
       <c r="M224" s="10"/>
       <c r="N224" s="10"/>
@@ -15278,10 +15306,10 @@
         <v>28</v>
       </c>
       <c r="P224" s="9" t="s">
-        <v>1176</v>
+        <v>1162</v>
       </c>
       <c r="Q224" s="9" t="s">
-        <v>1177</v>
+        <v>1163</v>
       </c>
       <c r="R224" s="9" t="s">
         <v>516</v>
@@ -15292,83 +15320,85 @@
     </row>
     <row r="225" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>1178</v>
+        <v>1164</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>1179</v>
+        <v>1158</v>
       </c>
       <c r="C225" s="9" t="s">
-        <v>1180</v>
+        <v>1159</v>
       </c>
       <c r="D225" s="9"/>
       <c r="E225" s="9"/>
       <c r="F225" s="9" t="s">
-        <v>1181</v>
+        <v>1160</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>39</v>
+        <v>577</v>
       </c>
       <c r="H225" s="9" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="I225" s="9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J225" s="9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K225" s="9"/>
       <c r="L225" s="10" t="s">
-        <v>1182</v>
+        <v>1165</v>
       </c>
       <c r="M225" s="10"/>
-      <c r="N225" s="10"/>
+      <c r="N225" s="10" t="s">
+        <v>1166</v>
+      </c>
       <c r="O225" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P225" s="9" t="s">
-        <v>826</v>
+        <v>1167</v>
       </c>
       <c r="Q225" s="9" t="s">
-        <v>983</v>
+        <v>1168</v>
       </c>
       <c r="R225" s="9" t="s">
-        <v>872</v>
+        <v>516</v>
       </c>
       <c r="S225" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
-        <v>1183</v>
+        <v>1169</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>1179</v>
+        <v>1158</v>
       </c>
       <c r="C226" s="9" t="s">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="D226" s="9"/>
       <c r="E226" s="9"/>
       <c r="F226" s="9" t="s">
-        <v>1181</v>
+        <v>700</v>
       </c>
       <c r="G226" s="9" t="s">
-        <v>39</v>
+        <v>961</v>
       </c>
       <c r="H226" s="9" t="s">
-        <v>1022</v>
+        <v>46</v>
       </c>
       <c r="I226" s="9" t="s">
-        <v>33</v>
+        <v>1083</v>
       </c>
       <c r="J226" s="9" t="s">
-        <v>334</v>
+        <v>1084</v>
       </c>
       <c r="K226" s="9"/>
       <c r="L226" s="10" t="s">
-        <v>1184</v>
+        <v>1171</v>
       </c>
       <c r="M226" s="10"/>
       <c r="N226" s="10"/>
@@ -15376,48 +15406,48 @@
         <v>28</v>
       </c>
       <c r="P226" s="9" t="s">
-        <v>1185</v>
+        <v>748</v>
       </c>
       <c r="Q226" s="9" t="s">
-        <v>1032</v>
+        <v>1172</v>
       </c>
       <c r="R226" s="9" t="s">
-        <v>872</v>
+        <v>516</v>
       </c>
       <c r="S226" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
-        <v>1186</v>
+        <v>1173</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>1179</v>
+        <v>1158</v>
       </c>
       <c r="C227" s="9" t="s">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="D227" s="9"/>
       <c r="E227" s="9"/>
       <c r="F227" s="9" t="s">
-        <v>1181</v>
+        <v>700</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>39</v>
+        <v>961</v>
       </c>
       <c r="H227" s="9" t="s">
-        <v>1022</v>
+        <v>55</v>
       </c>
       <c r="I227" s="9" t="s">
-        <v>102</v>
+        <v>1083</v>
       </c>
       <c r="J227" s="9" t="s">
-        <v>271</v>
+        <v>1084</v>
       </c>
       <c r="K227" s="9"/>
       <c r="L227" s="10" t="s">
-        <v>1187</v>
+        <v>1174</v>
       </c>
       <c r="M227" s="10"/>
       <c r="N227" s="10"/>
@@ -15425,48 +15455,48 @@
         <v>28</v>
       </c>
       <c r="P227" s="9" t="s">
-        <v>29</v>
+        <v>1175</v>
       </c>
       <c r="Q227" s="9" t="s">
-        <v>231</v>
+        <v>1176</v>
       </c>
       <c r="R227" s="9" t="s">
-        <v>872</v>
+        <v>516</v>
       </c>
       <c r="S227" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
-        <v>1188</v>
+        <v>1177</v>
       </c>
       <c r="B228" s="9" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C228" s="9" t="s">
         <v>1179</v>
-      </c>
-      <c r="C228" s="9" t="s">
-        <v>1180</v>
       </c>
       <c r="D228" s="9"/>
       <c r="E228" s="9"/>
       <c r="F228" s="9" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G228" s="9" t="s">
         <v>39</v>
       </c>
       <c r="H228" s="9" t="s">
-        <v>377</v>
+        <v>149</v>
       </c>
       <c r="I228" s="9" t="s">
-        <v>1189</v>
+        <v>40</v>
       </c>
       <c r="J228" s="9" t="s">
-        <v>1190</v>
+        <v>41</v>
       </c>
       <c r="K228" s="9"/>
       <c r="L228" s="10" t="s">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="M228" s="10"/>
       <c r="N228" s="10"/>
@@ -15474,13 +15504,13 @@
         <v>28</v>
       </c>
       <c r="P228" s="9" t="s">
-        <v>1192</v>
+        <v>826</v>
       </c>
       <c r="Q228" s="9" t="s">
-        <v>1193</v>
+        <v>982</v>
       </c>
       <c r="R228" s="9" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S228" s="9">
         <v>1</v>
@@ -15488,34 +15518,34 @@
     </row>
     <row r="229" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
-        <v>1194</v>
+        <v>1182</v>
       </c>
       <c r="B229" s="9" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C229" s="9" t="s">
         <v>1179</v>
-      </c>
-      <c r="C229" s="9" t="s">
-        <v>1180</v>
       </c>
       <c r="D229" s="9"/>
       <c r="E229" s="9"/>
       <c r="F229" s="9" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G229" s="9" t="s">
         <v>39</v>
       </c>
       <c r="H229" s="9" t="s">
-        <v>377</v>
+        <v>1021</v>
       </c>
       <c r="I229" s="9" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="J229" s="9" t="s">
-        <v>103</v>
+        <v>334</v>
       </c>
       <c r="K229" s="9"/>
       <c r="L229" s="10" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="M229" s="10"/>
       <c r="N229" s="10"/>
@@ -15523,13 +15553,13 @@
         <v>28</v>
       </c>
       <c r="P229" s="9" t="s">
-        <v>1032</v>
+        <v>1184</v>
       </c>
       <c r="Q229" s="9" t="s">
-        <v>236</v>
+        <v>1031</v>
       </c>
       <c r="R229" s="9" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S229" s="9">
         <v>1</v>
@@ -15537,34 +15567,34 @@
     </row>
     <row r="230" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
-        <v>1196</v>
+        <v>1185</v>
       </c>
       <c r="B230" s="9" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C230" s="9" t="s">
         <v>1179</v>
-      </c>
-      <c r="C230" s="9" t="s">
-        <v>1180</v>
       </c>
       <c r="D230" s="9"/>
       <c r="E230" s="9"/>
       <c r="F230" s="9" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G230" s="9" t="s">
         <v>39</v>
       </c>
       <c r="H230" s="9" t="s">
-        <v>856</v>
+        <v>1021</v>
       </c>
       <c r="I230" s="9" t="s">
-        <v>1189</v>
+        <v>102</v>
       </c>
       <c r="J230" s="9" t="s">
-        <v>1197</v>
+        <v>271</v>
       </c>
       <c r="K230" s="9"/>
       <c r="L230" s="10" t="s">
-        <v>1198</v>
+        <v>1186</v>
       </c>
       <c r="M230" s="10"/>
       <c r="N230" s="10"/>
@@ -15572,195 +15602,195 @@
         <v>28</v>
       </c>
       <c r="P230" s="9" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="Q230" s="9" t="s">
-        <v>951</v>
+        <v>231</v>
       </c>
       <c r="R230" s="9" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S230" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B231" s="2" t="s">
+    <row r="231" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="6" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C231" s="9" t="s">
         <v>1179</v>
       </c>
-      <c r="C231" s="2" t="s">
+      <c r="D231" s="9"/>
+      <c r="E231" s="9"/>
+      <c r="F231" s="9" t="s">
         <v>1180</v>
       </c>
-      <c r="D231" s="11"/>
-      <c r="E231" s="11"/>
-      <c r="F231" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="G231" s="2" t="s">
+      <c r="G231" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H231" s="2" t="s">
+      <c r="H231" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="I231" s="2" t="s">
-        <v>1200</v>
-      </c>
-      <c r="J231" s="2" t="s">
-        <v>1201</v>
-      </c>
-      <c r="K231" s="11"/>
-      <c r="L231" s="4" t="s">
-        <v>1202</v>
-      </c>
-      <c r="M231" s="4"/>
-      <c r="N231" s="4"/>
-      <c r="O231" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P231" s="2" t="s">
+      <c r="I231" s="9" t="s">
+        <v>1188</v>
+      </c>
+      <c r="J231" s="9" t="s">
+        <v>1189</v>
+      </c>
+      <c r="K231" s="9"/>
+      <c r="L231" s="10" t="s">
+        <v>1190</v>
+      </c>
+      <c r="M231" s="10"/>
+      <c r="N231" s="10"/>
+      <c r="O231" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P231" s="9" t="s">
+        <v>1191</v>
+      </c>
+      <c r="Q231" s="9" t="s">
         <v>1192</v>
       </c>
-      <c r="Q231" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="R231" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="S231" s="2">
+      <c r="R231" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="S231" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="B232" s="2" t="s">
+    <row r="232" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="6" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C232" s="9" t="s">
         <v>1179</v>
       </c>
-      <c r="C232" s="2" t="s">
+      <c r="D232" s="9"/>
+      <c r="E232" s="9"/>
+      <c r="F232" s="9" t="s">
         <v>1180</v>
       </c>
-      <c r="D232" s="11"/>
-      <c r="E232" s="11"/>
-      <c r="F232" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="G232" s="2" t="s">
+      <c r="G232" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H232" s="2" t="s">
+      <c r="H232" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="I232" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="J232" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="K232" s="9"/>
+      <c r="L232" s="10" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M232" s="10"/>
+      <c r="N232" s="10"/>
+      <c r="O232" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P232" s="9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="Q232" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="R232" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="S232" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="6" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C233" s="9" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D233" s="9"/>
+      <c r="E233" s="9"/>
+      <c r="F233" s="9" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G233" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="I232" s="2" t="s">
-        <v>1189</v>
-      </c>
-      <c r="J232" s="2" t="s">
+      <c r="H233" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="I233" s="9" t="s">
+        <v>1188</v>
+      </c>
+      <c r="J233" s="9" t="s">
+        <v>1196</v>
+      </c>
+      <c r="K233" s="9"/>
+      <c r="L233" s="10" t="s">
         <v>1197</v>
       </c>
-      <c r="K232" s="11"/>
-      <c r="L232" s="4" t="s">
-        <v>1204</v>
-      </c>
-      <c r="M232" s="4"/>
-      <c r="N232" s="4"/>
-      <c r="O232" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P232" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="Q232" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="R232" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="S232" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D233" s="11"/>
-      <c r="E233" s="11"/>
-      <c r="F233" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="G233" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H233" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="I233" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="J233" s="2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="K233" s="11"/>
-      <c r="L233" s="4" t="s">
-        <v>1209</v>
-      </c>
-      <c r="M233" s="4"/>
-      <c r="N233" s="4"/>
-      <c r="O233" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P233" s="2" t="s">
-        <v>1210</v>
-      </c>
-      <c r="Q233" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="R233" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="S233" s="2">
+      <c r="M233" s="10"/>
+      <c r="N233" s="10"/>
+      <c r="O233" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P233" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q233" s="9" t="s">
+        <v>950</v>
+      </c>
+      <c r="R233" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="S233" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>1211</v>
+        <v>1198</v>
       </c>
       <c r="B234" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>1179</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>1180</v>
       </c>
       <c r="D234" s="11"/>
       <c r="E234" s="11"/>
       <c r="F234" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>39</v>
+        <v>377</v>
       </c>
       <c r="I234" s="2" t="s">
-        <v>40</v>
+        <v>1199</v>
       </c>
       <c r="J234" s="2" t="s">
-        <v>41</v>
+        <v>1200</v>
       </c>
       <c r="K234" s="11"/>
       <c r="L234" s="4" t="s">
-        <v>1212</v>
+        <v>1201</v>
       </c>
       <c r="M234" s="4"/>
       <c r="N234" s="4"/>
@@ -15768,211 +15798,358 @@
         <v>28</v>
       </c>
       <c r="P234" s="2" t="s">
-        <v>1028</v>
+        <v>1191</v>
       </c>
       <c r="Q234" s="2" t="s">
-        <v>151</v>
+        <v>1031</v>
       </c>
       <c r="R234" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S234" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="6" t="s">
-        <v>1213</v>
-      </c>
-      <c r="B235" s="9" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C235" s="9" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D235" s="9"/>
-      <c r="E235" s="9"/>
-      <c r="F235" s="9" t="s">
-        <v>1216</v>
-      </c>
-      <c r="G235" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H235" s="9" t="s">
-        <v>1217</v>
-      </c>
-      <c r="I235" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="J235" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="K235" s="9"/>
-      <c r="L235" s="10" t="s">
-        <v>1218</v>
-      </c>
-      <c r="M235" s="10"/>
-      <c r="N235" s="10"/>
-      <c r="O235" s="9" t="s">
-        <v>1219</v>
-      </c>
-      <c r="P235" s="9" t="s">
-        <v>1220</v>
-      </c>
-      <c r="Q235" s="9" t="s">
-        <v>1221</v>
-      </c>
-      <c r="R235" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="S235" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="236" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="6" t="s">
-        <v>1222</v>
-      </c>
-      <c r="B236" s="9" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C236" s="9" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D236" s="9"/>
-      <c r="E236" s="9"/>
-      <c r="F236" s="9" t="s">
-        <v>1216</v>
-      </c>
-      <c r="G236" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H236" s="9" t="s">
-        <v>1223</v>
-      </c>
-      <c r="I236" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="J236" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="K236" s="9"/>
-      <c r="L236" s="10" t="s">
-        <v>1224</v>
-      </c>
-      <c r="M236" s="10"/>
-      <c r="N236" s="10"/>
-      <c r="O236" s="9" t="s">
-        <v>1225</v>
-      </c>
-      <c r="P236" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="Q236" s="9" t="s">
-        <v>1227</v>
-      </c>
-      <c r="R236" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="S236" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="237" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="6" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B237" s="9" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C237" s="9" t="s">
-        <v>1229</v>
-      </c>
-      <c r="D237" s="9"/>
-      <c r="E237" s="9"/>
-      <c r="F237" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="G237" s="9" t="s">
-        <v>852</v>
-      </c>
-      <c r="H237" s="9" t="s">
-        <v>834</v>
-      </c>
-      <c r="I237" s="9" t="s">
+    <row r="235" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D235" s="11"/>
+      <c r="E235" s="11"/>
+      <c r="F235" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H235" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I235" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="J235" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="K235" s="11"/>
+      <c r="L235" s="4" t="s">
+        <v>1203</v>
+      </c>
+      <c r="M235" s="4"/>
+      <c r="N235" s="4"/>
+      <c r="O235" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P235" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="Q235" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="R235" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="S235" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D236" s="11"/>
+      <c r="E236" s="11"/>
+      <c r="F236" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H236" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I236" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="J236" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K236" s="11"/>
+      <c r="L236" s="4" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M236" s="4"/>
+      <c r="N236" s="4"/>
+      <c r="O236" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P236" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="Q236" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="R236" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="S236" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D237" s="11"/>
+      <c r="E237" s="11"/>
+      <c r="F237" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G237" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I237" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J237" s="9" t="s">
+      <c r="J237" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K237" s="9"/>
-      <c r="L237" s="10" t="s">
-        <v>1230</v>
-      </c>
-      <c r="M237" s="10"/>
-      <c r="N237" s="10"/>
-      <c r="O237" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P237" s="9" t="s">
-        <v>715</v>
-      </c>
-      <c r="Q237" s="9" t="s">
-        <v>1231</v>
-      </c>
-      <c r="R237" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S237" s="9">
-        <v>3</v>
+      <c r="K237" s="11"/>
+      <c r="L237" s="4" t="s">
+        <v>1211</v>
+      </c>
+      <c r="M237" s="4"/>
+      <c r="N237" s="4"/>
+      <c r="O237" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P237" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="Q237" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="R237" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="S237" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
-        <v>1232</v>
+        <v>1212</v>
       </c>
       <c r="B238" s="9" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C238" s="9" t="s">
         <v>1214</v>
-      </c>
-      <c r="C238" s="9" t="s">
-        <v>1229</v>
       </c>
       <c r="D238" s="9"/>
       <c r="E238" s="9"/>
       <c r="F238" s="9" t="s">
-        <v>562</v>
+        <v>1215</v>
       </c>
       <c r="G238" s="9" t="s">
-        <v>852</v>
+        <v>53</v>
       </c>
       <c r="H238" s="9" t="s">
-        <v>83</v>
+        <v>1216</v>
       </c>
       <c r="I238" s="9" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="J238" s="9" t="s">
-        <v>41</v>
+        <v>184</v>
       </c>
       <c r="K238" s="9"/>
       <c r="L238" s="10" t="s">
-        <v>1233</v>
+        <v>1217</v>
       </c>
       <c r="M238" s="10"/>
       <c r="N238" s="10"/>
       <c r="O238" s="9" t="s">
-        <v>28</v>
+        <v>1218</v>
       </c>
       <c r="P238" s="9" t="s">
+        <v>1219</v>
+      </c>
+      <c r="Q238" s="9" t="s">
+        <v>1220</v>
+      </c>
+      <c r="R238" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="S238" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="6" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C239" s="9" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D239" s="9"/>
+      <c r="E239" s="9"/>
+      <c r="F239" s="9" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G239" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H239" s="9" t="s">
+        <v>1222</v>
+      </c>
+      <c r="I239" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="J239" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="K239" s="9"/>
+      <c r="L239" s="10" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M239" s="10"/>
+      <c r="N239" s="10"/>
+      <c r="O239" s="9" t="s">
+        <v>1224</v>
+      </c>
+      <c r="P239" s="9" t="s">
+        <v>1225</v>
+      </c>
+      <c r="Q239" s="9" t="s">
+        <v>1226</v>
+      </c>
+      <c r="R239" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="S239" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="6" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C240" s="9" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D240" s="9"/>
+      <c r="E240" s="9"/>
+      <c r="F240" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="G240" s="9" t="s">
+        <v>851</v>
+      </c>
+      <c r="H240" s="9" t="s">
+        <v>834</v>
+      </c>
+      <c r="I240" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J240" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K240" s="9"/>
+      <c r="L240" s="10" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M240" s="10"/>
+      <c r="N240" s="10"/>
+      <c r="O240" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P240" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="Q240" s="9" t="s">
+        <v>1230</v>
+      </c>
+      <c r="R240" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S240" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="6" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C241" s="9" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D241" s="9"/>
+      <c r="E241" s="9"/>
+      <c r="F241" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="G241" s="9" t="s">
+        <v>851</v>
+      </c>
+      <c r="H241" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I241" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J241" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K241" s="9"/>
+      <c r="L241" s="10" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M241" s="10"/>
+      <c r="N241" s="10"/>
+      <c r="O241" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P241" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="Q238" s="9" t="s">
-        <v>1234</v>
-      </c>
-      <c r="R238" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="S238" s="9">
+      <c r="Q241" s="9" t="s">
+        <v>1233</v>
+      </c>
+      <c r="R241" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S241" s="9">
         <v>3</v>
       </c>
     </row>
@@ -16125,96 +16302,99 @@
     <hyperlink ref="A148" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
     <hyperlink ref="A149" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
     <hyperlink ref="A150" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="A151" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="A152" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="A153" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="A154" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="A155" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="A156" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="A157" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="A158" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="A159" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="A160" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="A161" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="A162" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="A163" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="A164" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="A165" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="A166" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="A167" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="A168" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="A169" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="A170" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="A171" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="A172" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="A173" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="A174" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="A175" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="A176" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="A177" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="A178" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="A179" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="A180" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="A181" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="A182" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="A183" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="A184" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="A185" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="A186" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="A187" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="A188" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="A189" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="A190" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="A191" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="A192" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="A193" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="A194" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="A195" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="A196" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="A197" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="A198" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="A199" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="A200" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="A201" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="A202" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="A203" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="A204" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="A205" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="A206" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="A207" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="A208" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="A209" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="A210" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="A211" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="A212" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="A213" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="A214" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="A215" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="A216" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="A217" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="A218" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="A219" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="A220" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="A221" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="A222" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="A223" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="A224" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="A225" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="A226" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="A227" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="A228" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="A229" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="A230" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="A231" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="A232" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="A233" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="A234" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="A235" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="A236" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="A237" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="A238" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="A154" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="A155" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="A156" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="A157" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="A158" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="A159" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="A160" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="A161" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="A162" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="A163" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="A164" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="A165" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="A166" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="A167" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="A168" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="A169" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="A170" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="A171" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="A172" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="A173" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="A174" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="A175" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="A176" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="A177" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="A178" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="A179" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="A180" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="A181" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="A182" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="A183" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="A184" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="A185" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="A186" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="A187" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="A188" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="A189" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="A190" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="A191" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="A192" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="A193" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="A194" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="A195" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="A196" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="A197" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="A198" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="A199" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="A200" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="A201" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="A202" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="A203" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="A204" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="A205" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="A206" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="A207" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="A208" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="A209" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="A210" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="A211" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="A212" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="A213" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="A214" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="A215" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="A216" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="A217" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="A218" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="A219" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="A220" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="A221" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="A222" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="A223" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="A224" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="A225" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="A226" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="A227" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="A228" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="A229" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="A230" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="A231" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="A232" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="A233" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="A234" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="A235" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="A236" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="A237" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="A238" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="A239" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="A240" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="A241" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
     <hyperlink ref="A134" r:id="rId236" xr:uid="{4A4B0A83-2112-4619-AB91-366EF2F543FC}"/>
     <hyperlink ref="A18" r:id="rId237" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Camille_Pissarro_-_La_C%C3%B4te_du_Jallais%2C_Pontoise_-_1867.jpg/1280px-Camille_Pissarro_-_La_C%C3%B4te_du_Jallais%2C_Pontoise_-_1867.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1983AA0F-5B6C-4325-946D-9B6A9E22E192}"/>
+    <hyperlink ref="A151" r:id="rId238" xr:uid="{754AB718-3BBE-41CD-ADE5-4A65C8B74A56}"/>
+    <hyperlink ref="A152" r:id="rId239" xr:uid="{E23B0D6E-BEFF-48DE-BC26-EA6AE385F143}"/>
+    <hyperlink ref="A153" r:id="rId240" location="/media/File:Jean-Fran%C3%A7ois_Millet_(II)_-_Spring_-_WGA15693.jpg" xr:uid="{AC2946C4-78F0-4E7E-95FE-0935AB4E6098}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C21A134-395A-480A-BB5B-15B2C53F1DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606D8CDF-0C55-4F02-8AC7-C78DC6539D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3787,7 +3787,7 @@
     <t>Bergère avec son troupeau</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/File:Jean-Fran%C3%A7ois_Millet_(II)_006.jpg#/media/File:Jean-Fran%C3%A7ois_Millet_(II)_-_Spring_-_WGA15693.jpg</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/52/Jean-Fran%C3%A7ois_Millet_%28II%29_-_Spring_-_WGA15693.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
 </sst>
 </file>
@@ -16394,7 +16394,7 @@
     <hyperlink ref="A18" r:id="rId237" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Camille_Pissarro_-_La_C%C3%B4te_du_Jallais%2C_Pontoise_-_1867.jpg/1280px-Camille_Pissarro_-_La_C%C3%B4te_du_Jallais%2C_Pontoise_-_1867.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1983AA0F-5B6C-4325-946D-9B6A9E22E192}"/>
     <hyperlink ref="A151" r:id="rId238" xr:uid="{754AB718-3BBE-41CD-ADE5-4A65C8B74A56}"/>
     <hyperlink ref="A152" r:id="rId239" xr:uid="{E23B0D6E-BEFF-48DE-BC26-EA6AE385F143}"/>
-    <hyperlink ref="A153" r:id="rId240" location="/media/File:Jean-Fran%C3%A7ois_Millet_(II)_-_Spring_-_WGA15693.jpg" xr:uid="{AC2946C4-78F0-4E7E-95FE-0935AB4E6098}"/>
+    <hyperlink ref="A153" r:id="rId240" xr:uid="{02660EEF-8A95-40BB-92DC-77A665920B4D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606D8CDF-0C55-4F02-8AC7-C78DC6539D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396F1055-2B69-47C8-A4F9-0B13DCFA8440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7247,7 +7247,7 @@
         <v>353</v>
       </c>
       <c r="S60" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9141,7 +9141,7 @@
         <v>31</v>
       </c>
       <c r="S98" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10762,7 +10762,7 @@
         <v>31</v>
       </c>
       <c r="S131" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11058,7 +11058,7 @@
         <v>516</v>
       </c>
       <c r="S137" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11303,7 +11303,7 @@
         <v>31</v>
       </c>
       <c r="S142" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396F1055-2B69-47C8-A4F9-0B13DCFA8440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDFED77-2713-4E34-A656-D5E05FEA42D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3304,9 +3304,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Renoir_-_The_Two_Sisters%2C_On_the_Terrace.jpg/1280px-Renoir_-_The_Two_Sisters%2C_On_the_Terrace.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>"Les Deux Sœurs (Sur la terrasse)"</t>
-  </si>
-  <si>
     <t>100,5 cm</t>
   </si>
   <si>
@@ -3788,6 +3785,9 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/52/Jean-Fran%C3%A7ois_Millet_%28II%29_-_Spring_-_WGA15693.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>"Les Deux Sœurs"</t>
   </si>
 </sst>
 </file>
@@ -4883,7 +4883,7 @@
         <v>91</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="4" t="s">
@@ -5105,7 +5105,7 @@
     </row>
     <row r="18" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>97</v>
@@ -5131,10 +5131,10 @@
         <v>34</v>
       </c>
       <c r="K18" s="9" t="s">
+        <v>1240</v>
+      </c>
+      <c r="L18" s="10" t="s">
         <v>1241</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>1242</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
@@ -5145,7 +5145,7 @@
         <v>87</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="R18" s="9" t="s">
         <v>31</v>
@@ -6241,7 +6241,7 @@
         <v>31</v>
       </c>
       <c r="S40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6292,7 +6292,7 @@
         <v>31</v>
       </c>
       <c r="S41" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6343,7 +6343,7 @@
         <v>31</v>
       </c>
       <c r="S42" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6394,7 +6394,7 @@
         <v>31</v>
       </c>
       <c r="S43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6445,7 +6445,7 @@
         <v>31</v>
       </c>
       <c r="S44" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6927,7 +6927,7 @@
         <v>315</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>63</v>
@@ -7896,7 +7896,7 @@
         <v>31</v>
       </c>
       <c r="S73" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7947,7 +7947,7 @@
         <v>31</v>
       </c>
       <c r="S74" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7998,7 +7998,7 @@
         <v>31</v>
       </c>
       <c r="S75" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8104,7 +8104,7 @@
         <v>31</v>
       </c>
       <c r="S77" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8826,7 +8826,7 @@
         <v>91</v>
       </c>
       <c r="J92" s="9" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="K92" s="9"/>
       <c r="L92" s="10" t="s">
@@ -9022,7 +9022,7 @@
         <v>91</v>
       </c>
       <c r="J96" s="9" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="K96" s="9"/>
       <c r="L96" s="10" t="s">
@@ -9654,7 +9654,7 @@
         <v>640</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>445</v>
@@ -9703,7 +9703,7 @@
         <v>643</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>592</v>
@@ -9752,7 +9752,7 @@
         <v>288</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>592</v>
@@ -10865,7 +10865,7 @@
     </row>
     <row r="134" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="13" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B134" s="9" t="s">
         <v>743</v>
@@ -10892,11 +10892,11 @@
       </c>
       <c r="K134" s="9"/>
       <c r="L134" s="10" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="M134" s="10"/>
       <c r="N134" s="10" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="O134" s="9" t="s">
         <v>28</v>
@@ -11156,7 +11156,7 @@
         <v>31</v>
       </c>
       <c r="S139" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11205,7 +11205,7 @@
         <v>31</v>
       </c>
       <c r="S140" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="K149" s="9"/>
       <c r="L149" s="10" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="M149" s="10"/>
       <c r="N149" s="10"/>
@@ -11646,7 +11646,7 @@
         <v>31</v>
       </c>
       <c r="S149" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11695,12 +11695,12 @@
         <v>31</v>
       </c>
       <c r="S150" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="14" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B151" s="9" t="s">
         <v>838</v>
@@ -11723,11 +11723,11 @@
         <v>738</v>
       </c>
       <c r="J151" s="9" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="K151" s="9"/>
       <c r="L151" s="10" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="M151" s="10"/>
       <c r="N151" s="10"/>
@@ -11735,21 +11735,21 @@
         <v>28</v>
       </c>
       <c r="P151" s="9" t="s">
+        <v>1246</v>
+      </c>
+      <c r="Q151" s="9" t="s">
         <v>1247</v>
       </c>
-      <c r="Q151" s="9" t="s">
-        <v>1248</v>
-      </c>
       <c r="R151" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S151" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="14" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B152" s="9" t="s">
         <v>838</v>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="K152" s="9"/>
       <c r="L152" s="10" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="M152" s="10"/>
       <c r="N152" s="10"/>
@@ -11798,7 +11798,7 @@
     </row>
     <row r="153" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="14" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B153" s="9" t="s">
         <v>838</v>
@@ -11815,7 +11815,7 @@
         <v>46</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="I153" s="9" t="s">
         <v>40</v>
@@ -11825,7 +11825,7 @@
       </c>
       <c r="K153" s="9"/>
       <c r="L153" s="10" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="M153" s="10"/>
       <c r="N153" s="10"/>
@@ -12556,7 +12556,7 @@
         <v>91</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="K168" s="9"/>
       <c r="L168" s="10" t="s">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="K208" s="2"/>
       <c r="L208" s="4" t="s">
-        <v>1094</v>
+        <v>1255</v>
       </c>
       <c r="M208" s="3"/>
       <c r="N208" s="2"/>
@@ -14518,7 +14518,7 @@
         <v>28</v>
       </c>
       <c r="P208" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="Q208" s="2" t="s">
         <v>30</v>
@@ -14532,7 +14532,7 @@
     </row>
     <row r="209" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>1064</v>
@@ -14559,10 +14559,10 @@
       </c>
       <c r="K209" s="2"/>
       <c r="L209" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="M209" s="4" t="s">
         <v>1097</v>
-      </c>
-      <c r="M209" s="4" t="s">
-        <v>1098</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2" t="s">
@@ -14583,7 +14583,7 @@
     </row>
     <row r="210" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>1064</v>
@@ -14610,10 +14610,10 @@
       </c>
       <c r="K210" s="2"/>
       <c r="L210" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="M210" s="4" t="s">
         <v>1100</v>
-      </c>
-      <c r="M210" s="4" t="s">
-        <v>1101</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2" t="s">
@@ -14634,13 +14634,13 @@
     </row>
     <row r="211" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B211" s="9" t="s">
         <v>1053</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D211" s="9"/>
       <c r="E211" s="9"/>
@@ -14661,7 +14661,7 @@
       </c>
       <c r="K211" s="9"/>
       <c r="L211" s="10" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="M211" s="10"/>
       <c r="N211" s="10"/>
@@ -14669,10 +14669,10 @@
         <v>28</v>
       </c>
       <c r="P211" s="9" t="s">
+        <v>1104</v>
+      </c>
+      <c r="Q211" s="9" t="s">
         <v>1105</v>
-      </c>
-      <c r="Q211" s="9" t="s">
-        <v>1106</v>
       </c>
       <c r="R211" s="9" t="s">
         <v>31</v>
@@ -14683,13 +14683,13 @@
     </row>
     <row r="212" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B212" s="9" t="s">
         <v>1053</v>
       </c>
       <c r="C212" s="9" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D212" s="9"/>
       <c r="E212" s="9"/>
@@ -14710,7 +14710,7 @@
       </c>
       <c r="K212" s="9"/>
       <c r="L212" s="10" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="M212" s="10"/>
       <c r="N212" s="10"/>
@@ -14732,13 +14732,13 @@
     </row>
     <row r="213" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B213" s="9" t="s">
         <v>1109</v>
       </c>
-      <c r="B213" s="9" t="s">
+      <c r="C213" s="9" t="s">
         <v>1110</v>
-      </c>
-      <c r="C213" s="9" t="s">
-        <v>1111</v>
       </c>
       <c r="D213" s="9"/>
       <c r="E213" s="9"/>
@@ -14752,14 +14752,14 @@
         <v>1021</v>
       </c>
       <c r="I213" s="9" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="J213" s="9" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="K213" s="9"/>
       <c r="L213" s="10" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="M213" s="10"/>
       <c r="N213" s="10"/>
@@ -14767,10 +14767,10 @@
         <v>28</v>
       </c>
       <c r="P213" s="9" t="s">
+        <v>1113</v>
+      </c>
+      <c r="Q213" s="9" t="s">
         <v>1114</v>
-      </c>
-      <c r="Q213" s="9" t="s">
-        <v>1115</v>
       </c>
       <c r="R213" s="9" t="s">
         <v>31</v>
@@ -14781,13 +14781,13 @@
     </row>
     <row r="214" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B214" s="9" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C214" s="9" t="s">
         <v>1110</v>
-      </c>
-      <c r="C214" s="9" t="s">
-        <v>1111</v>
       </c>
       <c r="D214" s="9"/>
       <c r="E214" s="9"/>
@@ -14798,7 +14798,7 @@
         <v>23</v>
       </c>
       <c r="H214" s="9" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="I214" s="9" t="s">
         <v>33</v>
@@ -14808,7 +14808,7 @@
       </c>
       <c r="K214" s="9"/>
       <c r="L214" s="10" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="M214" s="10"/>
       <c r="N214" s="10"/>
@@ -14816,10 +14816,10 @@
         <v>28</v>
       </c>
       <c r="P214" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="Q214" s="9" t="s">
         <v>1119</v>
-      </c>
-      <c r="Q214" s="9" t="s">
-        <v>1120</v>
       </c>
       <c r="R214" s="9" t="s">
         <v>31</v>
@@ -14830,13 +14830,13 @@
     </row>
     <row r="215" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B215" s="9" t="s">
         <v>1121</v>
       </c>
-      <c r="B215" s="9" t="s">
+      <c r="C215" s="9" t="s">
         <v>1122</v>
-      </c>
-      <c r="C215" s="9" t="s">
-        <v>1123</v>
       </c>
       <c r="D215" s="9"/>
       <c r="E215" s="9"/>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="K215" s="9"/>
       <c r="L215" s="10" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="M215" s="10"/>
       <c r="N215" s="10"/>
@@ -14879,13 +14879,13 @@
     </row>
     <row r="216" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B216" s="9" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C216" s="9" t="s">
         <v>1122</v>
-      </c>
-      <c r="C216" s="9" t="s">
-        <v>1123</v>
       </c>
       <c r="D216" s="9"/>
       <c r="E216" s="9"/>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="K216" s="9"/>
       <c r="L216" s="10" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="M216" s="10"/>
       <c r="N216" s="10"/>
@@ -14928,13 +14928,13 @@
     </row>
     <row r="217" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B217" s="9" t="s">
         <v>1127</v>
       </c>
-      <c r="B217" s="9" t="s">
+      <c r="C217" s="9" t="s">
         <v>1128</v>
-      </c>
-      <c r="C217" s="9" t="s">
-        <v>1129</v>
       </c>
       <c r="D217" s="9"/>
       <c r="E217" s="9"/>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="K217" s="9"/>
       <c r="L217" s="10" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="M217" s="10"/>
       <c r="N217" s="10"/>
@@ -14963,27 +14963,27 @@
         <v>28</v>
       </c>
       <c r="P217" s="9" t="s">
+        <v>1130</v>
+      </c>
+      <c r="Q217" s="9" t="s">
         <v>1131</v>
       </c>
-      <c r="Q217" s="9" t="s">
-        <v>1132</v>
-      </c>
       <c r="R217" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S217" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B218" s="9" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C218" s="9" t="s">
         <v>1128</v>
-      </c>
-      <c r="C218" s="9" t="s">
-        <v>1129</v>
       </c>
       <c r="D218" s="9"/>
       <c r="E218" s="9"/>
@@ -14994,7 +14994,7 @@
         <v>387</v>
       </c>
       <c r="H218" s="9" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="I218" s="9" t="s">
         <v>40</v>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="K218" s="9"/>
       <c r="L218" s="10" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="M218" s="10"/>
       <c r="N218" s="10"/>
@@ -15012,27 +15012,27 @@
         <v>28</v>
       </c>
       <c r="P218" s="9" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Q218" s="9" t="s">
         <v>1136</v>
       </c>
-      <c r="Q218" s="9" t="s">
-        <v>1137</v>
-      </c>
       <c r="R218" s="9" t="s">
         <v>31</v>
       </c>
       <c r="S218" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B219" s="9" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C219" s="9" t="s">
         <v>1128</v>
-      </c>
-      <c r="C219" s="9" t="s">
-        <v>1129</v>
       </c>
       <c r="D219" s="9"/>
       <c r="E219" s="9"/>
@@ -15053,7 +15053,7 @@
       </c>
       <c r="K219" s="9"/>
       <c r="L219" s="10" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="M219" s="10"/>
       <c r="N219" s="10"/>
@@ -15064,7 +15064,7 @@
         <v>209</v>
       </c>
       <c r="Q219" s="9" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="R219" s="9" t="s">
         <v>31</v>
@@ -15075,13 +15075,13 @@
     </row>
     <row r="220" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B220" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C220" s="2" t="s">
         <v>1128</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>1129</v>
       </c>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -15092,17 +15092,17 @@
         <v>387</v>
       </c>
       <c r="H220" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="I220" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="I220" s="2" t="s">
+      <c r="J220" s="2" t="s">
         <v>1143</v>
-      </c>
-      <c r="J220" s="2" t="s">
-        <v>1144</v>
       </c>
       <c r="K220" s="2"/>
       <c r="L220" s="4" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="M220" s="3"/>
       <c r="N220" s="3"/>
@@ -15124,13 +15124,13 @@
     </row>
     <row r="221" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B221" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C221" s="2" t="s">
         <v>1128</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>1129</v>
       </c>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -15141,17 +15141,17 @@
         <v>387</v>
       </c>
       <c r="H221" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="I221" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="I221" s="2" t="s">
+      <c r="J221" s="2" t="s">
         <v>1148</v>
-      </c>
-      <c r="J221" s="2" t="s">
-        <v>1149</v>
       </c>
       <c r="K221" s="2"/>
       <c r="L221" s="4" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="M221" s="3"/>
       <c r="N221" s="3"/>
@@ -15173,18 +15173,18 @@
     </row>
     <row r="222" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C222" s="9" t="s">
         <v>1151</v>
-      </c>
-      <c r="B222" s="9" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C222" s="9" t="s">
-        <v>1152</v>
       </c>
       <c r="D222" s="9"/>
       <c r="E222" s="9"/>
       <c r="F222" s="9" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G222" s="9" t="s">
         <v>159</v>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="K222" s="9"/>
       <c r="L222" s="10" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="M222" s="10"/>
       <c r="N222" s="10"/>
@@ -15222,24 +15222,24 @@
     </row>
     <row r="223" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D223" s="9"/>
       <c r="E223" s="9"/>
       <c r="F223" s="9" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G223" s="9" t="s">
         <v>159</v>
       </c>
       <c r="H223" s="9" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="I223" s="9" t="s">
         <v>40</v>
@@ -15249,7 +15249,7 @@
       </c>
       <c r="K223" s="9"/>
       <c r="L223" s="10" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="M223" s="10"/>
       <c r="N223" s="10"/>
@@ -15271,18 +15271,18 @@
     </row>
     <row r="224" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B224" s="9" t="s">
         <v>1157</v>
       </c>
-      <c r="B224" s="9" t="s">
+      <c r="C224" s="9" t="s">
         <v>1158</v>
-      </c>
-      <c r="C224" s="9" t="s">
-        <v>1159</v>
       </c>
       <c r="D224" s="9"/>
       <c r="E224" s="9"/>
       <c r="F224" s="9" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G224" s="9" t="s">
         <v>577</v>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="K224" s="9"/>
       <c r="L224" s="10" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="M224" s="10"/>
       <c r="N224" s="10"/>
@@ -15306,10 +15306,10 @@
         <v>28</v>
       </c>
       <c r="P224" s="9" t="s">
+        <v>1161</v>
+      </c>
+      <c r="Q224" s="9" t="s">
         <v>1162</v>
-      </c>
-      <c r="Q224" s="9" t="s">
-        <v>1163</v>
       </c>
       <c r="R224" s="9" t="s">
         <v>516</v>
@@ -15320,18 +15320,18 @@
     </row>
     <row r="225" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B225" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C225" s="9" t="s">
         <v>1158</v>
-      </c>
-      <c r="C225" s="9" t="s">
-        <v>1159</v>
       </c>
       <c r="D225" s="9"/>
       <c r="E225" s="9"/>
       <c r="F225" s="9" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G225" s="9" t="s">
         <v>577</v>
@@ -15347,20 +15347,20 @@
       </c>
       <c r="K225" s="9"/>
       <c r="L225" s="10" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="M225" s="10"/>
       <c r="N225" s="10" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O225" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P225" s="9" t="s">
         <v>1166</v>
       </c>
-      <c r="O225" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P225" s="9" t="s">
+      <c r="Q225" s="9" t="s">
         <v>1167</v>
-      </c>
-      <c r="Q225" s="9" t="s">
-        <v>1168</v>
       </c>
       <c r="R225" s="9" t="s">
         <v>516</v>
@@ -15371,13 +15371,13 @@
     </row>
     <row r="226" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B226" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C226" s="9" t="s">
         <v>1169</v>
-      </c>
-      <c r="B226" s="9" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C226" s="9" t="s">
-        <v>1170</v>
       </c>
       <c r="D226" s="9"/>
       <c r="E226" s="9"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K226" s="9"/>
       <c r="L226" s="10" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="M226" s="10"/>
       <c r="N226" s="10"/>
@@ -15409,7 +15409,7 @@
         <v>748</v>
       </c>
       <c r="Q226" s="9" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="R226" s="9" t="s">
         <v>516</v>
@@ -15420,13 +15420,13 @@
     </row>
     <row r="227" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C227" s="9" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="D227" s="9"/>
       <c r="E227" s="9"/>
@@ -15447,7 +15447,7 @@
       </c>
       <c r="K227" s="9"/>
       <c r="L227" s="10" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="M227" s="10"/>
       <c r="N227" s="10"/>
@@ -15455,10 +15455,10 @@
         <v>28</v>
       </c>
       <c r="P227" s="9" t="s">
+        <v>1174</v>
+      </c>
+      <c r="Q227" s="9" t="s">
         <v>1175</v>
-      </c>
-      <c r="Q227" s="9" t="s">
-        <v>1176</v>
       </c>
       <c r="R227" s="9" t="s">
         <v>516</v>
@@ -15469,18 +15469,18 @@
     </row>
     <row r="228" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B228" s="9" t="s">
         <v>1177</v>
       </c>
-      <c r="B228" s="9" t="s">
+      <c r="C228" s="9" t="s">
         <v>1178</v>
-      </c>
-      <c r="C228" s="9" t="s">
-        <v>1179</v>
       </c>
       <c r="D228" s="9"/>
       <c r="E228" s="9"/>
       <c r="F228" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G228" s="9" t="s">
         <v>39</v>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="K228" s="9"/>
       <c r="L228" s="10" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="M228" s="10"/>
       <c r="N228" s="10"/>
@@ -15518,18 +15518,18 @@
     </row>
     <row r="229" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B229" s="9" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C229" s="9" t="s">
         <v>1178</v>
-      </c>
-      <c r="C229" s="9" t="s">
-        <v>1179</v>
       </c>
       <c r="D229" s="9"/>
       <c r="E229" s="9"/>
       <c r="F229" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G229" s="9" t="s">
         <v>39</v>
@@ -15545,7 +15545,7 @@
       </c>
       <c r="K229" s="9"/>
       <c r="L229" s="10" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="M229" s="10"/>
       <c r="N229" s="10"/>
@@ -15553,7 +15553,7 @@
         <v>28</v>
       </c>
       <c r="P229" s="9" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="Q229" s="9" t="s">
         <v>1031</v>
@@ -15567,18 +15567,18 @@
     </row>
     <row r="230" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B230" s="9" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C230" s="9" t="s">
         <v>1178</v>
-      </c>
-      <c r="C230" s="9" t="s">
-        <v>1179</v>
       </c>
       <c r="D230" s="9"/>
       <c r="E230" s="9"/>
       <c r="F230" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G230" s="9" t="s">
         <v>39</v>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="K230" s="9"/>
       <c r="L230" s="10" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="M230" s="10"/>
       <c r="N230" s="10"/>
@@ -15616,18 +15616,18 @@
     </row>
     <row r="231" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B231" s="9" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C231" s="9" t="s">
         <v>1178</v>
-      </c>
-      <c r="C231" s="9" t="s">
-        <v>1179</v>
       </c>
       <c r="D231" s="9"/>
       <c r="E231" s="9"/>
       <c r="F231" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G231" s="9" t="s">
         <v>39</v>
@@ -15636,14 +15636,14 @@
         <v>377</v>
       </c>
       <c r="I231" s="9" t="s">
+        <v>1187</v>
+      </c>
+      <c r="J231" s="9" t="s">
         <v>1188</v>
-      </c>
-      <c r="J231" s="9" t="s">
-        <v>1189</v>
       </c>
       <c r="K231" s="9"/>
       <c r="L231" s="10" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="M231" s="10"/>
       <c r="N231" s="10"/>
@@ -15651,10 +15651,10 @@
         <v>28</v>
       </c>
       <c r="P231" s="9" t="s">
+        <v>1190</v>
+      </c>
+      <c r="Q231" s="9" t="s">
         <v>1191</v>
-      </c>
-      <c r="Q231" s="9" t="s">
-        <v>1192</v>
       </c>
       <c r="R231" s="9" t="s">
         <v>871</v>
@@ -15665,18 +15665,18 @@
     </row>
     <row r="232" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B232" s="9" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C232" s="9" t="s">
         <v>1178</v>
-      </c>
-      <c r="C232" s="9" t="s">
-        <v>1179</v>
       </c>
       <c r="D232" s="9"/>
       <c r="E232" s="9"/>
       <c r="F232" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G232" s="9" t="s">
         <v>39</v>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="K232" s="9"/>
       <c r="L232" s="10" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="M232" s="10"/>
       <c r="N232" s="10"/>
@@ -15714,18 +15714,18 @@
     </row>
     <row r="233" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B233" s="9" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C233" s="9" t="s">
         <v>1178</v>
-      </c>
-      <c r="C233" s="9" t="s">
-        <v>1179</v>
       </c>
       <c r="D233" s="9"/>
       <c r="E233" s="9"/>
       <c r="F233" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G233" s="9" t="s">
         <v>39</v>
@@ -15734,14 +15734,14 @@
         <v>855</v>
       </c>
       <c r="I233" s="9" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="J233" s="9" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="K233" s="9"/>
       <c r="L233" s="10" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="M233" s="10"/>
       <c r="N233" s="10"/>
@@ -15763,18 +15763,18 @@
     </row>
     <row r="234" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B234" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>1178</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>1179</v>
       </c>
       <c r="D234" s="11"/>
       <c r="E234" s="11"/>
       <c r="F234" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>39</v>
@@ -15783,14 +15783,14 @@
         <v>377</v>
       </c>
       <c r="I234" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J234" s="2" t="s">
         <v>1199</v>
-      </c>
-      <c r="J234" s="2" t="s">
-        <v>1200</v>
       </c>
       <c r="K234" s="11"/>
       <c r="L234" s="4" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="M234" s="4"/>
       <c r="N234" s="4"/>
@@ -15798,7 +15798,7 @@
         <v>28</v>
       </c>
       <c r="P234" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="Q234" s="2" t="s">
         <v>1031</v>
@@ -15812,18 +15812,18 @@
     </row>
     <row r="235" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B235" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>1178</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>1179</v>
       </c>
       <c r="D235" s="11"/>
       <c r="E235" s="11"/>
       <c r="F235" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>39</v>
@@ -15832,14 +15832,14 @@
         <v>39</v>
       </c>
       <c r="I235" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="J235" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="K235" s="11"/>
       <c r="L235" s="4" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="M235" s="4"/>
       <c r="N235" s="4"/>
@@ -15847,10 +15847,10 @@
         <v>28</v>
       </c>
       <c r="P235" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="Q235" s="2" t="s">
         <v>1204</v>
-      </c>
-      <c r="Q235" s="2" t="s">
-        <v>1205</v>
       </c>
       <c r="R235" s="2" t="s">
         <v>871</v>
@@ -15861,18 +15861,18 @@
     </row>
     <row r="236" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B236" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C236" s="2" t="s">
         <v>1178</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>1179</v>
       </c>
       <c r="D236" s="11"/>
       <c r="E236" s="11"/>
       <c r="F236" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>39</v>
@@ -15884,11 +15884,11 @@
         <v>582</v>
       </c>
       <c r="J236" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K236" s="11"/>
       <c r="L236" s="4" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="M236" s="4"/>
       <c r="N236" s="4"/>
@@ -15896,7 +15896,7 @@
         <v>28</v>
       </c>
       <c r="P236" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="Q236" s="2" t="s">
         <v>106</v>
@@ -15910,18 +15910,18 @@
     </row>
     <row r="237" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B237" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C237" s="2" t="s">
         <v>1178</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>1179</v>
       </c>
       <c r="D237" s="11"/>
       <c r="E237" s="11"/>
       <c r="F237" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>39</v>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="K237" s="11"/>
       <c r="L237" s="4" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="M237" s="4"/>
       <c r="N237" s="4"/>
@@ -15959,24 +15959,24 @@
     </row>
     <row r="238" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B238" s="9" t="s">
         <v>1212</v>
       </c>
-      <c r="B238" s="9" t="s">
+      <c r="C238" s="9" t="s">
         <v>1213</v>
-      </c>
-      <c r="C238" s="9" t="s">
-        <v>1214</v>
       </c>
       <c r="D238" s="9"/>
       <c r="E238" s="9"/>
       <c r="F238" s="9" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G238" s="9" t="s">
         <v>53</v>
       </c>
       <c r="H238" s="9" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="I238" s="9" t="s">
         <v>102</v>
@@ -15986,18 +15986,18 @@
       </c>
       <c r="K238" s="9"/>
       <c r="L238" s="10" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="M238" s="10"/>
       <c r="N238" s="10"/>
       <c r="O238" s="9" t="s">
+        <v>1217</v>
+      </c>
+      <c r="P238" s="9" t="s">
         <v>1218</v>
       </c>
-      <c r="P238" s="9" t="s">
+      <c r="Q238" s="9" t="s">
         <v>1219</v>
-      </c>
-      <c r="Q238" s="9" t="s">
-        <v>1220</v>
       </c>
       <c r="R238" s="9" t="s">
         <v>187</v>
@@ -16008,24 +16008,24 @@
     </row>
     <row r="239" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B239" s="9" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C239" s="9" t="s">
         <v>1213</v>
-      </c>
-      <c r="C239" s="9" t="s">
-        <v>1214</v>
       </c>
       <c r="D239" s="9"/>
       <c r="E239" s="9"/>
       <c r="F239" s="9" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G239" s="9" t="s">
         <v>53</v>
       </c>
       <c r="H239" s="9" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="I239" s="9" t="s">
         <v>102</v>
@@ -16035,18 +16035,18 @@
       </c>
       <c r="K239" s="9"/>
       <c r="L239" s="10" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M239" s="10"/>
       <c r="N239" s="10"/>
       <c r="O239" s="9" t="s">
+        <v>1223</v>
+      </c>
+      <c r="P239" s="9" t="s">
         <v>1224</v>
       </c>
-      <c r="P239" s="9" t="s">
+      <c r="Q239" s="9" t="s">
         <v>1225</v>
-      </c>
-      <c r="Q239" s="9" t="s">
-        <v>1226</v>
       </c>
       <c r="R239" s="9" t="s">
         <v>187</v>
@@ -16057,13 +16057,13 @@
     </row>
     <row r="240" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C240" s="9" t="s">
         <v>1227</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>1213</v>
-      </c>
-      <c r="C240" s="9" t="s">
-        <v>1228</v>
       </c>
       <c r="D240" s="9"/>
       <c r="E240" s="9"/>
@@ -16084,7 +16084,7 @@
       </c>
       <c r="K240" s="9"/>
       <c r="L240" s="10" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="M240" s="10"/>
       <c r="N240" s="10"/>
@@ -16095,7 +16095,7 @@
         <v>715</v>
       </c>
       <c r="Q240" s="9" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="R240" s="9" t="s">
         <v>31</v>
@@ -16106,13 +16106,13 @@
     </row>
     <row r="241" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="C241" s="9" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D241" s="9"/>
       <c r="E241" s="9"/>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="K241" s="9"/>
       <c r="L241" s="10" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="M241" s="10"/>
       <c r="N241" s="10"/>
@@ -16144,7 +16144,7 @@
         <v>539</v>
       </c>
       <c r="Q241" s="9" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="R241" s="9" t="s">
         <v>31</v>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E46652-EEB4-4E62-AD7B-05E96F909C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9853AD-5CDB-4053-9B0C-0F78D57A624F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3444" uniqueCount="1362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3443" uniqueCount="1362">
   <si>
     <t>Image</t>
   </si>
@@ -1834,9 +1834,6 @@
     <t>55 cm</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a4/Courbet_LAtelier_du_peintre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1854-1855</t>
   </si>
   <si>
@@ -3016,9 +3013,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f3/Paul_C%C3%A9zanne_-_The_Buffet_-_Google_Art_Project.jpg/1280px-Paul_C%C3%A9zanne_-_The_Buffet_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>"Nature morte au Buffet (Le Buffet)"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/09/Pont_de_Maincy%2C_par_Paul_C%C3%A9zanne.jpg/1280px-Pont_de_Maincy%2C_par_Paul_C%C3%A9zanne.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -3055,9 +3049,6 @@
     <t>1888-1890</t>
   </si>
   <si>
-    <t>Zurich (Fondation E.G. Bührle, et non Orsay — à vérifier)</t>
-  </si>
-  <si>
     <t>Fondation E.G. Bührle</t>
   </si>
   <si>
@@ -4106,6 +4097,15 @@
   </si>
   <si>
     <t>"La Fileuse endormie"</t>
+  </si>
+  <si>
+    <t>"Nature morte au Buffet"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zurich </t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Courbet_LAtelier_du_peintre.jpg/1280px-Courbet_LAtelier_du_peintre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -4224,7 +4224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4251,6 +4251,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -9667,8 +9668,8 @@
       </c>
     </row>
     <row r="104" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="11" t="s">
-        <v>604</v>
+      <c r="A104" s="14" t="s">
+        <v>1361</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>562</v>
@@ -9685,7 +9686,7 @@
         <v>111</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I104" s="8" t="s">
         <v>40</v>
@@ -9695,7 +9696,7 @@
       </c>
       <c r="K104" s="8"/>
       <c r="L104" s="9" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="M104" s="9"/>
       <c r="N104" s="9"/>
@@ -9703,10 +9704,10 @@
         <v>28</v>
       </c>
       <c r="P104" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q104" s="8" t="s">
         <v>607</v>
-      </c>
-      <c r="Q104" s="8" t="s">
-        <v>608</v>
       </c>
       <c r="R104" s="8" t="s">
         <v>31</v>
@@ -9717,7 +9718,7 @@
     </row>
     <row r="105" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B105" s="8" t="s">
         <v>562</v>
@@ -9734,7 +9735,7 @@
         <v>111</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I105" s="8" t="s">
         <v>431</v>
@@ -9766,7 +9767,7 @@
     </row>
     <row r="106" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B106" s="8" t="s">
         <v>562</v>
@@ -9783,7 +9784,7 @@
         <v>111</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="I106" s="8" t="s">
         <v>431</v>
@@ -9793,7 +9794,7 @@
       </c>
       <c r="K106" s="8"/>
       <c r="L106" s="9" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M106" s="9"/>
       <c r="N106" s="9"/>
@@ -9801,7 +9802,7 @@
         <v>28</v>
       </c>
       <c r="P106" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q106" s="8" t="s">
         <v>295</v>
@@ -9815,7 +9816,7 @@
     </row>
     <row r="107" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>562</v>
@@ -9832,7 +9833,7 @@
         <v>111</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>40</v>
@@ -9842,7 +9843,7 @@
       </c>
       <c r="K107" s="2"/>
       <c r="L107" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -9850,10 +9851,10 @@
         <v>28</v>
       </c>
       <c r="P107" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="Q107" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="Q107" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="R107" s="2" t="s">
         <v>31</v>
@@ -9864,7 +9865,7 @@
     </row>
     <row r="108" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>562</v>
@@ -9884,14 +9885,14 @@
         <v>430</v>
       </c>
       <c r="I108" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="J108" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="J108" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="K108" s="2"/>
       <c r="L108" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
@@ -9899,10 +9900,10 @@
         <v>28</v>
       </c>
       <c r="P108" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="Q108" s="2" t="s">
         <v>624</v>
-      </c>
-      <c r="Q108" s="2" t="s">
-        <v>625</v>
       </c>
       <c r="R108" s="2" t="s">
         <v>31</v>
@@ -9913,7 +9914,7 @@
     </row>
     <row r="109" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>562</v>
@@ -9930,17 +9931,17 @@
         <v>111</v>
       </c>
       <c r="H109" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="I109" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>432</v>
       </c>
       <c r="K109" s="2"/>
       <c r="L109" s="4" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
@@ -9962,7 +9963,7 @@
     </row>
     <row r="110" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>562</v>
@@ -9979,17 +9980,17 @@
         <v>111</v>
       </c>
       <c r="H110" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="I110" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>579</v>
       </c>
       <c r="K110" s="2"/>
       <c r="L110" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
@@ -9997,10 +9998,10 @@
         <v>28</v>
       </c>
       <c r="P110" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="Q110" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="Q110" s="2" t="s">
-        <v>634</v>
       </c>
       <c r="R110" s="2" t="s">
         <v>31</v>
@@ -10011,7 +10012,7 @@
     </row>
     <row r="111" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>562</v>
@@ -10031,14 +10032,14 @@
         <v>279</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>579</v>
       </c>
       <c r="K111" s="2"/>
       <c r="L111" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
@@ -10046,7 +10047,7 @@
         <v>28</v>
       </c>
       <c r="P111" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="Q111" s="2" t="s">
         <v>222</v>
@@ -10060,7 +10061,7 @@
     </row>
     <row r="112" spans="1:19" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>562</v>
@@ -10087,10 +10088,10 @@
       </c>
       <c r="K112" s="2"/>
       <c r="L112" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="M112" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="M112" s="2" t="s">
-        <v>640</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2" t="s">
@@ -10100,7 +10101,7 @@
         <v>588</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="R112" s="2" t="s">
         <v>31</v>
@@ -10111,13 +10112,13 @@
     </row>
     <row r="113" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B113" s="8" t="s">
         <v>562</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
@@ -10138,18 +10139,18 @@
       </c>
       <c r="K113" s="8"/>
       <c r="L113" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="M113" s="9"/>
       <c r="N113" s="9"/>
       <c r="O113" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="P113" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="P113" s="8" t="s">
+      <c r="Q113" s="8" t="s">
         <v>646</v>
-      </c>
-      <c r="Q113" s="8" t="s">
-        <v>647</v>
       </c>
       <c r="R113" s="8" t="s">
         <v>31</v>
@@ -10160,13 +10161,13 @@
     </row>
     <row r="114" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B114" s="8" t="s">
         <v>562</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8"/>
@@ -10177,7 +10178,7 @@
         <v>350</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I114" s="8" t="s">
         <v>40</v>
@@ -10187,7 +10188,7 @@
       </c>
       <c r="K114" s="8"/>
       <c r="L114" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="M114" s="9"/>
       <c r="N114" s="9"/>
@@ -10198,7 +10199,7 @@
         <v>300</v>
       </c>
       <c r="Q114" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R114" s="8" t="s">
         <v>31</v>
@@ -10209,18 +10210,18 @@
     </row>
     <row r="115" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="B115" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="B115" s="8" t="s">
+      <c r="C115" s="8" t="s">
         <v>653</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>654</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8"/>
       <c r="F115" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G115" s="8" t="s">
         <v>54</v>
@@ -10229,14 +10230,14 @@
         <v>310</v>
       </c>
       <c r="I115" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="J115" s="8" t="s">
         <v>656</v>
-      </c>
-      <c r="J115" s="8" t="s">
-        <v>657</v>
       </c>
       <c r="K115" s="8"/>
       <c r="L115" s="9" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="M115" s="9"/>
       <c r="N115" s="9"/>
@@ -10244,10 +10245,10 @@
         <v>312</v>
       </c>
       <c r="P115" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="Q115" s="8" t="s">
         <v>659</v>
-      </c>
-      <c r="Q115" s="8" t="s">
-        <v>660</v>
       </c>
       <c r="R115" s="8" t="s">
         <v>31</v>
@@ -10258,18 +10259,18 @@
     </row>
     <row r="116" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B116" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="C116" s="8" t="s">
         <v>653</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>654</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8"/>
       <c r="F116" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G116" s="8" t="s">
         <v>54</v>
@@ -10285,7 +10286,7 @@
       </c>
       <c r="K116" s="8"/>
       <c r="L116" s="9" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="M116" s="9"/>
       <c r="N116" s="9"/>
@@ -10293,7 +10294,7 @@
         <v>323</v>
       </c>
       <c r="P116" s="8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="Q116" s="8" t="s">
         <v>48</v>
@@ -10307,18 +10308,18 @@
     </row>
     <row r="117" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B117" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="C117" s="8" t="s">
         <v>653</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>654</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G117" s="8" t="s">
         <v>54</v>
@@ -10334,7 +10335,7 @@
       </c>
       <c r="K117" s="8"/>
       <c r="L117" s="9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="M117" s="9"/>
       <c r="N117" s="9"/>
@@ -10342,10 +10343,10 @@
         <v>28</v>
       </c>
       <c r="P117" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="Q117" s="8" t="s">
         <v>666</v>
-      </c>
-      <c r="Q117" s="8" t="s">
-        <v>667</v>
       </c>
       <c r="R117" s="8" t="s">
         <v>31</v>
@@ -10356,18 +10357,18 @@
     </row>
     <row r="118" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B118" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="C118" s="8" t="s">
         <v>653</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>654</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8"/>
       <c r="F118" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G118" s="8" t="s">
         <v>54</v>
@@ -10376,19 +10377,19 @@
         <v>144</v>
       </c>
       <c r="I118" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="J118" s="8" t="s">
         <v>656</v>
-      </c>
-      <c r="J118" s="8" t="s">
-        <v>657</v>
       </c>
       <c r="K118" s="8"/>
       <c r="L118" s="9" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="M118" s="9"/>
       <c r="N118" s="9"/>
       <c r="O118" s="8" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P118" s="8" t="s">
         <v>545</v>
@@ -10405,18 +10406,18 @@
     </row>
     <row r="119" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B119" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C119" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>654</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
       <c r="F119" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>54</v>
@@ -10428,22 +10429,22 @@
         <v>40</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K119" s="2"/>
       <c r="L119" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="M119" s="3"/>
       <c r="N119" s="3"/>
       <c r="O119" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="P119" s="2" t="s">
         <v>276</v>
       </c>
       <c r="Q119" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="R119" s="2" t="s">
         <v>31</v>
@@ -10454,18 +10455,18 @@
     </row>
     <row r="120" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="B120" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="C120" s="8" t="s">
         <v>676</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>677</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8"/>
       <c r="F120" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G120" s="8" t="s">
         <v>83</v>
@@ -10481,7 +10482,7 @@
       </c>
       <c r="K120" s="8"/>
       <c r="L120" s="9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="M120" s="9"/>
       <c r="N120" s="9"/>
@@ -10489,10 +10490,10 @@
         <v>28</v>
       </c>
       <c r="P120" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="Q120" s="8" t="s">
         <v>680</v>
-      </c>
-      <c r="Q120" s="8" t="s">
-        <v>681</v>
       </c>
       <c r="R120" s="8" t="s">
         <v>31</v>
@@ -10503,24 +10504,24 @@
     </row>
     <row r="121" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B121" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="C121" s="8" t="s">
         <v>676</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>677</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8"/>
       <c r="F121" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>83</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="I121" s="8" t="s">
         <v>40</v>
@@ -10530,7 +10531,7 @@
       </c>
       <c r="K121" s="8"/>
       <c r="L121" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="M121" s="9"/>
       <c r="N121" s="9"/>
@@ -10538,7 +10539,7 @@
         <v>28</v>
       </c>
       <c r="P121" s="8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q121" s="8" t="s">
         <v>175</v>
@@ -10552,50 +10553,50 @@
     </row>
     <row r="122" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
+        <v>684</v>
+      </c>
+      <c r="B122" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="B122" s="8" t="s">
+      <c r="C122" s="8" t="s">
         <v>686</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>687</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8"/>
       <c r="F122" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="G122" s="8" t="s">
         <v>688</v>
       </c>
-      <c r="G122" s="8" t="s">
+      <c r="H122" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="H122" s="8" t="s">
+      <c r="I122" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="I122" s="8" t="s">
+      <c r="J122" s="8" t="s">
         <v>691</v>
-      </c>
-      <c r="J122" s="8" t="s">
-        <v>692</v>
       </c>
       <c r="K122" s="8"/>
       <c r="L122" s="9" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="M122" s="9"/>
       <c r="N122" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="O122" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P122" s="8" t="s">
         <v>694</v>
       </c>
-      <c r="O122" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="P122" s="8" t="s">
+      <c r="Q122" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="Q122" s="8" t="s">
+      <c r="R122" s="8" t="s">
         <v>696</v>
-      </c>
-      <c r="R122" s="8" t="s">
-        <v>697</v>
       </c>
       <c r="S122" s="8">
         <v>3</v>
@@ -10603,50 +10604,50 @@
     </row>
     <row r="123" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B123" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="C123" s="8" t="s">
         <v>686</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>687</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8"/>
       <c r="F123" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="G123" s="8" t="s">
         <v>688</v>
       </c>
-      <c r="G123" s="8" t="s">
-        <v>689</v>
-      </c>
       <c r="H123" s="8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="I123" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="J123" s="8" t="s">
         <v>691</v>
-      </c>
-      <c r="J123" s="8" t="s">
-        <v>692</v>
       </c>
       <c r="K123" s="8"/>
       <c r="L123" s="9" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M123" s="9"/>
       <c r="N123" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="O123" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P123" s="8" t="s">
         <v>701</v>
       </c>
-      <c r="O123" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="P123" s="8" t="s">
+      <c r="Q123" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="Q123" s="8" t="s">
-        <v>703</v>
-      </c>
       <c r="R123" s="8" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="S123" s="8">
         <v>3</v>
@@ -10654,21 +10655,21 @@
     </row>
     <row r="124" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="B124" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="B124" s="8" t="s">
+      <c r="C124" s="8" t="s">
         <v>705</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>706</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8"/>
       <c r="F124" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="G124" s="8" t="s">
         <v>707</v>
-      </c>
-      <c r="G124" s="8" t="s">
-        <v>708</v>
       </c>
       <c r="H124" s="8" t="s">
         <v>22</v>
@@ -10681,7 +10682,7 @@
       </c>
       <c r="K124" s="8"/>
       <c r="L124" s="9" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="M124" s="9"/>
       <c r="N124" s="9"/>
@@ -10689,10 +10690,10 @@
         <v>28</v>
       </c>
       <c r="P124" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="Q124" s="8" t="s">
         <v>710</v>
-      </c>
-      <c r="Q124" s="8" t="s">
-        <v>711</v>
       </c>
       <c r="R124" s="8" t="s">
         <v>191</v>
@@ -10703,21 +10704,21 @@
     </row>
     <row r="125" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B125" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="C125" s="8" t="s">
         <v>705</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>706</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
       <c r="F125" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="G125" s="8" t="s">
         <v>707</v>
-      </c>
-      <c r="G125" s="8" t="s">
-        <v>708</v>
       </c>
       <c r="H125" s="8" t="s">
         <v>597</v>
@@ -10730,7 +10731,7 @@
       </c>
       <c r="K125" s="8"/>
       <c r="L125" s="9" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="M125" s="9"/>
       <c r="N125" s="9"/>
@@ -10741,7 +10742,7 @@
         <v>338</v>
       </c>
       <c r="Q125" s="8" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="R125" s="8" t="s">
         <v>191</v>
@@ -10752,24 +10753,24 @@
     </row>
     <row r="126" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B126" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="C126" s="8" t="s">
         <v>705</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>706</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
       <c r="F126" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="G126" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="G126" s="8" t="s">
-        <v>708</v>
-      </c>
       <c r="H126" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I126" s="8" t="s">
         <v>102</v>
@@ -10779,7 +10780,7 @@
       </c>
       <c r="K126" s="8"/>
       <c r="L126" s="9" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="M126" s="9"/>
       <c r="N126" s="9"/>
@@ -10787,10 +10788,10 @@
         <v>28</v>
       </c>
       <c r="P126" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="Q126" s="8" t="s">
         <v>718</v>
-      </c>
-      <c r="Q126" s="8" t="s">
-        <v>719</v>
       </c>
       <c r="R126" s="8" t="s">
         <v>191</v>
@@ -10801,21 +10802,21 @@
     </row>
     <row r="127" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B127" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="C127" s="8" t="s">
         <v>705</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>706</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
       <c r="F127" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="G127" s="8" t="s">
         <v>707</v>
-      </c>
-      <c r="G127" s="8" t="s">
-        <v>708</v>
       </c>
       <c r="H127" s="8" t="s">
         <v>53</v>
@@ -10828,7 +10829,7 @@
       </c>
       <c r="K127" s="8"/>
       <c r="L127" s="9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="M127" s="9"/>
       <c r="N127" s="9"/>
@@ -10836,10 +10837,10 @@
         <v>28</v>
       </c>
       <c r="P127" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="Q127" s="8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="R127" s="8" t="s">
         <v>191</v>
@@ -10850,21 +10851,21 @@
     </row>
     <row r="128" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B128" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
       <c r="F128" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="G128" s="8" t="s">
         <v>707</v>
-      </c>
-      <c r="G128" s="8" t="s">
-        <v>708</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>22</v>
@@ -10877,7 +10878,7 @@
       </c>
       <c r="K128" s="2"/>
       <c r="L128" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="M128" s="3"/>
       <c r="N128" s="3"/>
@@ -10885,13 +10886,13 @@
         <v>28</v>
       </c>
       <c r="P128" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="Q128" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="Q128" s="2" t="s">
-        <v>711</v>
-      </c>
       <c r="R128" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="S128" s="2">
         <v>2</v>
@@ -10899,34 +10900,34 @@
     </row>
     <row r="129" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
       <c r="F129" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="G129" s="8" t="s">
         <v>707</v>
-      </c>
-      <c r="G129" s="8" t="s">
-        <v>708</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>127</v>
       </c>
       <c r="I129" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="J129" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="J129" s="2" t="s">
-        <v>727</v>
       </c>
       <c r="K129" s="2"/>
       <c r="L129" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="M129" s="3"/>
       <c r="N129" s="3"/>
@@ -10937,10 +10938,10 @@
         <v>338</v>
       </c>
       <c r="Q129" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R129" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="S129" s="2">
         <v>2</v>
@@ -10948,24 +10949,24 @@
     </row>
     <row r="130" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="B130" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="B130" s="8" t="s">
+      <c r="C130" s="8" t="s">
         <v>731</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>732</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
       <c r="F130" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G130" s="8" t="s">
         <v>549</v>
       </c>
       <c r="H130" s="8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="I130" s="8" t="s">
         <v>40</v>
@@ -10975,7 +10976,7 @@
       </c>
       <c r="K130" s="8"/>
       <c r="L130" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="M130" s="9"/>
       <c r="N130" s="9"/>
@@ -10983,10 +10984,10 @@
         <v>28</v>
       </c>
       <c r="P130" s="8" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="Q130" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="R130" s="8" t="s">
         <v>31</v>
@@ -10997,34 +10998,32 @@
     </row>
     <row r="131" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B131" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="C131" s="8" t="s">
         <v>731</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>732</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8"/>
       <c r="F131" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G131" s="8" t="s">
         <v>549</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>738</v>
-      </c>
-      <c r="I131" s="8" t="s">
-        <v>418</v>
-      </c>
+        <v>737</v>
+      </c>
+      <c r="I131" s="8"/>
       <c r="J131" s="8" t="s">
         <v>419</v>
       </c>
       <c r="K131" s="8"/>
       <c r="L131" s="9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="M131" s="9"/>
       <c r="N131" s="9"/>
@@ -11032,10 +11031,10 @@
         <v>28</v>
       </c>
       <c r="P131" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="Q131" s="8" t="s">
         <v>740</v>
-      </c>
-      <c r="Q131" s="8" t="s">
-        <v>741</v>
       </c>
       <c r="R131" s="8" t="s">
         <v>31</v>
@@ -11046,24 +11045,24 @@
     </row>
     <row r="132" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B132" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="C132" s="8" t="s">
         <v>731</v>
-      </c>
-      <c r="C132" s="8" t="s">
-        <v>732</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
       <c r="F132" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G132" s="8" t="s">
         <v>549</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="I132" s="8" t="s">
         <v>40</v>
@@ -11073,7 +11072,7 @@
       </c>
       <c r="K132" s="8"/>
       <c r="L132" s="9" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M132" s="9"/>
       <c r="N132" s="9"/>
@@ -11081,10 +11080,10 @@
         <v>28</v>
       </c>
       <c r="P132" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="Q132" s="8" t="s">
         <v>745</v>
-      </c>
-      <c r="Q132" s="8" t="s">
-        <v>746</v>
       </c>
       <c r="R132" s="8" t="s">
         <v>31</v>
@@ -11095,18 +11094,18 @@
     </row>
     <row r="133" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B133" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="C133" s="8" t="s">
         <v>731</v>
-      </c>
-      <c r="C133" s="8" t="s">
-        <v>732</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8"/>
       <c r="F133" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G133" s="8" t="s">
         <v>549</v>
@@ -11115,14 +11114,14 @@
         <v>374</v>
       </c>
       <c r="I133" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="J133" s="8" t="s">
         <v>748</v>
-      </c>
-      <c r="J133" s="8" t="s">
-        <v>749</v>
       </c>
       <c r="K133" s="8"/>
       <c r="L133" s="9" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="M133" s="9"/>
       <c r="N133" s="9"/>
@@ -11130,10 +11129,10 @@
         <v>28</v>
       </c>
       <c r="P133" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q133" s="8" t="s">
         <v>751</v>
-      </c>
-      <c r="Q133" s="8" t="s">
-        <v>752</v>
       </c>
       <c r="R133" s="8" t="s">
         <v>31</v>
@@ -11144,18 +11143,18 @@
     </row>
     <row r="134" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="13" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B134" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="C134" s="8" t="s">
         <v>731</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>732</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8"/>
       <c r="F134" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G134" s="8" t="s">
         <v>549</v>
@@ -11171,11 +11170,11 @@
       </c>
       <c r="K134" s="8"/>
       <c r="L134" s="9" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="M134" s="9"/>
       <c r="N134" s="9" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="O134" s="8" t="s">
         <v>28</v>
@@ -11195,21 +11194,21 @@
     </row>
     <row r="135" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
+        <v>754</v>
+      </c>
+      <c r="B135" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="B135" s="8" t="s">
+      <c r="C135" s="8" t="s">
         <v>756</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>757</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8"/>
       <c r="F135" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="G135" s="8" t="s">
         <v>758</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>759</v>
       </c>
       <c r="H135" s="8" t="s">
         <v>364</v>
@@ -11218,11 +11217,11 @@
         <v>569</v>
       </c>
       <c r="J135" s="8" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="K135" s="8"/>
       <c r="L135" s="9" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="M135" s="9"/>
       <c r="N135" s="9"/>
@@ -11230,13 +11229,13 @@
         <v>28</v>
       </c>
       <c r="P135" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q135" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="Q135" s="8" t="s">
+      <c r="R135" s="8" t="s">
         <v>763</v>
-      </c>
-      <c r="R135" s="8" t="s">
-        <v>764</v>
       </c>
       <c r="S135" s="8">
         <v>3</v>
@@ -11244,34 +11243,34 @@
     </row>
     <row r="136" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B136" s="8" t="s">
+        <v>755</v>
+      </c>
+      <c r="C136" s="8" t="s">
         <v>756</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>757</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8"/>
       <c r="F136" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="G136" s="8" t="s">
         <v>758</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>759</v>
       </c>
       <c r="H136" s="8" t="s">
         <v>39</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J136" s="8" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="K136" s="8"/>
       <c r="L136" s="9" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="M136" s="9"/>
       <c r="N136" s="9"/>
@@ -11279,13 +11278,13 @@
         <v>28</v>
       </c>
       <c r="P136" s="8" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="Q136" s="8" t="s">
         <v>305</v>
       </c>
       <c r="R136" s="8" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="S136" s="8">
         <v>3</v>
@@ -11293,13 +11292,13 @@
     </row>
     <row r="137" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="B137" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="B137" s="8" t="s">
+      <c r="C137" s="8" t="s">
         <v>770</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>771</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8"/>
@@ -11310,7 +11309,7 @@
         <v>100</v>
       </c>
       <c r="H137" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="I137" s="8" t="s">
         <v>40</v>
@@ -11320,7 +11319,7 @@
       </c>
       <c r="K137" s="8"/>
       <c r="L137" s="9" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="M137" s="9"/>
       <c r="N137" s="9"/>
@@ -11328,10 +11327,10 @@
         <v>28</v>
       </c>
       <c r="P137" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="Q137" s="8" t="s">
         <v>774</v>
-      </c>
-      <c r="Q137" s="8" t="s">
-        <v>775</v>
       </c>
       <c r="R137" s="8" t="s">
         <v>503</v>
@@ -11342,13 +11341,13 @@
     </row>
     <row r="138" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B138" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="C138" s="8" t="s">
         <v>770</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>771</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8"/>
@@ -11359,17 +11358,17 @@
         <v>100</v>
       </c>
       <c r="H138" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="I138" s="8" t="s">
         <v>777</v>
       </c>
-      <c r="I138" s="8" t="s">
+      <c r="J138" s="8" t="s">
         <v>778</v>
-      </c>
-      <c r="J138" s="8" t="s">
-        <v>779</v>
       </c>
       <c r="K138" s="8"/>
       <c r="L138" s="9" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="M138" s="9"/>
       <c r="N138" s="9"/>
@@ -11377,10 +11376,10 @@
         <v>28</v>
       </c>
       <c r="P138" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="Q138" s="8" t="s">
         <v>781</v>
-      </c>
-      <c r="Q138" s="8" t="s">
-        <v>782</v>
       </c>
       <c r="R138" s="8" t="s">
         <v>503</v>
@@ -11391,18 +11390,18 @@
     </row>
     <row r="139" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
+        <v>782</v>
+      </c>
+      <c r="B139" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="B139" s="8" t="s">
+      <c r="C139" s="8" t="s">
         <v>784</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>785</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
       <c r="F139" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G139" s="8" t="s">
         <v>163</v>
@@ -11418,7 +11417,7 @@
       </c>
       <c r="K139" s="8"/>
       <c r="L139" s="9" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="M139" s="9"/>
       <c r="N139" s="9"/>
@@ -11426,7 +11425,7 @@
         <v>28</v>
       </c>
       <c r="P139" s="8" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="Q139" s="8" t="s">
         <v>493</v>
@@ -11440,18 +11439,18 @@
     </row>
     <row r="140" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B140" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="C140" s="8" t="s">
         <v>784</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>785</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8"/>
       <c r="F140" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G140" s="8" t="s">
         <v>163</v>
@@ -11467,7 +11466,7 @@
       </c>
       <c r="K140" s="8"/>
       <c r="L140" s="9" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M140" s="9"/>
       <c r="N140" s="9"/>
@@ -11478,7 +11477,7 @@
         <v>338</v>
       </c>
       <c r="Q140" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="R140" s="8" t="s">
         <v>31</v>
@@ -11489,34 +11488,34 @@
     </row>
     <row r="141" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B141" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="C141" s="8" t="s">
         <v>784</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>785</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
       <c r="F141" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G141" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="I141" s="8" t="s">
         <v>40</v>
       </c>
       <c r="J141" s="8" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="K141" s="8"/>
       <c r="L141" s="9" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="M141" s="9"/>
       <c r="N141" s="9"/>
@@ -11538,24 +11537,24 @@
     </row>
     <row r="142" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B142" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="C142" s="8" t="s">
         <v>784</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>785</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8"/>
       <c r="F142" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="I142" s="8" t="s">
         <v>40</v>
@@ -11565,18 +11564,18 @@
       </c>
       <c r="K142" s="8"/>
       <c r="L142" s="9" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="M142" s="9"/>
       <c r="N142" s="9"/>
       <c r="O142" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="P142" s="8" t="s">
         <v>799</v>
       </c>
-      <c r="P142" s="8" t="s">
-        <v>800</v>
-      </c>
       <c r="Q142" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="R142" s="8" t="s">
         <v>31</v>
@@ -11587,34 +11586,34 @@
     </row>
     <row r="143" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B143" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="C143" s="8" t="s">
         <v>784</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>785</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8"/>
       <c r="F143" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G143" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H143" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="I143" s="8" t="s">
         <v>33</v>
       </c>
       <c r="J143" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="K143" s="8"/>
       <c r="L143" s="9" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="M143" s="9"/>
       <c r="N143" s="9"/>
@@ -11622,7 +11621,7 @@
         <v>28</v>
       </c>
       <c r="P143" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="Q143" s="8" t="s">
         <v>211</v>
@@ -11636,18 +11635,18 @@
     </row>
     <row r="144" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
+        <v>805</v>
+      </c>
+      <c r="B144" s="8" t="s">
         <v>806</v>
       </c>
-      <c r="B144" s="8" t="s">
+      <c r="C144" s="8" t="s">
         <v>807</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>808</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8"/>
       <c r="F144" s="8" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G144" s="8" t="s">
         <v>46</v>
@@ -11663,7 +11662,7 @@
       </c>
       <c r="K144" s="8"/>
       <c r="L144" s="9" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="M144" s="9"/>
       <c r="N144" s="9"/>
@@ -11671,10 +11670,10 @@
         <v>28</v>
       </c>
       <c r="P144" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q144" s="8" t="s">
         <v>811</v>
-      </c>
-      <c r="Q144" s="8" t="s">
-        <v>812</v>
       </c>
       <c r="R144" s="8" t="s">
         <v>31</v>
@@ -11685,18 +11684,18 @@
     </row>
     <row r="145" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B145" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="C145" s="8" t="s">
         <v>807</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>808</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
       <c r="F145" s="8" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G145" s="8" t="s">
         <v>46</v>
@@ -11712,7 +11711,7 @@
       </c>
       <c r="K145" s="8"/>
       <c r="L145" s="9" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="M145" s="9"/>
       <c r="N145" s="9"/>
@@ -11720,7 +11719,7 @@
         <v>28</v>
       </c>
       <c r="P145" s="8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="Q145" s="8" t="s">
         <v>493</v>
@@ -11734,18 +11733,18 @@
     </row>
     <row r="146" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B146" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="C146" s="8" t="s">
         <v>807</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>808</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8"/>
       <c r="F146" s="8" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G146" s="8" t="s">
         <v>46</v>
@@ -11761,7 +11760,7 @@
       </c>
       <c r="K146" s="8"/>
       <c r="L146" s="9" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="M146" s="9"/>
       <c r="N146" s="9"/>
@@ -11769,10 +11768,10 @@
         <v>28</v>
       </c>
       <c r="P146" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q146" s="8" t="s">
         <v>818</v>
-      </c>
-      <c r="Q146" s="8" t="s">
-        <v>819</v>
       </c>
       <c r="R146" s="8" t="s">
         <v>31</v>
@@ -11783,24 +11782,24 @@
     </row>
     <row r="147" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B147" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="C147" s="8" t="s">
         <v>807</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>808</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8"/>
       <c r="F147" s="8" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>46</v>
       </c>
       <c r="H147" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="I147" s="8" t="s">
         <v>40</v>
@@ -11810,7 +11809,7 @@
       </c>
       <c r="K147" s="8"/>
       <c r="L147" s="9" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="M147" s="9"/>
       <c r="N147" s="9"/>
@@ -11832,24 +11831,24 @@
     </row>
     <row r="148" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B148" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="C148" s="8" t="s">
         <v>807</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>808</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8"/>
       <c r="F148" s="8" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G148" s="8" t="s">
         <v>46</v>
       </c>
       <c r="H148" s="8" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I148" s="8" t="s">
         <v>40</v>
@@ -11859,7 +11858,7 @@
       </c>
       <c r="K148" s="8"/>
       <c r="L148" s="9" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="M148" s="9"/>
       <c r="N148" s="9"/>
@@ -11870,7 +11869,7 @@
         <v>282</v>
       </c>
       <c r="Q148" s="8" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="R148" s="8" t="s">
         <v>31</v>
@@ -11881,13 +11880,13 @@
     </row>
     <row r="149" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
+        <v>825</v>
+      </c>
+      <c r="B149" s="8" t="s">
         <v>826</v>
       </c>
-      <c r="B149" s="8" t="s">
+      <c r="C149" s="8" t="s">
         <v>827</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>828</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8"/>
@@ -11898,7 +11897,7 @@
         <v>46</v>
       </c>
       <c r="H149" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="I149" s="8" t="s">
         <v>40</v>
@@ -11908,7 +11907,7 @@
       </c>
       <c r="K149" s="8"/>
       <c r="L149" s="9" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="M149" s="9"/>
       <c r="N149" s="9"/>
@@ -11916,7 +11915,7 @@
         <v>28</v>
       </c>
       <c r="P149" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="Q149" s="8" t="s">
         <v>66</v>
@@ -11930,13 +11929,13 @@
     </row>
     <row r="150" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B150" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="C150" s="8" t="s">
         <v>827</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>828</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
@@ -11947,7 +11946,7 @@
         <v>46</v>
       </c>
       <c r="H150" s="8" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="I150" s="8" t="s">
         <v>40</v>
@@ -11957,7 +11956,7 @@
       </c>
       <c r="K150" s="8"/>
       <c r="L150" s="9" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="M150" s="9"/>
       <c r="N150" s="9"/>
@@ -11965,10 +11964,10 @@
         <v>28</v>
       </c>
       <c r="P150" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q150" s="8" t="s">
         <v>835</v>
-      </c>
-      <c r="Q150" s="8" t="s">
-        <v>836</v>
       </c>
       <c r="R150" s="8" t="s">
         <v>31</v>
@@ -11979,13 +11978,13 @@
     </row>
     <row r="151" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="12" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B151" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="C151" s="8" t="s">
         <v>827</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>828</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8"/>
@@ -11999,14 +11998,14 @@
         <v>1850</v>
       </c>
       <c r="I151" s="8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="K151" s="8"/>
       <c r="L151" s="9" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="M151" s="9"/>
       <c r="N151" s="9"/>
@@ -12014,10 +12013,10 @@
         <v>28</v>
       </c>
       <c r="P151" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q151" s="8" t="s">
         <v>840</v>
-      </c>
-      <c r="Q151" s="8" t="s">
-        <v>841</v>
       </c>
       <c r="R151" s="8" t="s">
         <v>31</v>
@@ -12028,13 +12027,13 @@
     </row>
     <row r="152" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B152" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="C152" s="8" t="s">
         <v>827</v>
-      </c>
-      <c r="C152" s="8" t="s">
-        <v>828</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8"/>
@@ -12055,7 +12054,7 @@
       </c>
       <c r="K152" s="8"/>
       <c r="L152" s="9" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="M152" s="9"/>
       <c r="N152" s="9"/>
@@ -12077,13 +12076,13 @@
     </row>
     <row r="153" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B153" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="C153" s="8" t="s">
         <v>827</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>828</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8"/>
@@ -12094,7 +12093,7 @@
         <v>46</v>
       </c>
       <c r="H153" s="8" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="I153" s="8" t="s">
         <v>40</v>
@@ -12104,7 +12103,7 @@
       </c>
       <c r="K153" s="8"/>
       <c r="L153" s="9" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="M153" s="9"/>
       <c r="N153" s="9"/>
@@ -12126,34 +12125,34 @@
     </row>
     <row r="154" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="B154" s="8" t="s">
         <v>847</v>
       </c>
-      <c r="B154" s="8" t="s">
+      <c r="C154" s="8" t="s">
         <v>848</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>849</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8"/>
       <c r="F154" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="G154" s="8" t="s">
         <v>850</v>
       </c>
-      <c r="G154" s="8" t="s">
-        <v>851</v>
-      </c>
       <c r="H154" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="I154" s="8" t="s">
         <v>40</v>
       </c>
       <c r="J154" s="8" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K154" s="8"/>
       <c r="L154" s="9" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="M154" s="9"/>
       <c r="N154" s="9"/>
@@ -12175,24 +12174,24 @@
     </row>
     <row r="155" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="C155" s="10" t="s">
         <v>848</v>
-      </c>
-      <c r="C155" s="10" t="s">
-        <v>849</v>
       </c>
       <c r="D155" s="10"/>
       <c r="E155" s="10"/>
       <c r="F155" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="G155" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="G155" s="2" t="s">
-        <v>851</v>
-      </c>
       <c r="H155" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I155" s="2" t="s">
         <v>40</v>
@@ -12202,7 +12201,7 @@
       </c>
       <c r="K155" s="10"/>
       <c r="L155" s="4" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="M155" s="4"/>
       <c r="N155" s="4"/>
@@ -12224,13 +12223,13 @@
     </row>
     <row r="156" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="B156" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="B156" s="8" t="s">
+      <c r="C156" s="8" t="s">
         <v>858</v>
-      </c>
-      <c r="C156" s="8" t="s">
-        <v>859</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8"/>
@@ -12238,10 +12237,10 @@
         <v>374</v>
       </c>
       <c r="G156" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="H156" s="8" t="s">
         <v>860</v>
-      </c>
-      <c r="H156" s="8" t="s">
-        <v>861</v>
       </c>
       <c r="I156" s="8" t="s">
         <v>40</v>
@@ -12251,7 +12250,7 @@
       </c>
       <c r="K156" s="8"/>
       <c r="L156" s="9" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="M156" s="9"/>
       <c r="N156" s="9"/>
@@ -12259,10 +12258,10 @@
         <v>28</v>
       </c>
       <c r="P156" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="Q156" s="8" t="s">
         <v>863</v>
-      </c>
-      <c r="Q156" s="8" t="s">
-        <v>864</v>
       </c>
       <c r="R156" s="8" t="s">
         <v>31</v>
@@ -12273,13 +12272,13 @@
     </row>
     <row r="157" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B157" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="C157" s="8" t="s">
         <v>858</v>
-      </c>
-      <c r="C157" s="8" t="s">
-        <v>859</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8"/>
@@ -12287,7 +12286,7 @@
         <v>374</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H157" s="8" t="s">
         <v>437</v>
@@ -12300,7 +12299,7 @@
       </c>
       <c r="K157" s="8"/>
       <c r="L157" s="9" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="M157" s="9"/>
       <c r="N157" s="9"/>
@@ -12311,7 +12310,7 @@
         <v>287</v>
       </c>
       <c r="Q157" s="8" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="R157" s="8" t="s">
         <v>31</v>
@@ -12322,13 +12321,13 @@
     </row>
     <row r="158" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="B158" s="8" t="s">
         <v>868</v>
       </c>
-      <c r="B158" s="8" t="s">
+      <c r="C158" s="8" t="s">
         <v>869</v>
-      </c>
-      <c r="C158" s="8" t="s">
-        <v>870</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8"/>
@@ -12339,7 +12338,7 @@
         <v>153</v>
       </c>
       <c r="H158" s="8" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I158" s="8" t="s">
         <v>33</v>
@@ -12349,7 +12348,7 @@
       </c>
       <c r="K158" s="8"/>
       <c r="L158" s="9" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="M158" s="9"/>
       <c r="N158" s="9"/>
@@ -12363,7 +12362,7 @@
         <v>74</v>
       </c>
       <c r="R158" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S158" s="8">
         <v>3</v>
@@ -12371,13 +12370,13 @@
     </row>
     <row r="159" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B159" s="8" t="s">
+        <v>868</v>
+      </c>
+      <c r="C159" s="8" t="s">
         <v>869</v>
-      </c>
-      <c r="C159" s="8" t="s">
-        <v>870</v>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8"/>
@@ -12388,7 +12387,7 @@
         <v>153</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="I159" s="8" t="s">
         <v>40</v>
@@ -12398,7 +12397,7 @@
       </c>
       <c r="K159" s="8"/>
       <c r="L159" s="9" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="M159" s="9"/>
       <c r="N159" s="9"/>
@@ -12412,7 +12411,7 @@
         <v>74</v>
       </c>
       <c r="R159" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S159" s="8">
         <v>2</v>
@@ -12420,24 +12419,24 @@
     </row>
     <row r="160" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
+        <v>875</v>
+      </c>
+      <c r="B160" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="B160" s="8" t="s">
+      <c r="C160" s="8" t="s">
         <v>877</v>
-      </c>
-      <c r="C160" s="8" t="s">
-        <v>878</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8"/>
       <c r="F160" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G160" s="8" t="s">
         <v>385</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="I160" s="8" t="s">
         <v>102</v>
@@ -12447,7 +12446,7 @@
       </c>
       <c r="K160" s="8"/>
       <c r="L160" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="M160" s="9"/>
       <c r="N160" s="9"/>
@@ -12455,10 +12454,10 @@
         <v>28</v>
       </c>
       <c r="P160" s="8" t="s">
+        <v>881</v>
+      </c>
+      <c r="Q160" s="8" t="s">
         <v>882</v>
-      </c>
-      <c r="Q160" s="8" t="s">
-        <v>883</v>
       </c>
       <c r="R160" s="8" t="s">
         <v>191</v>
@@ -12469,34 +12468,34 @@
     </row>
     <row r="161" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B161" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="C161" s="8" t="s">
         <v>877</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>878</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8"/>
       <c r="F161" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G161" s="8" t="s">
         <v>385</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I161" s="8" t="s">
         <v>102</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="K161" s="8"/>
       <c r="L161" s="9" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="M161" s="9"/>
       <c r="N161" s="9"/>
@@ -12504,10 +12503,10 @@
         <v>28</v>
       </c>
       <c r="P161" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="Q161" s="8" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="R161" s="8" t="s">
         <v>191</v>
@@ -12518,24 +12517,24 @@
     </row>
     <row r="162" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="11" t="s">
+        <v>887</v>
+      </c>
+      <c r="B162" s="8" t="s">
         <v>888</v>
       </c>
-      <c r="B162" s="8" t="s">
+      <c r="C162" s="8" t="s">
         <v>889</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>890</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8"/>
       <c r="F162" s="8" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G162" s="8" t="s">
+        <v>890</v>
+      </c>
+      <c r="H162" s="8" t="s">
         <v>891</v>
-      </c>
-      <c r="H162" s="8" t="s">
-        <v>892</v>
       </c>
       <c r="I162" s="8" t="s">
         <v>102</v>
@@ -12545,7 +12544,7 @@
       </c>
       <c r="K162" s="8"/>
       <c r="L162" s="9" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="M162" s="9"/>
       <c r="N162" s="9"/>
@@ -12556,7 +12555,7 @@
         <v>196</v>
       </c>
       <c r="Q162" s="8" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="R162" s="8" t="s">
         <v>191</v>
@@ -12567,21 +12566,21 @@
     </row>
     <row r="163" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B163" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="C163" s="8" t="s">
         <v>889</v>
-      </c>
-      <c r="C163" s="8" t="s">
-        <v>890</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8"/>
       <c r="F163" s="8" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H163" s="8" t="s">
         <v>592</v>
@@ -12594,7 +12593,7 @@
       </c>
       <c r="K163" s="8"/>
       <c r="L163" s="9" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="M163" s="9"/>
       <c r="N163" s="9"/>
@@ -12602,10 +12601,10 @@
         <v>28</v>
       </c>
       <c r="P163" s="8" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q163" s="8" t="s">
         <v>897</v>
-      </c>
-      <c r="Q163" s="8" t="s">
-        <v>898</v>
       </c>
       <c r="R163" s="8" t="s">
         <v>191</v>
@@ -12616,24 +12615,24 @@
     </row>
     <row r="164" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="B164" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="B164" s="8" t="s">
+      <c r="C164" s="8" t="s">
         <v>900</v>
-      </c>
-      <c r="C164" s="8" t="s">
-        <v>901</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8"/>
       <c r="F164" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="G164" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="G164" s="8" t="s">
+      <c r="H164" s="8" t="s">
         <v>903</v>
-      </c>
-      <c r="H164" s="8" t="s">
-        <v>904</v>
       </c>
       <c r="I164" s="8" t="s">
         <v>33</v>
@@ -12643,7 +12642,7 @@
       </c>
       <c r="K164" s="8"/>
       <c r="L164" s="9" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="M164" s="9"/>
       <c r="N164" s="9"/>
@@ -12651,10 +12650,10 @@
         <v>28</v>
       </c>
       <c r="P164" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="Q164" s="8" t="s">
         <v>906</v>
-      </c>
-      <c r="Q164" s="8" t="s">
-        <v>907</v>
       </c>
       <c r="R164" s="8" t="s">
         <v>503</v>
@@ -12665,24 +12664,24 @@
     </row>
     <row r="165" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B165" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="C165" s="8" t="s">
         <v>900</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>901</v>
       </c>
       <c r="D165" s="8"/>
       <c r="E165" s="8"/>
       <c r="F165" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="G165" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="G165" s="8" t="s">
-        <v>903</v>
-      </c>
       <c r="H165" s="8" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I165" s="8" t="s">
         <v>102</v>
@@ -12692,7 +12691,7 @@
       </c>
       <c r="K165" s="8"/>
       <c r="L165" s="9" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="M165" s="9"/>
       <c r="N165" s="9"/>
@@ -12700,10 +12699,10 @@
         <v>28</v>
       </c>
       <c r="P165" s="8" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="Q165" s="8" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="R165" s="8" t="s">
         <v>503</v>
@@ -12714,13 +12713,13 @@
     </row>
     <row r="166" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
+        <v>910</v>
+      </c>
+      <c r="B166" s="8" t="s">
         <v>911</v>
       </c>
-      <c r="B166" s="8" t="s">
+      <c r="C166" s="8" t="s">
         <v>912</v>
-      </c>
-      <c r="C166" s="8" t="s">
-        <v>913</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="8"/>
@@ -12741,7 +12740,7 @@
       </c>
       <c r="K166" s="8"/>
       <c r="L166" s="9" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="M166" s="9"/>
       <c r="N166" s="9"/>
@@ -12749,7 +12748,7 @@
         <v>28</v>
       </c>
       <c r="P166" s="8" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="Q166" s="8" t="s">
         <v>222</v>
@@ -12763,13 +12762,13 @@
     </row>
     <row r="167" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B167" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="C167" s="8" t="s">
         <v>912</v>
-      </c>
-      <c r="C167" s="8" t="s">
-        <v>913</v>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="8"/>
@@ -12783,14 +12782,14 @@
         <v>72</v>
       </c>
       <c r="I167" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="J167" s="8" t="s">
         <v>917</v>
-      </c>
-      <c r="J167" s="8" t="s">
-        <v>918</v>
       </c>
       <c r="K167" s="8"/>
       <c r="L167" s="9" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="M167" s="9"/>
       <c r="N167" s="9"/>
@@ -12798,10 +12797,10 @@
         <v>28</v>
       </c>
       <c r="P167" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="Q167" s="8" t="s">
         <v>920</v>
-      </c>
-      <c r="Q167" s="8" t="s">
-        <v>921</v>
       </c>
       <c r="R167" s="8" t="s">
         <v>191</v>
@@ -12812,18 +12811,18 @@
     </row>
     <row r="168" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
+        <v>921</v>
+      </c>
+      <c r="B168" s="8" t="s">
         <v>922</v>
       </c>
-      <c r="B168" s="8" t="s">
+      <c r="C168" s="8" t="s">
         <v>923</v>
-      </c>
-      <c r="C168" s="8" t="s">
-        <v>924</v>
       </c>
       <c r="D168" s="8"/>
       <c r="E168" s="8"/>
       <c r="F168" s="8" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G168" s="8" t="s">
         <v>143</v>
@@ -12839,7 +12838,7 @@
       </c>
       <c r="K168" s="8"/>
       <c r="L168" s="9" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="M168" s="9"/>
       <c r="N168" s="9"/>
@@ -12847,10 +12846,10 @@
         <v>28</v>
       </c>
       <c r="P168" s="8" t="s">
+        <v>925</v>
+      </c>
+      <c r="Q168" s="8" t="s">
         <v>926</v>
-      </c>
-      <c r="Q168" s="8" t="s">
-        <v>927</v>
       </c>
       <c r="R168" s="8" t="s">
         <v>503</v>
@@ -12861,18 +12860,18 @@
     </row>
     <row r="169" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B169" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="C169" s="8" t="s">
         <v>923</v>
-      </c>
-      <c r="C169" s="8" t="s">
-        <v>924</v>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
       <c r="F169" s="8" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>143</v>
@@ -12881,14 +12880,14 @@
         <v>181</v>
       </c>
       <c r="I169" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="J169" s="8" t="s">
         <v>778</v>
-      </c>
-      <c r="J169" s="8" t="s">
-        <v>779</v>
       </c>
       <c r="K169" s="8"/>
       <c r="L169" s="9" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="M169" s="9"/>
       <c r="N169" s="9"/>
@@ -12896,10 +12895,10 @@
         <v>28</v>
       </c>
       <c r="P169" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="Q169" s="8" t="s">
         <v>930</v>
-      </c>
-      <c r="Q169" s="8" t="s">
-        <v>931</v>
       </c>
       <c r="R169" s="8" t="s">
         <v>503</v>
@@ -12910,13 +12909,13 @@
     </row>
     <row r="170" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
+        <v>931</v>
+      </c>
+      <c r="B170" s="8" t="s">
         <v>932</v>
       </c>
-      <c r="B170" s="8" t="s">
+      <c r="C170" s="8" t="s">
         <v>933</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>934</v>
       </c>
       <c r="D170" s="8"/>
       <c r="E170" s="8"/>
@@ -12924,7 +12923,7 @@
         <v>513</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H170" s="8" t="s">
         <v>62</v>
@@ -12937,7 +12936,7 @@
       </c>
       <c r="K170" s="8"/>
       <c r="L170" s="9" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="M170" s="9"/>
       <c r="N170" s="9"/>
@@ -12945,10 +12944,10 @@
         <v>28</v>
       </c>
       <c r="P170" s="8" t="s">
+        <v>936</v>
+      </c>
+      <c r="Q170" s="8" t="s">
         <v>937</v>
-      </c>
-      <c r="Q170" s="8" t="s">
-        <v>938</v>
       </c>
       <c r="R170" s="8" t="s">
         <v>31</v>
@@ -12959,13 +12958,13 @@
     </row>
     <row r="171" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="11" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B171" s="8" t="s">
+        <v>932</v>
+      </c>
+      <c r="C171" s="8" t="s">
         <v>933</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>934</v>
       </c>
       <c r="D171" s="8"/>
       <c r="E171" s="8"/>
@@ -12973,20 +12972,20 @@
         <v>513</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H171" s="8" t="s">
         <v>39</v>
       </c>
       <c r="I171" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="J171" s="8" t="s">
         <v>940</v>
-      </c>
-      <c r="J171" s="8" t="s">
-        <v>941</v>
       </c>
       <c r="K171" s="8"/>
       <c r="L171" s="9" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="M171" s="9"/>
       <c r="N171" s="9"/>
@@ -12994,10 +12993,10 @@
         <v>28</v>
       </c>
       <c r="P171" s="8" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="Q171" s="8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="R171" s="8" t="s">
         <v>31</v>
@@ -13008,21 +13007,21 @@
     </row>
     <row r="172" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="B172" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="B172" s="8" t="s">
+      <c r="C172" s="8" t="s">
         <v>945</v>
-      </c>
-      <c r="C172" s="8" t="s">
-        <v>946</v>
       </c>
       <c r="D172" s="8"/>
       <c r="E172" s="8"/>
       <c r="F172" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H172" s="8" t="s">
         <v>39</v>
@@ -13031,27 +13030,27 @@
         <v>145</v>
       </c>
       <c r="J172" s="8" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="K172" s="8"/>
       <c r="L172" s="9" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="M172" s="9"/>
       <c r="N172" s="9" t="s">
+        <v>949</v>
+      </c>
+      <c r="O172" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P172" s="8" t="s">
         <v>950</v>
       </c>
-      <c r="O172" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="P172" s="8" t="s">
+      <c r="Q172" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="Q172" s="8" t="s">
-        <v>952</v>
-      </c>
       <c r="R172" s="8" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="S172" s="8">
         <v>3</v>
@@ -13059,50 +13058,50 @@
     </row>
     <row r="173" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="11" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B173" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="C173" s="8" t="s">
         <v>945</v>
-      </c>
-      <c r="C173" s="8" t="s">
-        <v>946</v>
       </c>
       <c r="D173" s="8"/>
       <c r="E173" s="8"/>
       <c r="F173" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H173" s="8" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I173" s="8" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J173" s="8" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="K173" s="8"/>
       <c r="L173" s="9" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="M173" s="9"/>
       <c r="N173" s="9" t="s">
+        <v>955</v>
+      </c>
+      <c r="O173" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P173" s="8" t="s">
         <v>956</v>
       </c>
-      <c r="O173" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="P173" s="8" t="s">
+      <c r="Q173" s="8" t="s">
         <v>957</v>
       </c>
-      <c r="Q173" s="8" t="s">
-        <v>958</v>
-      </c>
       <c r="R173" s="8" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="S173" s="8">
         <v>3</v>
@@ -13110,13 +13109,13 @@
     </row>
     <row r="174" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="11" t="s">
+        <v>958</v>
+      </c>
+      <c r="B174" s="8" t="s">
         <v>959</v>
       </c>
-      <c r="B174" s="8" t="s">
+      <c r="C174" s="8" t="s">
         <v>960</v>
-      </c>
-      <c r="C174" s="8" t="s">
-        <v>961</v>
       </c>
       <c r="D174" s="8"/>
       <c r="E174" s="8"/>
@@ -13124,7 +13123,7 @@
         <v>127</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H174" s="8" t="s">
         <v>39</v>
@@ -13137,7 +13136,7 @@
       </c>
       <c r="K174" s="8"/>
       <c r="L174" s="9" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="M174" s="9"/>
       <c r="N174" s="9"/>
@@ -13145,10 +13144,10 @@
         <v>323</v>
       </c>
       <c r="P174" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="Q174" s="8" t="s">
         <v>964</v>
-      </c>
-      <c r="Q174" s="8" t="s">
-        <v>965</v>
       </c>
       <c r="R174" s="8" t="s">
         <v>31</v>
@@ -13159,13 +13158,13 @@
     </row>
     <row r="175" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="11" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B175" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="C175" s="8" t="s">
         <v>960</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>961</v>
       </c>
       <c r="D175" s="8"/>
       <c r="E175" s="8"/>
@@ -13173,10 +13172,10 @@
         <v>127</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H175" s="8" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I175" s="8" t="s">
         <v>40</v>
@@ -13186,7 +13185,7 @@
       </c>
       <c r="K175" s="8"/>
       <c r="L175" s="9" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="M175" s="9"/>
       <c r="N175" s="9"/>
@@ -13194,10 +13193,10 @@
         <v>323</v>
       </c>
       <c r="P175" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="Q175" s="8" t="s">
         <v>969</v>
-      </c>
-      <c r="Q175" s="8" t="s">
-        <v>970</v>
       </c>
       <c r="R175" s="8" t="s">
         <v>31</v>
@@ -13208,13 +13207,13 @@
     </row>
     <row r="176" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="11" t="s">
+        <v>970</v>
+      </c>
+      <c r="B176" s="8" t="s">
         <v>971</v>
       </c>
-      <c r="B176" s="8" t="s">
+      <c r="C176" s="8" t="s">
         <v>972</v>
-      </c>
-      <c r="C176" s="8" t="s">
-        <v>973</v>
       </c>
       <c r="D176" s="8"/>
       <c r="E176" s="8"/>
@@ -13222,7 +13221,7 @@
         <v>22</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H176" s="8" t="s">
         <v>83</v>
@@ -13235,7 +13234,7 @@
       </c>
       <c r="K176" s="8"/>
       <c r="L176" s="9" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="M176" s="9"/>
       <c r="N176" s="9"/>
@@ -13257,13 +13256,13 @@
     </row>
     <row r="177" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="11" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B177" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="C177" s="8" t="s">
         <v>972</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>973</v>
       </c>
       <c r="D177" s="8"/>
       <c r="E177" s="8"/>
@@ -13271,7 +13270,7 @@
         <v>22</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H177" s="8" t="s">
         <v>153</v>
@@ -13284,7 +13283,7 @@
       </c>
       <c r="K177" s="8"/>
       <c r="L177" s="9" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="M177" s="9"/>
       <c r="N177" s="9"/>
@@ -13295,7 +13294,7 @@
         <v>338</v>
       </c>
       <c r="Q177" s="8" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="R177" s="8" t="s">
         <v>31</v>
@@ -13306,13 +13305,13 @@
     </row>
     <row r="178" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B178" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="C178" s="8" t="s">
         <v>972</v>
-      </c>
-      <c r="C178" s="8" t="s">
-        <v>973</v>
       </c>
       <c r="D178" s="8"/>
       <c r="E178" s="8"/>
@@ -13320,10 +13319,10 @@
         <v>22</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H178" s="8" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I178" s="8" t="s">
         <v>40</v>
@@ -13333,7 +13332,7 @@
       </c>
       <c r="K178" s="8"/>
       <c r="L178" s="9" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="M178" s="9"/>
       <c r="N178" s="9"/>
@@ -13341,10 +13340,10 @@
         <v>28</v>
       </c>
       <c r="P178" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="Q178" s="8" t="s">
         <v>982</v>
-      </c>
-      <c r="Q178" s="8" t="s">
-        <v>983</v>
       </c>
       <c r="R178" s="8" t="s">
         <v>31</v>
@@ -13355,13 +13354,13 @@
     </row>
     <row r="179" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B179" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="C179" s="8" t="s">
         <v>972</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>973</v>
       </c>
       <c r="D179" s="8"/>
       <c r="E179" s="8"/>
@@ -13369,20 +13368,20 @@
         <v>22</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H179" s="8" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="I179" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="J179" s="8" t="s">
         <v>778</v>
-      </c>
-      <c r="J179" s="8" t="s">
-        <v>779</v>
       </c>
       <c r="K179" s="8"/>
       <c r="L179" s="9" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M179" s="9"/>
       <c r="N179" s="9"/>
@@ -13390,10 +13389,10 @@
         <v>28</v>
       </c>
       <c r="P179" s="8" t="s">
+        <v>986</v>
+      </c>
+      <c r="Q179" s="8" t="s">
         <v>987</v>
-      </c>
-      <c r="Q179" s="8" t="s">
-        <v>988</v>
       </c>
       <c r="R179" s="8" t="s">
         <v>31</v>
@@ -13404,13 +13403,13 @@
     </row>
     <row r="180" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B180" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="C180" s="8" t="s">
         <v>972</v>
-      </c>
-      <c r="C180" s="8" t="s">
-        <v>973</v>
       </c>
       <c r="D180" s="8"/>
       <c r="E180" s="8"/>
@@ -13418,10 +13417,10 @@
         <v>22</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H180" s="8" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="I180" s="8" t="s">
         <v>102</v>
@@ -13431,7 +13430,7 @@
       </c>
       <c r="K180" s="8"/>
       <c r="L180" s="9" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="M180" s="9"/>
       <c r="N180" s="9"/>
@@ -13439,7 +13438,7 @@
         <v>28</v>
       </c>
       <c r="P180" s="8" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="Q180" s="8" t="s">
         <v>211</v>
@@ -13453,19 +13452,19 @@
     </row>
     <row r="181" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B181" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F181" s="8" t="s">
         <v>22</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>513</v>
@@ -13478,7 +13477,7 @@
       </c>
       <c r="K181" s="2"/>
       <c r="L181" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2" t="s">
@@ -13500,19 +13499,19 @@
     </row>
     <row r="182" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B182" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>22</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>101</v>
@@ -13525,7 +13524,7 @@
       </c>
       <c r="K182" s="2"/>
       <c r="L182" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2" t="s">
@@ -13535,7 +13534,7 @@
         <v>603</v>
       </c>
       <c r="Q182" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="R182" s="2" t="s">
         <v>31</v>
@@ -13547,19 +13546,19 @@
     </row>
     <row r="183" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F183" s="8" t="s">
         <v>22</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>111</v>
@@ -13572,7 +13571,7 @@
       </c>
       <c r="K183" s="2"/>
       <c r="L183" s="4" t="s">
-        <v>998</v>
+        <v>1359</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2" t="s">
@@ -13582,7 +13581,7 @@
         <v>382</v>
       </c>
       <c r="Q183" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="R183" s="2" t="s">
         <v>31</v>
@@ -13594,22 +13593,22 @@
     </row>
     <row r="184" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>22</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="I184" s="2" t="s">
         <v>40</v>
@@ -13619,17 +13618,17 @@
       </c>
       <c r="K184" s="2"/>
       <c r="L184" s="4" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2" t="s">
         <v>28</v>
       </c>
       <c r="P184" s="2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="Q184" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="R184" s="2" t="s">
         <v>31</v>
@@ -13641,22 +13640,22 @@
     </row>
     <row r="185" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="11" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>22</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I185" s="2" t="s">
         <v>33</v>
@@ -13666,7 +13665,7 @@
       </c>
       <c r="K185" s="2"/>
       <c r="L185" s="4" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2" t="s">
@@ -13676,7 +13675,7 @@
         <v>234</v>
       </c>
       <c r="Q185" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="R185" s="2" t="s">
         <v>31</v>
@@ -13688,22 +13687,22 @@
     </row>
     <row r="186" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B186" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>22</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="I186" s="2" t="s">
         <v>40</v>
@@ -13713,7 +13712,7 @@
       </c>
       <c r="K186" s="2"/>
       <c r="L186" s="4" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2" t="s">
@@ -13735,32 +13734,32 @@
     </row>
     <row r="187" spans="1:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>22</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="I187" s="2" t="s">
-        <v>1011</v>
+        <v>1360</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="K187" s="2"/>
       <c r="L187" s="4" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2" t="s">
@@ -13770,7 +13769,7 @@
         <v>287</v>
       </c>
       <c r="Q187" s="2" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="R187" s="2" t="s">
         <v>31</v>
@@ -13782,13 +13781,13 @@
     </row>
     <row r="188" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D188" s="8"/>
       <c r="E188" s="8"/>
@@ -13809,7 +13808,7 @@
       </c>
       <c r="K188" s="8"/>
       <c r="L188" s="9" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="M188" s="9"/>
       <c r="N188" s="9"/>
@@ -13831,13 +13830,13 @@
     </row>
     <row r="189" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D189" s="8"/>
       <c r="E189" s="8"/>
@@ -13858,7 +13857,7 @@
       </c>
       <c r="K189" s="8"/>
       <c r="L189" s="9" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="M189" s="9"/>
       <c r="N189" s="9"/>
@@ -13866,7 +13865,7 @@
         <v>28</v>
       </c>
       <c r="P189" s="8" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="Q189" s="8" t="s">
         <v>339</v>
@@ -13880,13 +13879,13 @@
     </row>
     <row r="190" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D190" s="8"/>
       <c r="E190" s="8"/>
@@ -13897,7 +13896,7 @@
         <v>100</v>
       </c>
       <c r="H190" s="8" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="I190" s="8" t="s">
         <v>102</v>
@@ -13907,7 +13906,7 @@
       </c>
       <c r="K190" s="8"/>
       <c r="L190" s="9" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="M190" s="9"/>
       <c r="N190" s="9"/>
@@ -13915,10 +13914,10 @@
         <v>65</v>
       </c>
       <c r="P190" s="8" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="Q190" s="8" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="R190" s="8" t="s">
         <v>31</v>
@@ -13929,13 +13928,13 @@
     </row>
     <row r="191" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="11" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D191" s="8"/>
       <c r="E191" s="8"/>
@@ -13956,7 +13955,7 @@
       </c>
       <c r="K191" s="8"/>
       <c r="L191" s="9" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="M191" s="9"/>
       <c r="N191" s="9"/>
@@ -13967,7 +13966,7 @@
         <v>59</v>
       </c>
       <c r="Q191" s="8" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="R191" s="8" t="s">
         <v>31</v>
@@ -13978,13 +13977,13 @@
     </row>
     <row r="192" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="11" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D192" s="8"/>
       <c r="E192" s="8"/>
@@ -13995,17 +13994,17 @@
         <v>100</v>
       </c>
       <c r="H192" s="8" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="I192" s="8" t="s">
         <v>33</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="K192" s="8"/>
       <c r="L192" s="9" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="M192" s="9"/>
       <c r="N192" s="9"/>
@@ -14013,10 +14012,10 @@
         <v>28</v>
       </c>
       <c r="P192" s="8" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="Q192" s="8" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="R192" s="8" t="s">
         <v>31</v>
@@ -14027,13 +14026,13 @@
     </row>
     <row r="193" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="11" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D193" s="8"/>
       <c r="E193" s="8"/>
@@ -14044,17 +14043,17 @@
         <v>100</v>
       </c>
       <c r="H193" s="8" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="I193" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="J193" s="8" t="s">
         <v>726</v>
-      </c>
-      <c r="J193" s="8" t="s">
-        <v>727</v>
       </c>
       <c r="K193" s="8"/>
       <c r="L193" s="9" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="M193" s="9"/>
       <c r="N193" s="9"/>
@@ -14062,10 +14061,10 @@
         <v>28</v>
       </c>
       <c r="P193" s="8" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="Q193" s="8" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="R193" s="8" t="s">
         <v>31</v>
@@ -14076,21 +14075,21 @@
     </row>
     <row r="194" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="11" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="D194" s="8"/>
       <c r="E194" s="8"/>
       <c r="F194" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="H194" s="8" t="s">
         <v>364</v>
@@ -14103,7 +14102,7 @@
       </c>
       <c r="K194" s="8"/>
       <c r="L194" s="9" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="M194" s="9"/>
       <c r="N194" s="9"/>
@@ -14114,7 +14113,7 @@
         <v>234</v>
       </c>
       <c r="Q194" s="8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="R194" s="8" t="s">
         <v>31</v>
@@ -14125,24 +14124,24 @@
     </row>
     <row r="195" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="11" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="D195" s="8"/>
       <c r="E195" s="8"/>
       <c r="F195" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="H195" s="8" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="I195" s="8" t="s">
         <v>40</v>
@@ -14152,7 +14151,7 @@
       </c>
       <c r="K195" s="8"/>
       <c r="L195" s="9" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="M195" s="9"/>
       <c r="N195" s="9"/>
@@ -14163,7 +14162,7 @@
         <v>234</v>
       </c>
       <c r="Q195" s="8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="R195" s="8" t="s">
         <v>31</v>
@@ -14174,13 +14173,13 @@
     </row>
     <row r="196" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="11" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="D196" s="8"/>
       <c r="E196" s="8"/>
@@ -14188,7 +14187,7 @@
         <v>259</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="H196" s="8" t="s">
         <v>39</v>
@@ -14201,7 +14200,7 @@
       </c>
       <c r="K196" s="8"/>
       <c r="L196" s="9" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="M196" s="9"/>
       <c r="N196" s="9"/>
@@ -14212,7 +14211,7 @@
         <v>339</v>
       </c>
       <c r="Q196" s="8" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="R196" s="8" t="s">
         <v>31</v>
@@ -14223,13 +14222,13 @@
     </row>
     <row r="197" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="D197" s="10"/>
       <c r="E197" s="10"/>
@@ -14237,20 +14236,20 @@
         <v>259</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>23</v>
       </c>
       <c r="I197" s="2" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="J197" s="2" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="K197" s="10"/>
       <c r="L197" s="4" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="M197" s="4"/>
       <c r="N197" s="4"/>
@@ -14272,13 +14271,13 @@
     </row>
     <row r="198" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="D198" s="8"/>
       <c r="E198" s="8"/>
@@ -14286,7 +14285,7 @@
         <v>163</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="H198" s="8" t="s">
         <v>310</v>
@@ -14299,7 +14298,7 @@
       </c>
       <c r="K198" s="8"/>
       <c r="L198" s="9" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="M198" s="9"/>
       <c r="N198" s="9"/>
@@ -14307,10 +14306,10 @@
         <v>323</v>
       </c>
       <c r="P198" s="8" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="Q198" s="8" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="R198" s="8" t="s">
         <v>31</v>
@@ -14321,13 +14320,13 @@
     </row>
     <row r="199" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="11" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="D199" s="10"/>
       <c r="E199" s="10"/>
@@ -14335,7 +14334,7 @@
         <v>163</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>153</v>
@@ -14344,16 +14343,16 @@
         <v>40</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="K199" s="10"/>
       <c r="L199" s="4" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="M199" s="4"/>
       <c r="N199" s="4"/>
       <c r="O199" s="2" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="P199" s="2" t="s">
         <v>287</v>
@@ -14370,13 +14369,13 @@
     </row>
     <row r="200" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D200" s="8"/>
       <c r="E200" s="8"/>
@@ -14384,7 +14383,7 @@
         <v>71</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H200" s="8" t="s">
         <v>24</v>
@@ -14397,7 +14396,7 @@
       </c>
       <c r="K200" s="8"/>
       <c r="L200" s="9" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="M200" s="9"/>
       <c r="N200" s="9"/>
@@ -14405,10 +14404,10 @@
         <v>28</v>
       </c>
       <c r="P200" s="8" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="Q200" s="8" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="R200" s="8" t="s">
         <v>31</v>
@@ -14419,13 +14418,13 @@
     </row>
     <row r="201" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="11" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D201" s="8"/>
       <c r="E201" s="8"/>
@@ -14433,7 +14432,7 @@
         <v>71</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H201" s="8" t="s">
         <v>24</v>
@@ -14446,7 +14445,7 @@
       </c>
       <c r="K201" s="8"/>
       <c r="L201" s="9" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="M201" s="9"/>
       <c r="N201" s="9"/>
@@ -14468,13 +14467,13 @@
     </row>
     <row r="202" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="11" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D202" s="8"/>
       <c r="E202" s="8"/>
@@ -14482,20 +14481,20 @@
         <v>71</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="I202" s="8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="J202" s="8" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="K202" s="8"/>
       <c r="L202" s="9" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="M202" s="9"/>
       <c r="N202" s="9"/>
@@ -14503,10 +14502,10 @@
         <v>28</v>
       </c>
       <c r="P202" s="8" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="Q202" s="8" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="R202" s="8" t="s">
         <v>31</v>
@@ -14517,13 +14516,13 @@
     </row>
     <row r="203" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="11" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="B203" s="8" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D203" s="8"/>
       <c r="E203" s="8"/>
@@ -14531,7 +14530,7 @@
         <v>71</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H203" s="8" t="s">
         <v>144</v>
@@ -14544,7 +14543,7 @@
       </c>
       <c r="K203" s="8"/>
       <c r="L203" s="9" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="M203" s="9"/>
       <c r="N203" s="9"/>
@@ -14552,10 +14551,10 @@
         <v>28</v>
       </c>
       <c r="P203" s="8" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="Q203" s="8" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="R203" s="8" t="s">
         <v>31</v>
@@ -14566,13 +14565,13 @@
     </row>
     <row r="204" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="11" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D204" s="8"/>
       <c r="E204" s="8"/>
@@ -14580,7 +14579,7 @@
         <v>71</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H204" s="8" t="s">
         <v>24</v>
@@ -14593,7 +14592,7 @@
       </c>
       <c r="K204" s="8"/>
       <c r="L204" s="9" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="M204" s="9"/>
       <c r="N204" s="9"/>
@@ -14615,13 +14614,13 @@
     </row>
     <row r="205" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="11" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D205" s="8"/>
       <c r="E205" s="8"/>
@@ -14629,20 +14628,20 @@
         <v>71</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H205" s="8" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="I205" s="8" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="J205" s="8" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="K205" s="8"/>
       <c r="L205" s="9" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M205" s="9"/>
       <c r="N205" s="9"/>
@@ -14650,10 +14649,10 @@
         <v>28</v>
       </c>
       <c r="P205" s="8" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="Q205" s="8" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="R205" s="8" t="s">
         <v>31</v>
@@ -14664,13 +14663,13 @@
     </row>
     <row r="206" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="11" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -14678,7 +14677,7 @@
         <v>71</v>
       </c>
       <c r="G206" s="10" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>76</v>
@@ -14691,7 +14690,7 @@
       </c>
       <c r="K206" s="2"/>
       <c r="L206" s="4" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="M206" s="3"/>
       <c r="N206" s="2"/>
@@ -14702,7 +14701,7 @@
         <v>287</v>
       </c>
       <c r="Q206" s="2" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="R206" s="2" t="s">
         <v>31</v>
@@ -14713,13 +14712,13 @@
     </row>
     <row r="207" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -14727,7 +14726,7 @@
         <v>71</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>181</v>
@@ -14740,7 +14739,7 @@
       </c>
       <c r="K207" s="2"/>
       <c r="L207" s="4" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="M207" s="3"/>
       <c r="N207" s="2"/>
@@ -14748,10 +14747,10 @@
         <v>28</v>
       </c>
       <c r="P207" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="Q207" s="2" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="R207" s="2" t="s">
         <v>31</v>
@@ -14762,13 +14761,13 @@
     </row>
     <row r="208" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -14776,10 +14775,10 @@
         <v>71</v>
       </c>
       <c r="G208" s="10" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I208" s="2" t="s">
         <v>91</v>
@@ -14789,7 +14788,7 @@
       </c>
       <c r="K208" s="2"/>
       <c r="L208" s="4" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="M208" s="3"/>
       <c r="N208" s="2"/>
@@ -14797,7 +14796,7 @@
         <v>28</v>
       </c>
       <c r="P208" s="2" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="Q208" s="2" t="s">
         <v>30</v>
@@ -14811,13 +14810,13 @@
     </row>
     <row r="209" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -14825,7 +14824,7 @@
         <v>71</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>258</v>
@@ -14838,10 +14837,10 @@
       </c>
       <c r="K209" s="2"/>
       <c r="L209" s="4" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="M209" s="4" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2" t="s">
@@ -14851,7 +14850,7 @@
         <v>396</v>
       </c>
       <c r="Q209" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="R209" s="2" t="s">
         <v>31</v>
@@ -14862,13 +14861,13 @@
     </row>
     <row r="210" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -14876,7 +14875,7 @@
         <v>71</v>
       </c>
       <c r="G210" s="10" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>258</v>
@@ -14889,10 +14888,10 @@
       </c>
       <c r="K210" s="2"/>
       <c r="L210" s="4" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="M210" s="4" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2" t="s">
@@ -14902,7 +14901,7 @@
         <v>396</v>
       </c>
       <c r="Q210" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="R210" s="2" t="s">
         <v>31</v>
@@ -14913,13 +14912,13 @@
     </row>
     <row r="211" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="11" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="D211" s="8"/>
       <c r="E211" s="8"/>
@@ -14930,7 +14929,7 @@
         <v>350</v>
       </c>
       <c r="H211" s="8" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I211" s="8" t="s">
         <v>40</v>
@@ -14940,7 +14939,7 @@
       </c>
       <c r="K211" s="8"/>
       <c r="L211" s="9" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="M211" s="9"/>
       <c r="N211" s="9"/>
@@ -14948,10 +14947,10 @@
         <v>28</v>
       </c>
       <c r="P211" s="8" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="Q211" s="8" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="R211" s="8" t="s">
         <v>31</v>
@@ -14962,13 +14961,13 @@
     </row>
     <row r="212" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="11" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="D212" s="8"/>
       <c r="E212" s="8"/>
@@ -14989,7 +14988,7 @@
       </c>
       <c r="K212" s="8"/>
       <c r="L212" s="9" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="M212" s="9"/>
       <c r="N212" s="9"/>
@@ -15011,13 +15010,13 @@
     </row>
     <row r="213" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="11" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="D213" s="8"/>
       <c r="E213" s="8"/>
@@ -15028,17 +15027,17 @@
         <v>23</v>
       </c>
       <c r="H213" s="8" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="I213" s="8" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="J213" s="8" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="K213" s="8"/>
       <c r="L213" s="9" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="M213" s="9"/>
       <c r="N213" s="9"/>
@@ -15046,10 +15045,10 @@
         <v>28</v>
       </c>
       <c r="P213" s="8" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="Q213" s="8" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="R213" s="8" t="s">
         <v>31</v>
@@ -15060,13 +15059,13 @@
     </row>
     <row r="214" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="D214" s="8"/>
       <c r="E214" s="8"/>
@@ -15077,7 +15076,7 @@
         <v>23</v>
       </c>
       <c r="H214" s="8" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="I214" s="8" t="s">
         <v>33</v>
@@ -15087,7 +15086,7 @@
       </c>
       <c r="K214" s="8"/>
       <c r="L214" s="9" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="M214" s="9"/>
       <c r="N214" s="9"/>
@@ -15095,10 +15094,10 @@
         <v>28</v>
       </c>
       <c r="P214" s="8" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="Q214" s="8" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="R214" s="8" t="s">
         <v>31</v>
@@ -15109,13 +15108,13 @@
     </row>
     <row r="215" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="11" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="D215" s="8"/>
       <c r="E215" s="8"/>
@@ -15136,7 +15135,7 @@
       </c>
       <c r="K215" s="8"/>
       <c r="L215" s="9" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="M215" s="9"/>
       <c r="N215" s="9"/>
@@ -15150,7 +15149,7 @@
         <v>114.5</v>
       </c>
       <c r="R215" s="8" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="S215" s="8">
         <v>3</v>
@@ -15158,13 +15157,13 @@
     </row>
     <row r="216" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="D216" s="8"/>
       <c r="E216" s="8"/>
@@ -15185,7 +15184,7 @@
       </c>
       <c r="K216" s="8"/>
       <c r="L216" s="9" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="M216" s="9"/>
       <c r="N216" s="9"/>
@@ -15199,7 +15198,7 @@
         <v>129</v>
       </c>
       <c r="R216" s="8" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="S216" s="8">
         <v>3</v>
@@ -15207,13 +15206,13 @@
     </row>
     <row r="217" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="D217" s="8"/>
       <c r="E217" s="8"/>
@@ -15234,7 +15233,7 @@
       </c>
       <c r="K217" s="8"/>
       <c r="L217" s="9" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="M217" s="9"/>
       <c r="N217" s="9"/>
@@ -15242,10 +15241,10 @@
         <v>28</v>
       </c>
       <c r="P217" s="8" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="Q217" s="8" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="R217" s="8" t="s">
         <v>31</v>
@@ -15256,13 +15255,13 @@
     </row>
     <row r="218" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C218" s="8" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="D218" s="8"/>
       <c r="E218" s="8"/>
@@ -15273,7 +15272,7 @@
         <v>374</v>
       </c>
       <c r="H218" s="8" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="I218" s="8" t="s">
         <v>40</v>
@@ -15283,7 +15282,7 @@
       </c>
       <c r="K218" s="8"/>
       <c r="L218" s="9" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="M218" s="9"/>
       <c r="N218" s="9"/>
@@ -15291,10 +15290,10 @@
         <v>28</v>
       </c>
       <c r="P218" s="8" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="Q218" s="8" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="R218" s="8" t="s">
         <v>31</v>
@@ -15305,13 +15304,13 @@
     </row>
     <row r="219" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C219" s="8" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="D219" s="8"/>
       <c r="E219" s="8"/>
@@ -15322,7 +15321,7 @@
         <v>374</v>
       </c>
       <c r="H219" s="8" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="I219" s="8" t="s">
         <v>40</v>
@@ -15332,7 +15331,7 @@
       </c>
       <c r="K219" s="8"/>
       <c r="L219" s="9" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="M219" s="9"/>
       <c r="N219" s="9"/>
@@ -15343,7 +15342,7 @@
         <v>211</v>
       </c>
       <c r="Q219" s="8" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="R219" s="8" t="s">
         <v>31</v>
@@ -15354,13 +15353,13 @@
     </row>
     <row r="220" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -15371,17 +15370,17 @@
         <v>374</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="I220" s="2" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="J220" s="2" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="K220" s="2"/>
       <c r="L220" s="4" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="M220" s="3"/>
       <c r="N220" s="3"/>
@@ -15389,7 +15388,7 @@
         <v>28</v>
       </c>
       <c r="P220" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="Q220" s="2" t="s">
         <v>217</v>
@@ -15403,13 +15402,13 @@
     </row>
     <row r="221" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="11" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -15420,17 +15419,17 @@
         <v>374</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="I221" s="2" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="J221" s="2" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="K221" s="2"/>
       <c r="L221" s="4" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="M221" s="3"/>
       <c r="N221" s="3"/>
@@ -15452,24 +15451,24 @@
     </row>
     <row r="222" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="D222" s="8"/>
       <c r="E222" s="8"/>
       <c r="F222" s="8" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H222" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I222" s="8" t="s">
         <v>40</v>
@@ -15479,7 +15478,7 @@
       </c>
       <c r="K222" s="8"/>
       <c r="L222" s="9" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="M222" s="9"/>
       <c r="N222" s="9"/>
@@ -15490,7 +15489,7 @@
         <v>179</v>
       </c>
       <c r="Q222" s="8" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="R222" s="8" t="s">
         <v>31</v>
@@ -15501,24 +15500,24 @@
     </row>
     <row r="223" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="11" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="B223" s="8" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="D223" s="8"/>
       <c r="E223" s="8"/>
       <c r="F223" s="8" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H223" s="8" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="I223" s="8" t="s">
         <v>40</v>
@@ -15528,7 +15527,7 @@
       </c>
       <c r="K223" s="8"/>
       <c r="L223" s="9" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="M223" s="9"/>
       <c r="N223" s="9"/>
@@ -15536,10 +15535,10 @@
         <v>28</v>
       </c>
       <c r="P223" s="8" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="Q223" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R223" s="8" t="s">
         <v>31</v>
@@ -15550,34 +15549,34 @@
     </row>
     <row r="224" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="D224" s="8"/>
       <c r="E224" s="8"/>
       <c r="F224" s="8" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>564</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I224" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="J224" s="8" t="s">
         <v>778</v>
-      </c>
-      <c r="J224" s="8" t="s">
-        <v>779</v>
       </c>
       <c r="K224" s="8"/>
       <c r="L224" s="9" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="M224" s="9"/>
       <c r="N224" s="9"/>
@@ -15585,10 +15584,10 @@
         <v>28</v>
       </c>
       <c r="P224" s="8" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="Q224" s="8" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="R224" s="8" t="s">
         <v>503</v>
@@ -15599,18 +15598,18 @@
     </row>
     <row r="225" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="D225" s="8"/>
       <c r="E225" s="8"/>
       <c r="F225" s="8" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>564</v>
@@ -15626,20 +15625,20 @@
       </c>
       <c r="K225" s="8"/>
       <c r="L225" s="9" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="M225" s="9"/>
       <c r="N225" s="9" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="O225" s="8" t="s">
         <v>28</v>
       </c>
       <c r="P225" s="8" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="Q225" s="8" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="R225" s="8" t="s">
         <v>503</v>
@@ -15650,34 +15649,34 @@
     </row>
     <row r="226" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="D226" s="8"/>
       <c r="E226" s="8"/>
       <c r="F226" s="8" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G226" s="8" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H226" s="8" t="s">
         <v>46</v>
       </c>
       <c r="I226" s="8" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="J226" s="8" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="K226" s="8"/>
       <c r="L226" s="9" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="M226" s="9"/>
       <c r="N226" s="9"/>
@@ -15685,10 +15684,10 @@
         <v>28</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="Q226" s="8" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="R226" s="8" t="s">
         <v>503</v>
@@ -15699,34 +15698,34 @@
     </row>
     <row r="227" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="D227" s="8"/>
       <c r="E227" s="8"/>
       <c r="F227" s="8" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G227" s="8" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H227" s="8" t="s">
         <v>55</v>
       </c>
       <c r="I227" s="8" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="J227" s="8" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="K227" s="8"/>
       <c r="L227" s="9" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="M227" s="9"/>
       <c r="N227" s="9"/>
@@ -15734,10 +15733,10 @@
         <v>28</v>
       </c>
       <c r="P227" s="8" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="Q227" s="8" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="R227" s="8" t="s">
         <v>503</v>
@@ -15748,18 +15747,18 @@
     </row>
     <row r="228" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="D228" s="8"/>
       <c r="E228" s="8"/>
       <c r="F228" s="8" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G228" s="8" t="s">
         <v>39</v>
@@ -15775,7 +15774,7 @@
       </c>
       <c r="K228" s="8"/>
       <c r="L228" s="9" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="M228" s="9"/>
       <c r="N228" s="9"/>
@@ -15783,13 +15782,13 @@
         <v>28</v>
       </c>
       <c r="P228" s="8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="Q228" s="8" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="R228" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S228" s="8">
         <v>1</v>
@@ -15797,24 +15796,24 @@
     </row>
     <row r="229" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="11" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="D229" s="8"/>
       <c r="E229" s="8"/>
       <c r="F229" s="8" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G229" s="8" t="s">
         <v>39</v>
       </c>
       <c r="H229" s="8" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="I229" s="8" t="s">
         <v>33</v>
@@ -15824,7 +15823,7 @@
       </c>
       <c r="K229" s="8"/>
       <c r="L229" s="9" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="M229" s="9"/>
       <c r="N229" s="9"/>
@@ -15832,13 +15831,13 @@
         <v>28</v>
       </c>
       <c r="P229" s="8" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="Q229" s="8" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="R229" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S229" s="8">
         <v>1</v>
@@ -15846,24 +15845,24 @@
     </row>
     <row r="230" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="D230" s="8"/>
       <c r="E230" s="8"/>
       <c r="F230" s="8" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G230" s="8" t="s">
         <v>39</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="I230" s="8" t="s">
         <v>102</v>
@@ -15873,7 +15872,7 @@
       </c>
       <c r="K230" s="8"/>
       <c r="L230" s="9" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="M230" s="9"/>
       <c r="N230" s="9"/>
@@ -15887,7 +15886,7 @@
         <v>230</v>
       </c>
       <c r="R230" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S230" s="8">
         <v>1</v>
@@ -15895,18 +15894,18 @@
     </row>
     <row r="231" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="11" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="D231" s="8"/>
       <c r="E231" s="8"/>
       <c r="F231" s="8" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G231" s="8" t="s">
         <v>39</v>
@@ -15915,14 +15914,14 @@
         <v>364</v>
       </c>
       <c r="I231" s="8" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="J231" s="8" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="K231" s="8"/>
       <c r="L231" s="9" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="M231" s="9"/>
       <c r="N231" s="9"/>
@@ -15930,13 +15929,13 @@
         <v>28</v>
       </c>
       <c r="P231" s="8" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="Q231" s="8" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="R231" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S231" s="8">
         <v>1</v>
@@ -15944,18 +15943,18 @@
     </row>
     <row r="232" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="11" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="D232" s="8"/>
       <c r="E232" s="8"/>
       <c r="F232" s="8" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G232" s="8" t="s">
         <v>39</v>
@@ -15971,7 +15970,7 @@
       </c>
       <c r="K232" s="8"/>
       <c r="L232" s="9" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="M232" s="9"/>
       <c r="N232" s="9"/>
@@ -15979,13 +15978,13 @@
         <v>28</v>
       </c>
       <c r="P232" s="8" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="Q232" s="8" t="s">
         <v>234</v>
       </c>
       <c r="R232" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S232" s="8">
         <v>1</v>
@@ -15993,34 +15992,34 @@
     </row>
     <row r="233" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="11" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="D233" s="8"/>
       <c r="E233" s="8"/>
       <c r="F233" s="8" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G233" s="8" t="s">
         <v>39</v>
       </c>
       <c r="H233" s="8" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I233" s="8" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="J233" s="8" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="K233" s="8"/>
       <c r="L233" s="9" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="M233" s="9"/>
       <c r="N233" s="9"/>
@@ -16031,10 +16030,10 @@
         <v>175</v>
       </c>
       <c r="Q233" s="8" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="R233" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S233" s="8">
         <v>1</v>
@@ -16042,18 +16041,18 @@
     </row>
     <row r="234" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="11" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="D234" s="10"/>
       <c r="E234" s="10"/>
       <c r="F234" s="2" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>39</v>
@@ -16062,14 +16061,14 @@
         <v>364</v>
       </c>
       <c r="I234" s="2" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="J234" s="2" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="K234" s="10"/>
       <c r="L234" s="4" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="M234" s="4"/>
       <c r="N234" s="4"/>
@@ -16077,13 +16076,13 @@
         <v>28</v>
       </c>
       <c r="P234" s="2" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="Q234" s="2" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="R234" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S234" s="2">
         <v>1</v>
@@ -16091,18 +16090,18 @@
     </row>
     <row r="235" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="11" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="D235" s="10"/>
       <c r="E235" s="10"/>
       <c r="F235" s="2" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>39</v>
@@ -16111,14 +16110,14 @@
         <v>39</v>
       </c>
       <c r="I235" s="2" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="J235" s="2" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="K235" s="10"/>
       <c r="L235" s="4" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="M235" s="4"/>
       <c r="N235" s="4"/>
@@ -16126,13 +16125,13 @@
         <v>28</v>
       </c>
       <c r="P235" s="2" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="Q235" s="2" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="R235" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S235" s="2">
         <v>1</v>
@@ -16140,34 +16139,34 @@
     </row>
     <row r="236" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="11" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="D236" s="10"/>
       <c r="E236" s="10"/>
       <c r="F236" s="2" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="I236" s="2" t="s">
         <v>569</v>
       </c>
       <c r="J236" s="2" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="K236" s="10"/>
       <c r="L236" s="4" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="M236" s="4"/>
       <c r="N236" s="4"/>
@@ -16175,13 +16174,13 @@
         <v>28</v>
       </c>
       <c r="P236" s="2" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="Q236" s="2" t="s">
         <v>106</v>
       </c>
       <c r="R236" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S236" s="2">
         <v>1</v>
@@ -16189,18 +16188,18 @@
     </row>
     <row r="237" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="11" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="D237" s="10"/>
       <c r="E237" s="10"/>
       <c r="F237" s="2" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>39</v>
@@ -16216,7 +16215,7 @@
       </c>
       <c r="K237" s="10"/>
       <c r="L237" s="4" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="M237" s="4"/>
       <c r="N237" s="4"/>
@@ -16224,13 +16223,13 @@
         <v>28</v>
       </c>
       <c r="P237" s="2" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="Q237" s="2" t="s">
         <v>155</v>
       </c>
       <c r="R237" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="S237" s="2">
         <v>1</v>
@@ -16238,24 +16237,24 @@
     </row>
     <row r="238" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="B238" s="8" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C238" s="8" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="D238" s="8"/>
       <c r="E238" s="8"/>
       <c r="F238" s="8" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="G238" s="8" t="s">
         <v>53</v>
       </c>
       <c r="H238" s="8" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="I238" s="8" t="s">
         <v>102</v>
@@ -16265,18 +16264,18 @@
       </c>
       <c r="K238" s="8"/>
       <c r="L238" s="9" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="M238" s="9"/>
       <c r="N238" s="9"/>
       <c r="O238" s="8" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="P238" s="8" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="Q238" s="8" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="R238" s="8" t="s">
         <v>191</v>
@@ -16287,24 +16286,24 @@
     </row>
     <row r="239" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C239" s="8" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="D239" s="8"/>
       <c r="E239" s="8"/>
       <c r="F239" s="8" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>53</v>
       </c>
       <c r="H239" s="8" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="I239" s="8" t="s">
         <v>102</v>
@@ -16314,18 +16313,18 @@
       </c>
       <c r="K239" s="8"/>
       <c r="L239" s="9" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="M239" s="9"/>
       <c r="N239" s="9"/>
       <c r="O239" s="8" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="P239" s="8" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="Q239" s="8" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="R239" s="8" t="s">
         <v>191</v>
@@ -16336,13 +16335,13 @@
     </row>
     <row r="240" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C240" s="8" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="D240" s="8"/>
       <c r="E240" s="8"/>
@@ -16350,10 +16349,10 @@
         <v>549</v>
       </c>
       <c r="G240" s="8" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H240" s="8" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I240" s="8" t="s">
         <v>40</v>
@@ -16363,7 +16362,7 @@
       </c>
       <c r="K240" s="8"/>
       <c r="L240" s="9" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="M240" s="9"/>
       <c r="N240" s="9"/>
@@ -16371,10 +16370,10 @@
         <v>28</v>
       </c>
       <c r="P240" s="8" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="Q240" s="8" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="R240" s="8" t="s">
         <v>31</v>
@@ -16385,13 +16384,13 @@
     </row>
     <row r="241" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="11" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C241" s="8" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="D241" s="8"/>
       <c r="E241" s="8"/>
@@ -16399,7 +16398,7 @@
         <v>549</v>
       </c>
       <c r="G241" s="8" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H241" s="8" t="s">
         <v>83</v>
@@ -16412,7 +16411,7 @@
       </c>
       <c r="K241" s="8"/>
       <c r="L241" s="9" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="M241" s="9"/>
       <c r="N241" s="9"/>
@@ -16423,7 +16422,7 @@
         <v>526</v>
       </c>
       <c r="Q241" s="8" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="R241" s="8" t="s">
         <v>31</v>
@@ -16434,21 +16433,21 @@
     </row>
     <row r="242" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
       <c r="F242" s="3" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>259</v>
@@ -16461,7 +16460,7 @@
       </c>
       <c r="K242" s="3"/>
       <c r="L242" s="4" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="M242" s="3"/>
       <c r="N242" s="3"/>
@@ -16472,7 +16471,7 @@
         <v>268</v>
       </c>
       <c r="Q242" s="2" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="R242" s="2" t="s">
         <v>31</v>
@@ -16483,24 +16482,24 @@
     </row>
     <row r="243" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
       <c r="F243" s="3" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="I243" s="2" t="s">
         <v>431</v>
@@ -16510,7 +16509,7 @@
       </c>
       <c r="K243" s="3"/>
       <c r="L243" s="4" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="M243" s="3"/>
       <c r="N243" s="3"/>
@@ -16518,7 +16517,7 @@
         <v>28</v>
       </c>
       <c r="P243" s="2" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="Q243" s="2" t="s">
         <v>262</v>
@@ -16532,13 +16531,13 @@
     </row>
     <row r="244" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -16546,7 +16545,7 @@
         <v>591</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>597</v>
@@ -16559,7 +16558,7 @@
       </c>
       <c r="K244" s="3"/>
       <c r="L244" s="4" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="M244" s="3"/>
       <c r="N244" s="3"/>
@@ -16570,7 +16569,7 @@
         <v>396</v>
       </c>
       <c r="Q244" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="R244" s="2" t="s">
         <v>31</v>
@@ -16581,13 +16580,13 @@
     </row>
     <row r="245" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -16595,10 +16594,10 @@
         <v>591</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="I245" s="2" t="s">
         <v>40</v>
@@ -16608,7 +16607,7 @@
       </c>
       <c r="K245" s="3"/>
       <c r="L245" s="4" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="M245" s="3"/>
       <c r="N245" s="3"/>
@@ -16616,10 +16615,10 @@
         <v>28</v>
       </c>
       <c r="P245" s="2" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="Q245" s="2" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="R245" s="2" t="s">
         <v>31</v>
@@ -16630,21 +16629,21 @@
     </row>
     <row r="246" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
       <c r="F246" s="3" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>76</v>
@@ -16657,7 +16656,7 @@
       </c>
       <c r="K246" s="3"/>
       <c r="L246" s="4" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="M246" s="3"/>
       <c r="N246" s="3"/>
@@ -16665,10 +16664,10 @@
         <v>28</v>
       </c>
       <c r="P246" s="2" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="Q246" s="2" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="R246" s="2" t="s">
         <v>31</v>
@@ -16679,34 +16678,34 @@
     </row>
     <row r="247" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
       <c r="F247" s="3" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I247" s="2" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="J247" s="2" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="K247" s="3"/>
       <c r="L247" s="4" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="M247" s="3"/>
       <c r="N247" s="3"/>
@@ -16714,10 +16713,10 @@
         <v>28</v>
       </c>
       <c r="P247" s="2" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="Q247" s="2" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="R247" s="2" t="s">
         <v>31</v>
@@ -16728,34 +16727,34 @@
     </row>
     <row r="248" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
       <c r="F248" s="3" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="G248" s="3" t="s">
         <v>498</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I248" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="J248" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="J248" s="2" t="s">
-        <v>692</v>
       </c>
       <c r="K248" s="3"/>
       <c r="L248" s="4" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="M248" s="3"/>
       <c r="N248" s="3"/>
@@ -16763,13 +16762,13 @@
         <v>28</v>
       </c>
       <c r="P248" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="Q248" s="2" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="R248" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="S248" s="2">
         <v>3</v>
@@ -16777,34 +16776,34 @@
     </row>
     <row r="249" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
       <c r="F249" s="3" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="G249" s="3" t="s">
         <v>498</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I249" s="2" t="s">
         <v>145</v>
       </c>
       <c r="J249" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="K249" s="3"/>
       <c r="L249" s="4" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="M249" s="3"/>
       <c r="N249" s="3"/>
@@ -16818,7 +16817,7 @@
         <v>271</v>
       </c>
       <c r="R249" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="S249" s="2">
         <v>3</v>
@@ -16826,21 +16825,21 @@
     </row>
     <row r="250" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
       <c r="F250" s="3" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>23</v>
@@ -16853,7 +16852,7 @@
       </c>
       <c r="K250" s="3"/>
       <c r="L250" s="4" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="M250" s="3"/>
       <c r="N250" s="3"/>
@@ -16861,10 +16860,10 @@
         <v>28</v>
       </c>
       <c r="P250" s="2" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="Q250" s="2" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="R250" s="2" t="s">
         <v>503</v>
@@ -16875,34 +16874,34 @@
     </row>
     <row r="251" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
       <c r="F251" s="3" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>55</v>
       </c>
       <c r="I251" s="2" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="J251" s="2" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="K251" s="3"/>
       <c r="L251" s="4" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="M251" s="3"/>
       <c r="N251" s="3"/>
@@ -16924,34 +16923,34 @@
     </row>
     <row r="252" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
       <c r="F252" s="3" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>528</v>
       </c>
       <c r="I252" s="2" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="J252" s="2" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="K252" s="3"/>
       <c r="L252" s="4" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="M252" s="3"/>
       <c r="N252" s="3"/>
@@ -16959,10 +16958,10 @@
         <v>28</v>
       </c>
       <c r="P252" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="Q252" s="2" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="R252" s="2" t="s">
         <v>60</v>
@@ -16973,13 +16972,13 @@
     </row>
     <row r="253" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -16987,7 +16986,7 @@
         <v>99</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>259</v>
@@ -17000,7 +16999,7 @@
       </c>
       <c r="K253" s="3"/>
       <c r="L253" s="4" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="M253" s="3"/>
       <c r="N253" s="3"/>
@@ -17008,10 +17007,10 @@
         <v>28</v>
       </c>
       <c r="P253" s="2" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="Q253" s="2" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="R253" s="2" t="s">
         <v>503</v>
@@ -17022,13 +17021,13 @@
     </row>
     <row r="254" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -17036,20 +17035,20 @@
         <v>99</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>279</v>
       </c>
       <c r="I254" s="2" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="J254" s="2" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="K254" s="3"/>
       <c r="L254" s="4" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="M254" s="3"/>
       <c r="N254" s="3"/>
@@ -17057,10 +17056,10 @@
         <v>28</v>
       </c>
       <c r="P254" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="Q254" s="2" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="R254" s="2" t="s">
         <v>503</v>
@@ -17071,45 +17070,45 @@
     </row>
     <row r="255" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
       <c r="F255" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I255" s="2" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="J255" s="2" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="K255" s="3"/>
       <c r="L255" s="4" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="M255" s="3"/>
       <c r="N255" s="3"/>
       <c r="O255" s="2" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="P255" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="Q255" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="R255" s="2" t="s">
         <v>60</v>
@@ -17120,21 +17119,21 @@
     </row>
     <row r="256" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
       <c r="F256" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>23</v>
@@ -17147,12 +17146,12 @@
       </c>
       <c r="K256" s="3"/>
       <c r="L256" s="4" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="M256" s="3"/>
       <c r="N256" s="3"/>
       <c r="O256" s="2" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="P256" s="2" t="s">
         <v>158</v>
@@ -17169,21 +17168,21 @@
     </row>
     <row r="257" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
       <c r="F257" s="3" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>364</v>
@@ -17196,7 +17195,7 @@
       </c>
       <c r="K257" s="3"/>
       <c r="L257" s="4" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="M257" s="3"/>
       <c r="N257" s="3"/>
@@ -17204,13 +17203,13 @@
         <v>28</v>
       </c>
       <c r="P257" s="2" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="Q257" s="2" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="R257" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="S257" s="2">
         <v>3</v>
@@ -17218,21 +17217,21 @@
     </row>
     <row r="258" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
       <c r="F258" s="3" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>310</v>
@@ -17241,11 +17240,11 @@
         <v>569</v>
       </c>
       <c r="J258" s="2" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="K258" s="3"/>
       <c r="L258" s="4" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="M258" s="3"/>
       <c r="N258" s="3"/>
@@ -17253,13 +17252,13 @@
         <v>28</v>
       </c>
       <c r="P258" s="2" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="Q258" s="2" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="R258" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="S258" s="2">
         <v>3</v>
@@ -17267,13 +17266,13 @@
     </row>
     <row r="259" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -17287,28 +17286,28 @@
         <v>62</v>
       </c>
       <c r="I259" s="2" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="J259" s="2" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="K259" s="3"/>
       <c r="L259" s="4" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="M259" s="3"/>
       <c r="N259" s="3"/>
       <c r="O259" s="2" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="P259" s="2" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="Q259" s="2" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="R259" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="S259" s="2">
         <v>3</v>
@@ -17316,13 +17315,13 @@
     </row>
     <row r="260" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -17343,21 +17342,21 @@
       </c>
       <c r="K260" s="3"/>
       <c r="L260" s="4" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="M260" s="3"/>
       <c r="N260" s="3"/>
       <c r="O260" s="2" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="P260" s="2" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="Q260" s="2" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="R260" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="S260" s="2">
         <v>3</v>
@@ -17365,21 +17364,21 @@
     </row>
     <row r="261" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
       <c r="F261" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>310</v>
@@ -17388,25 +17387,25 @@
         <v>40</v>
       </c>
       <c r="J261" s="2" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="K261" s="3"/>
       <c r="L261" s="4" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="M261" s="3"/>
       <c r="N261" s="3"/>
       <c r="O261" s="2" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="P261" s="2" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="Q261" s="2" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="R261" s="2" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="S261" s="2">
         <v>2</v>
@@ -17414,48 +17413,48 @@
     </row>
     <row r="262" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
       <c r="F262" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I262" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J262" s="2" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="K262" s="3"/>
       <c r="L262" s="4" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="M262" s="3"/>
       <c r="N262" s="3"/>
       <c r="O262" s="2" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="P262" s="2" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="Q262" s="2" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="R262" s="2" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="S262" s="2">
         <v>2</v>
@@ -17463,48 +17462,48 @@
     </row>
     <row r="263" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
       <c r="F263" s="3" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="G263" s="3" t="s">
         <v>430</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="I263" s="2" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="J263" s="2" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="K263" s="3"/>
       <c r="L263" s="4" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="M263" s="3"/>
       <c r="N263" s="3"/>
       <c r="O263" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="P263" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="Q263" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="R263" s="2" t="s">
         <v>1352</v>
-      </c>
-      <c r="P263" s="2" t="s">
-        <v>1353</v>
-      </c>
-      <c r="Q263" s="2" t="s">
-        <v>1354</v>
-      </c>
-      <c r="R263" s="2" t="s">
-        <v>1355</v>
       </c>
       <c r="S263" s="2">
         <v>1</v>
@@ -17512,48 +17511,48 @@
     </row>
     <row r="264" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
       <c r="F264" s="3" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="G264" s="3" t="s">
         <v>430</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="I264" s="2" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="J264" s="2" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="K264" s="3"/>
       <c r="L264" s="4" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="M264" s="3"/>
       <c r="N264" s="3"/>
       <c r="O264" s="2" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="P264" s="2" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="Q264" s="2" t="s">
         <v>81</v>
       </c>
       <c r="R264" s="2" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="S264" s="2">
         <v>2</v>
@@ -17663,167 +17662,167 @@
     <hyperlink ref="A101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
     <hyperlink ref="A102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
     <hyperlink ref="A103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="A104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="A105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="A106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="A107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="A108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="A109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="A110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="A111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="A112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="A113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="A114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="A115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="A116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="A117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="A118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="A119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="A120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="A121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="A122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="A123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="A124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="A125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="A126" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="A127" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="A128" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="A129" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="A130" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="A131" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="A132" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="A133" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="A134" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="A135" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="A136" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="A137" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="A138" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="A139" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="A140" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="A141" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="A142" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="A143" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="A144" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="A145" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="A146" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="A147" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="A148" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="A149" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="A150" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="A151" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="A152" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="A153" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="A154" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="A155" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="A156" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="A157" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="A158" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="A159" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="A160" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="A161" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="A162" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="A163" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="A164" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="A165" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="A166" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="A167" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="A168" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="A169" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="A170" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="A171" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="A172" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="A173" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="A174" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="A175" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="A176" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="A177" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="A178" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="A179" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="A180" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="A181" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="A182" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="A183" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="A184" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="A185" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="A186" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="A187" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="A188" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="A189" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="A190" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="A191" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="A192" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="A193" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="A194" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="A195" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="A196" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="A197" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="A198" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="A199" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="A200" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="A201" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="A202" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="A203" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="A204" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="A205" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="A206" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="A207" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="A208" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="A209" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="A210" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="A211" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="A212" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="A213" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="A214" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="A215" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="A216" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="A217" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="A218" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="A219" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="A220" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="A221" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="A222" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="A223" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="A224" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="A225" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="A226" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="A227" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="A228" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="A229" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="A230" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="A231" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="A232" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="A233" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="A234" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="A235" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="A236" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="A237" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="A238" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="A239" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="A240" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="A241" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="A242" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="A243" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="A244" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="A245" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="A246" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="A247" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="A248" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="A249" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="A250" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="A251" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="A252" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="A253" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="A254" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="A255" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="A256" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="A257" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="A258" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="A259" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="A260" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="A261" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="A262" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="A263" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="A264" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="A105" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="A106" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="A107" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="A108" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="A109" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="A110" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="A111" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="A112" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="A113" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="A114" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="A115" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="A116" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="A117" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="A118" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="A119" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="A120" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="A121" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="A122" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="A123" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="A124" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="A125" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="A126" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="A127" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="A128" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="A129" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="A130" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="A131" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="A132" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="A133" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="A134" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="A135" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="A136" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="A137" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="A138" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="A139" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="A140" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="A141" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="A142" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="A143" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="A144" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="A145" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="A146" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="A147" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="A148" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="A149" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="A150" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="A151" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="A152" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="A153" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="A154" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="A155" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="A156" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="A157" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="A158" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="A159" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="A160" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="A161" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="A162" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="A163" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="A164" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="A165" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="A166" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="A167" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="A168" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="A169" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="A170" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="A171" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="A172" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="A173" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="A174" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="A175" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="A176" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="A177" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="A178" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="A179" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="A180" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="A181" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="A182" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="A183" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="A184" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="A185" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="A186" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="A187" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="A188" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="A189" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="A190" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="A191" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="A192" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="A193" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="A194" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="A195" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="A196" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="A197" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="A198" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="A199" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="A200" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="A201" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="A202" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="A203" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="A204" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="A205" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="A206" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="A207" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="A208" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="A209" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="A210" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="A211" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="A212" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="A213" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="A214" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="A215" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="A216" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="A217" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="A218" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="A219" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="A220" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="A221" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="A222" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="A223" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="A224" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="A225" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="A226" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="A227" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="A228" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="A229" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="A230" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="A231" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="A232" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="A233" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="A234" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="A235" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="A236" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="A237" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="A238" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="A239" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="A240" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="A241" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="A242" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="A243" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="A244" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="A245" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="A246" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="A247" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="A248" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="A249" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="A250" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="A251" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="A252" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="A253" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="A254" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="A255" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="A256" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="A257" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="A258" r:id="rId256" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="A259" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="A260" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="A261" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="A262" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="A263" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="A264" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="A104" r:id="rId263" xr:uid="{F2EC9C13-C593-4D2B-93DB-6A936C5AC211}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-19e.xlsx
+++ b/quizzes/peinture-19e.xlsx
@@ -10318,7 +10318,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>environ 1830-1832</t>
+          <t>1830-1832 environ</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>environ 1830-1832</t>
+          <t>1830-1832 environ</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
